--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE856C5-9D7C-4616-93C8-3BEB796FFB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4433DD-4579-49B3-9EBA-F5158F0986B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4433DD-4579-49B3-9EBA-F5158F0986B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B3D36F-790D-48FD-A8CA-D5B357136F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Theo dõi HĐ_Chi tiết" sheetId="2" r:id="rId1"/>
@@ -39034,7 +39034,6 @@
         <v>95</v>
       </c>
       <c r="C8" s="189">
-        <f>9600000*0.8</f>
         <v>7680000</v>
       </c>
       <c r="D8" s="189"/>
@@ -39329,7 +39328,6 @@
         <v>257</v>
       </c>
       <c r="C11" s="189">
-        <f>10800000*0.8</f>
         <v>8640000</v>
       </c>
       <c r="D11" s="237" t="s">
@@ -39626,7 +39624,6 @@
         <v>260</v>
       </c>
       <c r="C14" s="208">
-        <f>7400000*0.8</f>
         <v>5920000</v>
       </c>
       <c r="D14" s="208"/>
@@ -39921,7 +39918,6 @@
         <v>190</v>
       </c>
       <c r="C17" s="208">
-        <f>9900000*0.8</f>
         <v>7920000</v>
       </c>
       <c r="D17" s="208"/>
@@ -48149,7 +48145,6 @@
         <v>1090</v>
       </c>
       <c r="F10" s="227">
-        <f>7200000*1.1</f>
         <v>7920000.0000000009</v>
       </c>
       <c r="G10" s="226" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B3D36F-790D-48FD-A8CA-D5B357136F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DD8AFC2-49BE-44D3-8825-C8567622CC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB224DC7-EBC4-417C-BE6F-5683AFDDE08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699BAA19-F505-4651-B696-028DFC42D01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23285,7 +23285,7 @@
       </c>
       <c r="AP100" s="122"/>
     </row>
-    <row r="101" spans="1:42" ht="24" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>98</v>
       </c>
@@ -46907,7 +46907,7 @@
         <v>45884</v>
       </c>
       <c r="G85" s="233">
-        <f>EDATE(F85,6)</f>
+        <f t="shared" ref="G85:G90" si="38">EDATE(F85,6)</f>
         <v>46068</v>
       </c>
       <c r="H85" s="233">
@@ -47005,7 +47005,7 @@
         <v>45891</v>
       </c>
       <c r="G86" s="233">
-        <f>EDATE(F86,6)</f>
+        <f t="shared" si="38"/>
         <v>46075</v>
       </c>
       <c r="H86" s="233">
@@ -47103,7 +47103,7 @@
         <v>45884</v>
       </c>
       <c r="G87" s="233">
-        <f>EDATE(F87,6)</f>
+        <f t="shared" si="38"/>
         <v>46068</v>
       </c>
       <c r="H87" s="233">
@@ -47201,7 +47201,7 @@
         <v>45905</v>
       </c>
       <c r="G88" s="233">
-        <f>EDATE(F88,6)</f>
+        <f t="shared" si="38"/>
         <v>46086</v>
       </c>
       <c r="H88" s="233">
@@ -47299,7 +47299,7 @@
         <v>45827</v>
       </c>
       <c r="G89" s="233">
-        <f>EDATE(F89,6)</f>
+        <f t="shared" si="38"/>
         <v>46010</v>
       </c>
       <c r="H89" s="233">
@@ -47397,7 +47397,7 @@
         <v>45952</v>
       </c>
       <c r="G90" s="233">
-        <f>EDATE(F90,6)</f>
+        <f t="shared" si="38"/>
         <v>46134</v>
       </c>
       <c r="H90" s="233">
@@ -47473,7 +47473,7 @@
         <v>49421</v>
       </c>
       <c r="Z90" s="203">
-        <f t="shared" ref="Z90:Z91" si="38">C90*6</f>
+        <f t="shared" ref="Z90:Z91" si="39">C90*6</f>
         <v>54000000</v>
       </c>
     </row>
@@ -47571,7 +47571,7 @@
         <v>49356</v>
       </c>
       <c r="Z91" s="203">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>63600000</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699BAA19-F505-4651-B696-028DFC42D01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F340E435-5AD3-4309-969A-2D3D6FDE3C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Theo dõi HĐ_Chi tiết" sheetId="2" r:id="rId1"/>
@@ -28986,40 +28986,40 @@
         <v>46082</v>
       </c>
       <c r="Z17" s="168">
-        <f>EDATE(Y17,3)-1</f>
-        <v>46173</v>
+        <f>EDATE(Y17,3)</f>
+        <v>46174</v>
       </c>
       <c r="AA17" s="168">
         <f t="shared" si="16"/>
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="AB17" s="168">
         <f t="shared" si="16"/>
-        <v>46356</v>
+        <v>46357</v>
       </c>
       <c r="AC17" s="168">
         <f t="shared" si="16"/>
-        <v>46446</v>
+        <v>46447</v>
       </c>
       <c r="AD17" s="168">
         <f t="shared" si="16"/>
-        <v>46535</v>
+        <v>46539</v>
       </c>
       <c r="AE17" s="168">
         <f t="shared" si="16"/>
-        <v>46627</v>
+        <v>46631</v>
       </c>
       <c r="AF17" s="168">
         <f t="shared" si="16"/>
-        <v>46719</v>
+        <v>46722</v>
       </c>
       <c r="AG17" s="168">
         <f t="shared" si="16"/>
-        <v>46811</v>
+        <v>46813</v>
       </c>
       <c r="AH17" s="188">
         <f ca="1">Z17-TODAY()</f>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AI17" s="166">
         <f>3*D17</f>
@@ -38099,100 +38099,100 @@
         <v>45931</v>
       </c>
       <c r="K85" s="184">
-        <f>EDATE(J85,6)-1</f>
-        <v>46112</v>
+        <f>EDATE(J85,6)</f>
+        <v>46113</v>
       </c>
       <c r="L85" s="184">
         <f t="shared" si="67"/>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M85" s="184">
         <f t="shared" si="67"/>
-        <v>46476</v>
+        <v>46478</v>
       </c>
       <c r="N85" s="184">
         <f t="shared" si="67"/>
-        <v>46660</v>
+        <v>46661</v>
       </c>
       <c r="O85" s="184">
         <f t="shared" si="67"/>
-        <v>46842</v>
+        <v>46844</v>
       </c>
       <c r="P85" s="184">
         <f t="shared" si="67"/>
-        <v>47026</v>
+        <v>47027</v>
       </c>
       <c r="Q85" s="184">
         <f t="shared" si="67"/>
-        <v>47207</v>
+        <v>47209</v>
       </c>
       <c r="R85" s="184">
         <f t="shared" si="67"/>
-        <v>47391</v>
+        <v>47392</v>
       </c>
       <c r="S85" s="184">
         <f t="shared" si="67"/>
-        <v>47572</v>
+        <v>47574</v>
       </c>
       <c r="T85" s="184">
         <f t="shared" si="67"/>
-        <v>47756</v>
+        <v>47757</v>
       </c>
       <c r="U85" s="184">
         <f t="shared" si="67"/>
-        <v>47937</v>
+        <v>47939</v>
       </c>
       <c r="V85" s="184">
         <f t="shared" si="67"/>
-        <v>48121</v>
+        <v>48122</v>
       </c>
       <c r="W85" s="184">
         <f t="shared" si="66"/>
-        <v>48303</v>
+        <v>48305</v>
       </c>
       <c r="X85" s="184">
         <f t="shared" si="66"/>
-        <v>48487</v>
+        <v>48488</v>
       </c>
       <c r="Y85" s="184">
         <f t="shared" si="66"/>
-        <v>48668</v>
+        <v>48670</v>
       </c>
       <c r="Z85" s="184">
         <f t="shared" si="66"/>
-        <v>48852</v>
+        <v>48853</v>
       </c>
       <c r="AA85" s="184">
         <f t="shared" si="66"/>
-        <v>49033</v>
+        <v>49035</v>
       </c>
       <c r="AB85" s="184">
         <f t="shared" si="66"/>
-        <v>49217</v>
+        <v>49218</v>
       </c>
       <c r="AC85" s="184">
         <f t="shared" si="66"/>
-        <v>49398</v>
+        <v>49400</v>
       </c>
       <c r="AD85" s="184">
         <f t="shared" si="66"/>
-        <v>49582</v>
+        <v>49583</v>
       </c>
       <c r="AE85" s="184">
         <f t="shared" si="66"/>
-        <v>49764</v>
+        <v>49766</v>
       </c>
       <c r="AF85" s="184">
         <f t="shared" si="66"/>
-        <v>49948</v>
+        <v>49949</v>
       </c>
       <c r="AG85" s="184">
         <f t="shared" si="66"/>
-        <v>50129</v>
+        <v>50131</v>
       </c>
       <c r="AH85" s="188">
         <f ca="1">K85-TODAY()</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI85" s="203">
         <f t="shared" si="61"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F340E435-5AD3-4309-969A-2D3D6FDE3C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9211F1D-35E6-487D-A211-536261AE378B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Theo dõi HĐ_Chi tiết" sheetId="2" r:id="rId1"/>
@@ -505,7 +505,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3228" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3247" uniqueCount="1154">
   <si>
     <t>filter</t>
   </si>
@@ -4267,6 +4267,9 @@
   </si>
   <si>
     <t>SGN0339</t>
+  </si>
+  <si>
+    <t>Cá nhân</t>
   </si>
 </sst>
 </file>
@@ -6886,21 +6889,6 @@
           <cell r="AF4" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AG4">
-            <v>44683</v>
-          </cell>
-          <cell r="AH4" t="str">
-            <v>221954599</v>
-          </cell>
-          <cell r="AI4" t="str">
-            <v>Nguyễn Phùng Thành</v>
-          </cell>
-          <cell r="AJ4" t="str">
-            <v xml:space="preserve">Ngân hàng VP Bank </v>
-          </cell>
-          <cell r="AK4" t="str">
-            <v>4597-VT/DKV/2021</v>
-          </cell>
         </row>
         <row r="5">
           <cell r="B5" t="str">
@@ -6969,21 +6957,6 @@
           <cell r="AF5" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AG5">
-            <v>44626</v>
-          </cell>
-          <cell r="AH5" t="str">
-            <v xml:space="preserve">0071004454681 </v>
-          </cell>
-          <cell r="AI5" t="str">
-            <v>Hoàng Đình Cường</v>
-          </cell>
-          <cell r="AJ5" t="str">
-            <v>Ngân hàng VietcomBank CN TPHCM</v>
-          </cell>
-          <cell r="AK5" t="str">
-            <v>0362-VT/DKV/2021</v>
-          </cell>
         </row>
         <row r="6">
           <cell r="B6" t="str">
@@ -7052,21 +7025,6 @@
           <cell r="AF6" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AG6">
-            <v>44725</v>
-          </cell>
-          <cell r="AH6" t="str">
-            <v>915049911500001</v>
-          </cell>
-          <cell r="AI6" t="str">
-            <v>Nguyễn Chí Công</v>
-          </cell>
-          <cell r="AJ6" t="str">
-            <v>Ngân hàng TMCP Nam Á – Chi nhánh Trường Chinh</v>
-          </cell>
-          <cell r="AK6" t="str">
-            <v>0008-VT/DKV/2021</v>
-          </cell>
         </row>
         <row r="7">
           <cell r="B7" t="str">
@@ -7135,21 +7093,6 @@
           <cell r="AF7" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AG7">
-            <v>44832</v>
-          </cell>
-          <cell r="AH7" t="str">
-            <v>060209529672</v>
-          </cell>
-          <cell r="AI7" t="str">
-            <v>Nguyễn Tuấn Khanh</v>
-          </cell>
-          <cell r="AJ7" t="str">
-            <v>Ngân hàng Sacombank</v>
-          </cell>
-          <cell r="AK7" t="str">
-            <v>0643-11-VT/DKV/2021</v>
-          </cell>
         </row>
         <row r="8">
           <cell r="B8" t="str">
@@ -7221,18 +7164,6 @@
           <cell r="AF8" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH8" t="str">
-            <v>Nguyễn Thị Ly</v>
-          </cell>
-          <cell r="AI8" t="str">
-            <v>Nguyễn Thị Ly</v>
-          </cell>
-          <cell r="AJ8" t="str">
-            <v>Nguyễn Thị Ly</v>
-          </cell>
-          <cell r="AK8" t="str">
-            <v>S0005VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="9">
           <cell r="B9" t="str">
@@ -7301,21 +7232,6 @@
           <cell r="AF9" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AG9">
-            <v>44803</v>
-          </cell>
-          <cell r="AH9" t="str">
-            <v>19031400962018</v>
-          </cell>
-          <cell r="AI9" t="str">
-            <v>Phạm Bá Thanh</v>
-          </cell>
-          <cell r="AJ9" t="str">
-            <v>Techcombank</v>
-          </cell>
-          <cell r="AK9" t="str">
-            <v>4634-VT/DKV/2021</v>
-          </cell>
         </row>
         <row r="10">
           <cell r="B10" t="str">
@@ -7384,21 +7300,6 @@
           <cell r="AF10" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AG10">
-            <v>44802</v>
-          </cell>
-          <cell r="AH10" t="str">
-            <v>19037760913016</v>
-          </cell>
-          <cell r="AI10" t="str">
-            <v>Thái Văn</v>
-          </cell>
-          <cell r="AJ10" t="str">
-            <v>Techcombank</v>
-          </cell>
-          <cell r="AK10" t="str">
-            <v>0382-VT/DKV/2021</v>
-          </cell>
         </row>
         <row r="11">
           <cell r="B11" t="str">
@@ -7473,21 +7374,6 @@
           <cell r="AF11" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AG11">
-            <v>44803</v>
-          </cell>
-          <cell r="AH11" t="str">
-            <v>7313757</v>
-          </cell>
-          <cell r="AI11" t="str">
-            <v>Hoàng Thị Dung</v>
-          </cell>
-          <cell r="AJ11" t="str">
-            <v>ACB Chi nhánh Chợ Lớn</v>
-          </cell>
-          <cell r="AK11" t="str">
-            <v>0739-VT/DKV/2021</v>
-          </cell>
         </row>
         <row r="12">
           <cell r="B12" t="str">
@@ -7557,21 +7443,6 @@
           <cell r="AF12" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AG12">
-            <v>44735</v>
-          </cell>
-          <cell r="AH12" t="str">
-            <v>0071000075364</v>
-          </cell>
-          <cell r="AI12" t="str">
-            <v>Nghiêm Gia Thuận</v>
-          </cell>
-          <cell r="AJ12" t="str">
-            <v>Vietcombank</v>
-          </cell>
-          <cell r="AK12" t="str">
-            <v>0341-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="13">
           <cell r="B13" t="str">
@@ -7640,21 +7511,6 @@
           <cell r="AF13" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AG13">
-            <v>44833</v>
-          </cell>
-          <cell r="AH13" t="str">
-            <v>0071001305920</v>
-          </cell>
-          <cell r="AI13" t="str">
-            <v>Nguyễn Ngọc Quỳnh</v>
-          </cell>
-          <cell r="AJ13" t="str">
-            <v>Vietcombank</v>
-          </cell>
-          <cell r="AK13" t="str">
-            <v>0750-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="14">
           <cell r="B14" t="str">
@@ -7732,23 +7588,6 @@
           <cell r="AF14" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AG14">
-            <v>44743</v>
-          </cell>
-          <cell r="AH14" t="str">
-            <v>060223722272 _ Sacom
-38803257_ACB</v>
-          </cell>
-          <cell r="AI14" t="str">
-            <v>Phạm Thị Hồng Nhung</v>
-          </cell>
-          <cell r="AJ14" t="str">
-            <v>Sacombank
-ACB</v>
-          </cell>
-          <cell r="AK14" t="str">
-            <v>0207-12-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="15">
           <cell r="B15" t="str">
@@ -7814,18 +7653,6 @@
           <cell r="AF15" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH15" t="str">
-            <v>0065100013370003</v>
-          </cell>
-          <cell r="AI15" t="str">
-            <v>Trần Thị Mai Hương</v>
-          </cell>
-          <cell r="AJ15" t="str">
-            <v>Ngân hàng cổ phần Phương Đông – OCB CN Quận 4</v>
-          </cell>
-          <cell r="AK15" t="str">
-            <v>2269-11-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="16">
           <cell r="B16" t="str">
@@ -7891,18 +7718,6 @@
           <cell r="AF16" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH16" t="str">
-            <v>7662537</v>
-          </cell>
-          <cell r="AI16" t="str">
-            <v>Nguyễn Thu Hương</v>
-          </cell>
-          <cell r="AJ16" t="str">
-            <v>Ngân hàng ACB</v>
-          </cell>
-          <cell r="AK16" t="str">
-            <v>3871-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="17">
           <cell r="B17" t="str">
@@ -7974,18 +7789,6 @@
           <cell r="AF17" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH17" t="str">
-            <v>59601049</v>
-          </cell>
-          <cell r="AI17" t="str">
-            <v>Nguyễn Thị Loan</v>
-          </cell>
-          <cell r="AJ17" t="str">
-            <v>Ngân hàng ACB</v>
-          </cell>
-          <cell r="AK17" t="str">
-            <v>0440-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="18">
           <cell r="B18" t="str">
@@ -8054,18 +7857,6 @@
           <cell r="AF18" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH18" t="str">
-            <v>19022625139011</v>
-          </cell>
-          <cell r="AI18" t="str">
-            <v>Nguyễn Phi Hiệp</v>
-          </cell>
-          <cell r="AJ18" t="str">
-            <v>Techcombank</v>
-          </cell>
-          <cell r="AK18" t="str">
-            <v>S0161-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="19">
           <cell r="B19" t="str">
@@ -8134,18 +7925,6 @@
           <cell r="AF19" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH19" t="str">
-            <v>0511 000419347</v>
-          </cell>
-          <cell r="AI19" t="str">
-            <v>Hồ Nguyễn Thụy Thảo</v>
-          </cell>
-          <cell r="AJ19" t="str">
-            <v>Vietcombank  - CN Quận 5</v>
-          </cell>
-          <cell r="AK19" t="str">
-            <v>S0764-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="20">
           <cell r="B20" t="str">
@@ -8211,18 +7990,6 @@
           <cell r="AF20" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH20" t="str">
-            <v>106002279059</v>
-          </cell>
-          <cell r="AI20" t="str">
-            <v>Nguyễn Đăng Tân</v>
-          </cell>
-          <cell r="AJ20" t="str">
-            <v>NH Vietin Bank</v>
-          </cell>
-          <cell r="AK20" t="str">
-            <v>H4644-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="21">
           <cell r="B21" t="str">
@@ -8285,18 +8052,6 @@
           <cell r="AF21" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH21" t="str">
-            <v>106870603289</v>
-          </cell>
-          <cell r="AI21" t="str">
-            <v>Nguyễn Thị Thu</v>
-          </cell>
-          <cell r="AJ21" t="str">
-            <v>NH Vietin Bank CN Bắc SG</v>
-          </cell>
-          <cell r="AK21" t="str">
-            <v>590-359-VN/DKV/2022</v>
-          </cell>
         </row>
         <row r="22">
           <cell r="B22" t="str">
@@ -8362,18 +8117,6 @@
           <cell r="AF22" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH22" t="str">
-            <v>1010105106008</v>
-          </cell>
-          <cell r="AI22" t="str">
-            <v>Trần Quang Vũ</v>
-          </cell>
-          <cell r="AJ22" t="str">
-            <v>Ngan Hang Quan Doi MB</v>
-          </cell>
-          <cell r="AK22" t="str">
-            <v>HCM0629-11-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="23">
           <cell r="B23" t="str">
@@ -8436,18 +8179,6 @@
           <cell r="AF23" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH23" t="str">
-            <v>0908002423</v>
-          </cell>
-          <cell r="AI23" t="str">
-            <v>Hàn Đức Vinh</v>
-          </cell>
-          <cell r="AJ23" t="str">
-            <v>MB Bank</v>
-          </cell>
-          <cell r="AK23" t="str">
-            <v>0504-VN/DKV/2022</v>
-          </cell>
         </row>
         <row r="24">
           <cell r="B24" t="str">
@@ -8516,18 +8247,6 @@
           <cell r="AF24" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH24">
-            <v>60195282024</v>
-          </cell>
-          <cell r="AI24" t="str">
-            <v>Mai Văn Hữu</v>
-          </cell>
-          <cell r="AJ24" t="str">
-            <v>Sacombank CN Hóc Môn</v>
-          </cell>
-          <cell r="AK24" t="str">
-            <v>S0639-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="25">
           <cell r="B25" t="str">
@@ -8590,18 +8309,6 @@
           <cell r="AF25" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH25" t="str">
-            <v>6140205903134</v>
-          </cell>
-          <cell r="AI25" t="str">
-            <v>Trần Thị Hồng Thảo</v>
-          </cell>
-          <cell r="AJ25" t="str">
-            <v>Ngân hàng: Agribank</v>
-          </cell>
-          <cell r="AK25" t="str">
-            <v>S0645-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="26">
           <cell r="B26" t="str">
@@ -8667,21 +8374,6 @@
           <cell r="AF26" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH26" t="str">
-            <v>6300205203149
-823459089999</v>
-          </cell>
-          <cell r="AI26" t="str">
-            <v>Phạm Tiến Mạnh
-Bùi Thị Liên</v>
-          </cell>
-          <cell r="AJ26" t="str">
-            <v>Agribank CN Q09
-MB Bank</v>
-          </cell>
-          <cell r="AK26" t="str">
-            <v>H4081-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="27">
           <cell r="B27" t="str">
@@ -8756,18 +8448,6 @@
           <cell r="AF27" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH27" t="str">
-            <v>Tiền mặt</v>
-          </cell>
-          <cell r="AI27" t="str">
-            <v xml:space="preserve">Nguyễn Thúy Kiều                </v>
-          </cell>
-          <cell r="AJ27" t="str">
-            <v>Tiền mặt</v>
-          </cell>
-          <cell r="AK27" t="str">
-            <v>TUH-013-VN/DKV/2022</v>
-          </cell>
         </row>
         <row r="28">
           <cell r="B28" t="str">
@@ -8843,18 +8523,6 @@
           <cell r="AF28" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH28" t="str">
-            <v>017003453071</v>
-          </cell>
-          <cell r="AI28" t="str">
-            <v>Nguyễn Thị Tuyết Hồng</v>
-          </cell>
-          <cell r="AJ28" t="str">
-            <v>Ngân Hàng Vietcombank – Tây Sài Gòn</v>
-          </cell>
-          <cell r="AK28" t="str">
-            <v>TUH-010-VN/DKV/2022</v>
-          </cell>
         </row>
         <row r="29">
           <cell r="B29" t="str">
@@ -8914,18 +8582,6 @@
           <cell r="AF29" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH29" t="str">
-            <v>2200116730002</v>
-          </cell>
-          <cell r="AI29" t="str">
-            <v>Nguyễn Anh Khoa</v>
-          </cell>
-          <cell r="AJ29" t="str">
-            <v>MB Bank</v>
-          </cell>
-          <cell r="AK29" t="str">
-            <v>H4332-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="30">
           <cell r="B30" t="str">
@@ -8991,18 +8647,6 @@
           <cell r="AF30" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH30" t="str">
-            <v>13212000002119</v>
-          </cell>
-          <cell r="AI30" t="str">
-            <v>Nguyễn Đắc Duy</v>
-          </cell>
-          <cell r="AJ30" t="str">
-            <v>BIDV</v>
-          </cell>
-          <cell r="AK30" t="str">
-            <v>S0789-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="31">
           <cell r="B31" t="str">
@@ -9065,18 +8709,6 @@
           <cell r="AF31" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH31" t="str">
-            <v>060252739761</v>
-          </cell>
-          <cell r="AI31" t="str">
-            <v>Đinh Thái Lâm</v>
-          </cell>
-          <cell r="AJ31" t="str">
-            <v>Sacombank</v>
-          </cell>
-          <cell r="AK31" t="str">
-            <v>S0580-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="32">
           <cell r="B32" t="str">
@@ -9135,18 +8767,6 @@
           </cell>
           <cell r="AF32" t="str">
             <v>3 tháng</v>
-          </cell>
-          <cell r="AH32" t="str">
-            <v>31810000230918</v>
-          </cell>
-          <cell r="AI32" t="str">
-            <v>Hoàng Thị Thu Thuỷ</v>
-          </cell>
-          <cell r="AJ32" t="str">
-            <v>NH BIDV</v>
-          </cell>
-          <cell r="AK32" t="str">
-            <v>H1550-11/VT/DKV/2022</v>
           </cell>
         </row>
         <row r="33">
@@ -9216,18 +8836,6 @@
           <cell r="AF33" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH33" t="str">
-            <v>14010000654036</v>
-          </cell>
-          <cell r="AI33" t="str">
-            <v>Nguyễn Hữu Hồng</v>
-          </cell>
-          <cell r="AJ33" t="str">
-            <v>NH BIDV</v>
-          </cell>
-          <cell r="AK33" t="str">
-            <v>S0676-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="34">
           <cell r="B34" t="str">
@@ -9287,18 +8895,6 @@
           <cell r="AF34" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH34" t="str">
-            <v>31810000506628</v>
-          </cell>
-          <cell r="AI34" t="str">
-            <v>Đặng Kiên Cường</v>
-          </cell>
-          <cell r="AJ34" t="str">
-            <v>BIDV</v>
-          </cell>
-          <cell r="AK34" t="str">
-            <v>S0443-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="35">
           <cell r="B35" t="str">
@@ -9361,18 +8957,6 @@
           <cell r="AF35" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH35" t="str">
-            <v>101006160611</v>
-          </cell>
-          <cell r="AI35" t="str">
-            <v>Kiều Thị Thuý Nga</v>
-          </cell>
-          <cell r="AJ35" t="str">
-            <v>Viettinbank</v>
-          </cell>
-          <cell r="AK35" t="str">
-            <v>S0754-VN/DKV/2022</v>
-          </cell>
         </row>
         <row r="36">
           <cell r="B36" t="str">
@@ -9432,18 +9016,6 @@
           <cell r="AF36" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH36" t="str">
-            <v>6120201006313</v>
-          </cell>
-          <cell r="AI36" t="str">
-            <v>Nguyễn Văn Châu</v>
-          </cell>
-          <cell r="AJ36" t="str">
-            <v>NH Agribank</v>
-          </cell>
-          <cell r="AK36" t="str">
-            <v>H2331-11/VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="37">
           <cell r="B37" t="str">
@@ -9503,18 +9075,6 @@
           <cell r="AF37" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH37" t="str">
-            <v>0109536714</v>
-          </cell>
-          <cell r="AI37" t="str">
-            <v xml:space="preserve">Hà Thị Nga </v>
-          </cell>
-          <cell r="AJ37" t="str">
-            <v>Ngân hàng Đông Á</v>
-          </cell>
-          <cell r="AK37" t="str">
-            <v>S0480 -VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="38">
           <cell r="B38" t="str">
@@ -9574,18 +9134,6 @@
           <cell r="AF38" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH38" t="str">
-            <v>060234285591</v>
-          </cell>
-          <cell r="AI38" t="str">
-            <v xml:space="preserve">Duong Thai Anh </v>
-          </cell>
-          <cell r="AJ38" t="str">
-            <v>Ngân hàng Sacombank</v>
-          </cell>
-          <cell r="AK38" t="str">
-            <v>S0504 -VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="39">
           <cell r="B39" t="str">
@@ -9645,18 +9193,6 @@
           <cell r="AF39" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH39" t="str">
-            <v>20111 0000 3006</v>
-          </cell>
-          <cell r="AI39" t="str">
-            <v>Công ty CP 32</v>
-          </cell>
-          <cell r="AJ39" t="str">
-            <v>TMCP Quân Đội - Bắc SG</v>
-          </cell>
-          <cell r="AK39" t="str">
-            <v>S0160 -VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="40">
           <cell r="B40" t="str">
@@ -9716,18 +9252,6 @@
           <cell r="AF40" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH40" t="str">
-            <v>6360903176599</v>
-          </cell>
-          <cell r="AI40" t="str">
-            <v>Nguyễn Văn Quế</v>
-          </cell>
-          <cell r="AJ40" t="str">
-            <v>Ngân hàng Agribank</v>
-          </cell>
-          <cell r="AK40" t="str">
-            <v>S0792 -VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="41">
           <cell r="B41" t="str">
@@ -9784,18 +9308,6 @@
           <cell r="AF41" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH41" t="str">
-            <v>0531002535283</v>
-          </cell>
-          <cell r="AI41" t="str">
-            <v>Hồ Hoàng Nam</v>
-          </cell>
-          <cell r="AJ41" t="str">
-            <v>Ngân hàng Vietcombank</v>
-          </cell>
-          <cell r="AK41" t="str">
-            <v>H3266-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="42">
           <cell r="B42" t="str">
@@ -9849,18 +9361,6 @@
           <cell r="AF42" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH42" t="str">
-            <v>2310718</v>
-          </cell>
-          <cell r="AI42" t="str">
-            <v xml:space="preserve">Nguyễn Khắc Anh </v>
-          </cell>
-          <cell r="AJ42" t="str">
-            <v>Ngân hàng ACB Chi nhánh Bình Thạnh</v>
-          </cell>
-          <cell r="AK42" t="str">
-            <v>S862-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="43">
           <cell r="B43" t="str">
@@ -9917,18 +9417,6 @@
           <cell r="AF43" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH43" t="str">
-            <v>19033785562018</v>
-          </cell>
-          <cell r="AI43" t="str">
-            <v>Đặng Ngọc Phúc</v>
-          </cell>
-          <cell r="AJ43" t="str">
-            <v>Ngân hàng Techcombank</v>
-          </cell>
-          <cell r="AK43" t="str">
-            <v>H1636-12-VT/DKV/2022</v>
-          </cell>
         </row>
         <row r="44">
           <cell r="B44" t="str">
@@ -9982,18 +9470,6 @@
           <cell r="AF44" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH44" t="str">
-            <v>22097788</v>
-          </cell>
-          <cell r="AI44" t="str">
-            <v>Hà Thị Thuý Nga</v>
-          </cell>
-          <cell r="AJ44" t="str">
-            <v>Ngân hàng ACB</v>
-          </cell>
-          <cell r="AK44" t="str">
-            <v>S1092 -VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="45">
           <cell r="B45" t="str">
@@ -10044,18 +9520,6 @@
           <cell r="AF45" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH45" t="str">
-            <v>060140286845</v>
-          </cell>
-          <cell r="AI45" t="str">
-            <v>Nguyễn Ngọc Cương</v>
-          </cell>
-          <cell r="AJ45" t="str">
-            <v>Sacombank</v>
-          </cell>
-          <cell r="AK45" t="str">
-            <v>H4639 -VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="46">
           <cell r="B46" t="str">
@@ -10106,18 +9570,6 @@
           <cell r="AF46" t="str">
             <v>3 tháng</v>
           </cell>
-          <cell r="AH46" t="str">
-            <v>1010127605008</v>
-          </cell>
-          <cell r="AI46" t="str">
-            <v>Nguyễn Thảo Quyên</v>
-          </cell>
-          <cell r="AJ46" t="str">
-            <v>MB Bank</v>
-          </cell>
-          <cell r="AK46" t="str">
-            <v>H1041-13 -VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="47">
           <cell r="B47" t="str">
@@ -10171,18 +9623,6 @@
           <cell r="AF47" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH47" t="str">
-            <v>100.000.136.053</v>
-          </cell>
-          <cell r="AI47" t="str">
-            <v>Nguyễn Thị Ấm</v>
-          </cell>
-          <cell r="AJ47" t="str">
-            <v xml:space="preserve">NH Vietinbank </v>
-          </cell>
-          <cell r="AK47" t="str">
-            <v>H0339</v>
-          </cell>
         </row>
         <row r="48">
           <cell r="B48" t="str">
@@ -10236,18 +9676,6 @@
           <cell r="AF48" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH48" t="str">
-            <v>1603205228943</v>
-          </cell>
-          <cell r="AI48" t="str">
-            <v>Nguyễn Hoàng Yến</v>
-          </cell>
-          <cell r="AJ48" t="str">
-            <v xml:space="preserve">Agribank </v>
-          </cell>
-          <cell r="AK48" t="str">
-            <v>H0926-11 -VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="49">
           <cell r="B49" t="str">
@@ -10298,18 +9726,6 @@
           <cell r="AF49" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH49" t="str">
-            <v>1020192779779</v>
-          </cell>
-          <cell r="AI49" t="str">
-            <v>Trần Phú Lâm</v>
-          </cell>
-          <cell r="AJ49" t="str">
-            <v>MB Bank</v>
-          </cell>
-          <cell r="AK49" t="str">
-            <v>S1007-VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="50">
           <cell r="B50" t="str">
@@ -10363,18 +9779,6 @@
           <cell r="AF50" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH50" t="str">
-            <v>060141139919</v>
-          </cell>
-          <cell r="AI50" t="str">
-            <v>Nguyễn Thị Dung</v>
-          </cell>
-          <cell r="AJ50" t="str">
-            <v>Sacombank</v>
-          </cell>
-          <cell r="AK50" t="str">
-            <v>H1065-11-VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="51">
           <cell r="B51" t="str">
@@ -10428,18 +9832,6 @@
           <cell r="AF51" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH51" t="str">
-            <v>0938089918</v>
-          </cell>
-          <cell r="AI51" t="str">
-            <v>Nguyễn Ngọc Diệp Phương Linh</v>
-          </cell>
-          <cell r="AJ51" t="str">
-            <v>Mbbank</v>
-          </cell>
-          <cell r="AK51" t="str">
-            <v>H1074-12-VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="52">
           <cell r="B52" t="str">
@@ -10490,18 +9882,6 @@
           <cell r="AF52" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH52" t="str">
-            <v>000001927590</v>
-          </cell>
-          <cell r="AI52" t="str">
-            <v xml:space="preserve">Lê Văn Thành  </v>
-          </cell>
-          <cell r="AJ52" t="str">
-            <v>VietBank</v>
-          </cell>
-          <cell r="AK52" t="str">
-            <v>S0203 -VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="53">
           <cell r="B53" t="str">
@@ -10555,18 +9935,6 @@
           <cell r="AF53" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH53" t="str">
-            <v>686861972</v>
-          </cell>
-          <cell r="AI53" t="str">
-            <v>Nguyễn Minh Đức</v>
-          </cell>
-          <cell r="AJ53" t="str">
-            <v>Mbbank</v>
-          </cell>
-          <cell r="AK53" t="str">
-            <v>S1012 -VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="54">
           <cell r="B54" t="str">
@@ -10620,18 +9988,6 @@
           <cell r="AF54" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH54" t="str">
-            <v>072100058574</v>
-          </cell>
-          <cell r="AI54" t="str">
-            <v>Hồ Hữu Hải</v>
-          </cell>
-          <cell r="AJ54" t="str">
-            <v>VietComBank chi nhánh Kỳ Đồng</v>
-          </cell>
-          <cell r="AK54" t="str">
-            <v>S10008 -VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="55">
           <cell r="B55" t="str">
@@ -10682,18 +10038,6 @@
           <cell r="AF55" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH55" t="str">
-            <v>0381000416443</v>
-          </cell>
-          <cell r="AI55" t="str">
-            <v>Trương Minh Hùng</v>
-          </cell>
-          <cell r="AJ55" t="str">
-            <v>Ngân hàng Vietcombank CN Thủ Đức</v>
-          </cell>
-          <cell r="AK55" t="str">
-            <v>S1273 -VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="56">
           <cell r="B56" t="str">
@@ -10744,18 +10088,6 @@
           <cell r="AF56" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH56" t="str">
-            <v>0031000141408</v>
-          </cell>
-          <cell r="AI56" t="str">
-            <v>Bùi Thế Đích</v>
-          </cell>
-          <cell r="AJ56" t="str">
-            <v>Vietcombank</v>
-          </cell>
-          <cell r="AK56" t="str">
-            <v>H2434-11-VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="57">
           <cell r="B57" t="str">
@@ -10806,18 +10138,6 @@
           <cell r="AF57" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH57" t="str">
-            <v>1010115364005</v>
-          </cell>
-          <cell r="AI57" t="str">
-            <v>Võ Minh Trí</v>
-          </cell>
-          <cell r="AJ57" t="str">
-            <v>Mbbank</v>
-          </cell>
-          <cell r="AK57" t="str">
-            <v>H0498-15-VT/DKV/2023</v>
-          </cell>
         </row>
         <row r="58">
           <cell r="B58" t="str">
@@ -10871,18 +10191,6 @@
           <cell r="AF58" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH58" t="str">
-            <v>1709.1965.99999</v>
-          </cell>
-          <cell r="AI58" t="str">
-            <v>Nguyễn Thái Thìn</v>
-          </cell>
-          <cell r="AJ58" t="str">
-            <v>MB Bank</v>
-          </cell>
-          <cell r="AK58" t="str">
-            <v>H0612-12-VT/DKV/2024</v>
-          </cell>
         </row>
         <row r="59">
           <cell r="B59" t="str">
@@ -10933,18 +10241,6 @@
           <cell r="AF59" t="str">
             <v>6 tháng</v>
           </cell>
-          <cell r="AH59" t="str">
-            <v>13610000117945</v>
-          </cell>
-          <cell r="AI59" t="str">
-            <v xml:space="preserve">Nguyen Vinh Thuy </v>
-          </cell>
-          <cell r="AJ59" t="str">
-            <v>BIDV</v>
-          </cell>
-          <cell r="AK59" t="str">
-            <v>H1096-11-VT/DKV/2024</v>
-          </cell>
         </row>
         <row r="60">
           <cell r="B60" t="str">
@@ -10994,18 +10290,6 @@
           </cell>
           <cell r="AF60" t="str">
             <v>6 tháng</v>
-          </cell>
-          <cell r="AH60" t="str">
-            <v>933007020</v>
-          </cell>
-          <cell r="AI60" t="str">
-            <v>Cao Kế Siêu</v>
-          </cell>
-          <cell r="AJ60" t="str">
-            <v>VIB Bank</v>
-          </cell>
-          <cell r="AK60" t="str">
-            <v>H0373-15-VT/DKV/2024</v>
           </cell>
         </row>
         <row r="61">
@@ -26756,7 +26040,9 @@
   <dimension ref="A1:AJ85"/>
   <sheetFormatPr defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="9" style="161" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="161" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="161" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="161" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.33203125" style="224" customWidth="1"/>
     <col min="5" max="11" width="9" style="161" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.5546875" style="161" customWidth="1"/>
@@ -27149,21 +26435,17 @@
       <c r="D4" s="166">
         <v>6500000</v>
       </c>
-      <c r="E4" s="166">
-        <f>VLOOKUP($B4,'[1]Theo dõi HĐ_Chi tiết'!$B$4:$AK$60,32,0)</f>
-        <v>44683</v>
-      </c>
-      <c r="F4" s="166" t="str">
-        <f>VLOOKUP($B4,'[1]Theo dõi HĐ_Chi tiết'!$B$4:$AK$60,33,0)</f>
-        <v>221954599</v>
-      </c>
-      <c r="G4" s="166" t="str">
-        <f>VLOOKUP($B4,'[1]Theo dõi HĐ_Chi tiết'!$B$4:$AK$60,34,0)</f>
-        <v>Nguyễn Phùng Thành</v>
-      </c>
-      <c r="H4" s="166" t="str">
-        <f>VLOOKUP($B4,'[1]Theo dõi HĐ_Chi tiết'!$B$4:$AK$60,35,0)</f>
-        <v xml:space="preserve">Ngân hàng VP Bank </v>
+      <c r="E4" s="166" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="166" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="166" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="166" t="s">
+        <v>69</v>
       </c>
       <c r="I4" s="167" t="s">
         <v>77</v>
@@ -29300,8 +28582,8 @@
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A20" s="164">
-        <v>17</v>
+      <c r="A20" s="164" t="s">
+        <v>1153</v>
       </c>
       <c r="B20" s="174" t="s">
         <v>427</v>
@@ -32538,8 +31820,8 @@
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A44" s="164">
-        <v>41</v>
+      <c r="A44" s="164" t="s">
+        <v>1153</v>
       </c>
       <c r="B44" s="164" t="s">
         <v>1152</v>
@@ -39338,8 +38620,8 @@
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A8" s="164">
-        <v>5</v>
+      <c r="A8" s="164" t="s">
+        <v>1153</v>
       </c>
       <c r="B8" s="165" t="s">
         <v>95</v>
@@ -42296,8 +41578,8 @@
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A38" s="164">
-        <v>35</v>
+      <c r="A38" s="164" t="s">
+        <v>1153</v>
       </c>
       <c r="B38" s="212" t="s">
         <v>1031</v>
@@ -42590,8 +41872,8 @@
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A41" s="164">
-        <v>38</v>
+      <c r="A41" s="164" t="s">
+        <v>1153</v>
       </c>
       <c r="B41" s="241" t="s">
         <v>1152</v>
@@ -42882,8 +42164,8 @@
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A44" s="164">
-        <v>41</v>
+      <c r="A44" s="164" t="s">
+        <v>1153</v>
       </c>
       <c r="B44" s="235" t="s">
         <v>565</v>
@@ -43568,8 +42850,8 @@
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A51" s="164">
-        <v>48</v>
+      <c r="A51" s="164" t="s">
+        <v>1153</v>
       </c>
       <c r="B51" s="165" t="s">
         <v>1041</v>
@@ -44649,8 +43931,8 @@
       </c>
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A62" s="164">
-        <v>59</v>
+      <c r="A62" s="164" t="s">
+        <v>1153</v>
       </c>
       <c r="B62" s="236" t="s">
         <v>1046</v>
@@ -47086,8 +46368,8 @@
       </c>
     </row>
     <row r="87" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A87" s="164">
-        <v>84</v>
+      <c r="A87" s="164" t="s">
+        <v>1153</v>
       </c>
       <c r="B87" s="165" t="s">
         <v>400</v>
@@ -47584,10 +46866,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A93212-344E-4288-8D1E-646D88DABF7E}">
-  <dimension ref="A1:AF12"/>
+  <dimension ref="A1:AG12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" customWidth="1"/>
     <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" customWidth="1"/>
@@ -47598,7 +46880,7 @@
     <col min="32" max="32" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A1" s="225" t="s">
         <v>24</v>
       </c>
@@ -47695,8 +46977,11 @@
       <c r="AF1" s="249" t="s">
         <v>1099</v>
       </c>
+      <c r="AG1" s="225" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="225"/>
       <c r="B2" s="225">
         <f>SUBTOTAL(3,B4:B50)</f>
@@ -47816,8 +47101,9 @@
         <f>SUBTOTAL(9,AF4:AF50)</f>
         <v>233673000</v>
       </c>
+      <c r="AG2" s="17"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="41"/>
       <c r="B3" s="41" t="s">
         <v>0</v>
@@ -47908,10 +47194,13 @@
       <c r="AF3" s="41" t="s">
         <v>0</v>
       </c>
+      <c r="AG3" s="41" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A4" s="226">
-        <v>1</v>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" s="226" t="s">
+        <v>1153</v>
       </c>
       <c r="B4" s="226" t="s">
         <v>1067</v>
@@ -48029,8 +47318,11 @@
         <f t="shared" ref="AF4:AF10" si="8">F4*3</f>
         <v>20460000</v>
       </c>
+      <c r="AG4" s="17" t="s">
+        <v>1153</v>
+      </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" s="226">
         <v>2</v>
       </c>
@@ -48151,8 +47443,9 @@
         <f t="shared" si="8"/>
         <v>20955000</v>
       </c>
+      <c r="AG5" s="17"/>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" s="226">
         <v>3</v>
       </c>
@@ -48271,8 +47564,9 @@
         <f t="shared" si="8"/>
         <v>32208000</v>
       </c>
+      <c r="AG6" s="17"/>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="226">
         <v>4</v>
       </c>
@@ -48392,8 +47686,9 @@
         <f t="shared" si="8"/>
         <v>33000000</v>
       </c>
+      <c r="AG7" s="17"/>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" s="226">
         <v>5</v>
       </c>
@@ -48513,8 +47808,9 @@
         <f t="shared" si="8"/>
         <v>34650000</v>
       </c>
+      <c r="AG8" s="17"/>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="226">
         <v>6</v>
       </c>
@@ -48634,10 +47930,11 @@
         <f t="shared" si="8"/>
         <v>33990000</v>
       </c>
+      <c r="AG9" s="17"/>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A10" s="226">
-        <v>7</v>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" s="226" t="s">
+        <v>1153</v>
       </c>
       <c r="B10" s="226" t="s">
         <v>1087</v>
@@ -48755,8 +48052,11 @@
         <f t="shared" si="8"/>
         <v>23760000.000000004</v>
       </c>
+      <c r="AG10" s="17" t="s">
+        <v>1153</v>
+      </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="226">
         <v>8</v>
       </c>
@@ -48876,8 +48176,9 @@
         <f t="shared" ref="AF11:AF12" si="18">F11*3</f>
         <v>18150000</v>
       </c>
+      <c r="AG11" s="17"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="226">
         <v>9</v>
       </c>
@@ -48997,6 +48298,7 @@
         <f t="shared" si="18"/>
         <v>16500000</v>
       </c>
+      <c r="AG12" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="30" type="noConversion"/>
@@ -49009,7 +48311,7 @@
   <dimension ref="A1:Y12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" customWidth="1"/>
     <col min="2" max="2" width="15.77734375" customWidth="1"/>
     <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9211F1D-35E6-487D-A211-536261AE378B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E56817F-CB6D-4719-B467-A42DE35C12DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Theo dõi HĐ_Chi tiết" sheetId="2" r:id="rId1"/>
@@ -505,7 +505,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3247" uniqueCount="1154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3247" uniqueCount="1153">
   <si>
     <t>filter</t>
   </si>
@@ -3490,9 +3490,6 @@
   </si>
   <si>
     <t>Không có</t>
-  </si>
-  <si>
-    <t>c</t>
   </si>
   <si>
     <t>SMC</t>
@@ -12808,10 +12805,10 @@
         <v>35</v>
       </c>
       <c r="G1" s="83" t="s">
+        <v>903</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>904</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>905</v>
       </c>
       <c r="I1" s="31" t="s">
         <v>2</v>
@@ -12820,7 +12817,7 @@
         <v>145</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="L1" s="32" t="s">
         <v>468</v>
@@ -12883,7 +12880,7 @@
         <v>93</v>
       </c>
       <c r="AF1" s="7" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="AG1" s="7" t="s">
         <v>94</v>
@@ -13224,10 +13221,10 @@
         <v>356</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I4" s="33" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="J4" s="20">
         <v>44525</v>
@@ -13332,7 +13329,7 @@
         <v>356</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>901</v>
@@ -13532,7 +13529,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>32</v>
@@ -13657,7 +13654,7 @@
         <v>356</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I8" s="25" t="s">
         <v>901</v>
@@ -13870,10 +13867,10 @@
         <v>356</v>
       </c>
       <c r="H10" s="33" t="s">
+        <v>905</v>
+      </c>
+      <c r="I10" s="31" t="s">
         <v>906</v>
-      </c>
-      <c r="I10" s="31" t="s">
-        <v>907</v>
       </c>
       <c r="J10" s="20">
         <v>44586</v>
@@ -13980,7 +13977,7 @@
         <v>901</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="J11" s="20">
         <v>44586</v>
@@ -14304,7 +14301,7 @@
         <v>357</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I14" s="25" t="s">
         <v>901</v>
@@ -14417,10 +14414,10 @@
         <v>356</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I15" s="35" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="J15" s="20">
         <v>44631</v>
@@ -14621,7 +14618,7 @@
         <v>356</v>
       </c>
       <c r="H17" s="35" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I17" s="25" t="s">
         <v>901</v>
@@ -14935,7 +14932,7 @@
         <v>356</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I20" s="25" t="s">
         <v>901</v>
@@ -15037,7 +15034,7 @@
         <v>356</v>
       </c>
       <c r="H21" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I21" s="25" t="s">
         <v>901</v>
@@ -15239,7 +15236,7 @@
         <v>357</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I23" s="25" t="s">
         <v>901</v>
@@ -15339,7 +15336,7 @@
         <v>356</v>
       </c>
       <c r="H24" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I24" s="25" t="s">
         <v>901</v>
@@ -15443,10 +15440,10 @@
         <v>356</v>
       </c>
       <c r="H25" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I25" s="35" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="J25" s="20">
         <v>44703</v>
@@ -15645,16 +15642,16 @@
         <v>901</v>
       </c>
       <c r="H27" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I27" s="25" t="s">
         <v>901</v>
       </c>
       <c r="J27" s="97" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K27" s="97" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L27" s="34" t="s">
         <v>175</v>
@@ -15752,7 +15749,7 @@
         <v>901</v>
       </c>
       <c r="H28" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I28" s="25" t="s">
         <v>901</v>
@@ -15860,7 +15857,7 @@
         <v>356</v>
       </c>
       <c r="H29" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I29" s="25" t="s">
         <v>901</v>
@@ -15903,7 +15900,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="102" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="AE29" s="112" t="s">
         <v>383</v>
@@ -16060,7 +16057,7 @@
         <v>356</v>
       </c>
       <c r="H31" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I31" s="25" t="s">
         <v>901</v>
@@ -16190,7 +16187,7 @@
       <c r="W32" s="48"/>
       <c r="X32" s="48"/>
       <c r="Y32" s="18" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="Z32" s="102">
         <v>3000000</v>
@@ -16261,7 +16258,7 @@
         <v>901</v>
       </c>
       <c r="I33" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="J33" s="98">
         <v>44774</v>
@@ -16389,7 +16386,7 @@
       <c r="W34" s="48"/>
       <c r="X34" s="48"/>
       <c r="Y34" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="Z34" s="102">
         <v>5000000</v>
@@ -16562,7 +16559,7 @@
         <v>901</v>
       </c>
       <c r="I36" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="J36" s="98">
         <v>44774</v>
@@ -16686,7 +16683,7 @@
       <c r="W37" s="48"/>
       <c r="X37" s="48"/>
       <c r="Y37" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="Z37" s="102">
         <v>5000000</v>
@@ -16754,7 +16751,7 @@
         <v>477</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>902</v>
+        <v>356</v>
       </c>
       <c r="H38" s="27" t="s">
         <v>901</v>
@@ -16785,7 +16782,7 @@
       <c r="W38" s="48"/>
       <c r="X38" s="48"/>
       <c r="Y38" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z38" s="102">
         <v>5500000</v>
@@ -16884,7 +16881,7 @@
       <c r="W39" s="48"/>
       <c r="X39" s="48"/>
       <c r="Y39" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z39" s="102">
         <v>7700000</v>
@@ -16985,7 +16982,7 @@
       <c r="W40" s="48"/>
       <c r="X40" s="48"/>
       <c r="Y40" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="Z40" s="102">
         <v>6000000</v>
@@ -17082,7 +17079,7 @@
       <c r="W41" s="48"/>
       <c r="X41" s="48"/>
       <c r="Y41" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z41" s="102">
         <v>7000000</v>
@@ -17177,7 +17174,7 @@
       <c r="W42" s="48"/>
       <c r="X42" s="48"/>
       <c r="Y42" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z42" s="102">
         <v>8000000</v>
@@ -17249,7 +17246,7 @@
         <v>901</v>
       </c>
       <c r="I43" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="J43" s="125">
         <v>44885</v>
@@ -17272,7 +17269,7 @@
       <c r="W43" s="48"/>
       <c r="X43" s="48"/>
       <c r="Y43" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z43" s="102">
         <v>7000000</v>
@@ -17369,7 +17366,7 @@
       <c r="W44" s="48"/>
       <c r="X44" s="48"/>
       <c r="Y44" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z44" s="102">
         <v>6500000</v>
@@ -17464,7 +17461,7 @@
       <c r="W45" s="48"/>
       <c r="X45" s="48"/>
       <c r="Y45" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z45" s="102">
         <v>6000000</v>
@@ -17557,7 +17554,7 @@
       <c r="W46" s="48"/>
       <c r="X46" s="48"/>
       <c r="Y46" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="Z46" s="102">
         <v>0</v>
@@ -17606,7 +17603,7 @@
         <v>44</v>
       </c>
       <c r="B47" s="155" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>32</v>
@@ -17630,10 +17627,10 @@
         <v>901</v>
       </c>
       <c r="J47" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K47" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L47" s="112"/>
       <c r="M47" s="98">
@@ -17651,7 +17648,7 @@
       <c r="W47" s="48"/>
       <c r="X47" s="48"/>
       <c r="Y47" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="Z47" s="102">
         <v>0</v>
@@ -17740,7 +17737,7 @@
       <c r="W48" s="48"/>
       <c r="X48" s="48"/>
       <c r="Y48" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="Z48" s="102">
         <v>4300000</v>
@@ -17835,7 +17832,7 @@
       <c r="W49" s="48"/>
       <c r="X49" s="48"/>
       <c r="Y49" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z49" s="102">
         <v>6000000</v>
@@ -17928,7 +17925,7 @@
       <c r="W50" s="48"/>
       <c r="X50" s="48"/>
       <c r="Y50" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z50" s="102">
         <v>4000000</v>
@@ -18023,7 +18020,7 @@
       <c r="W51" s="48"/>
       <c r="X51" s="48"/>
       <c r="Y51" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="Z51" s="102">
         <v>4000000</v>
@@ -18118,7 +18115,7 @@
       <c r="W52" s="48"/>
       <c r="X52" s="48"/>
       <c r="Y52" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z52" s="102">
         <v>6500000</v>
@@ -18211,7 +18208,7 @@
       <c r="W53" s="48"/>
       <c r="X53" s="48"/>
       <c r="Y53" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z53" s="102">
         <v>6000000</v>
@@ -18306,7 +18303,7 @@
       <c r="W54" s="48"/>
       <c r="X54" s="48"/>
       <c r="Y54" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z54" s="102">
         <v>6000000</v>
@@ -18401,7 +18398,7 @@
       <c r="W55" s="48"/>
       <c r="X55" s="48"/>
       <c r="Y55" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z55" s="102">
         <v>6000000</v>
@@ -18494,7 +18491,7 @@
       <c r="W56" s="48"/>
       <c r="X56" s="48"/>
       <c r="Y56" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z56" s="102">
         <v>4000000</v>
@@ -18587,7 +18584,7 @@
       <c r="W57" s="48"/>
       <c r="X57" s="48"/>
       <c r="Y57" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z57" s="102">
         <v>4500000</v>
@@ -18680,7 +18677,7 @@
       <c r="W58" s="48"/>
       <c r="X58" s="48"/>
       <c r="Y58" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z58" s="102">
         <v>4000000</v>
@@ -18775,7 +18772,7 @@
       <c r="W59" s="48"/>
       <c r="X59" s="48"/>
       <c r="Y59" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z59" s="102">
         <v>4000000</v>
@@ -18868,7 +18865,7 @@
       <c r="W60" s="48"/>
       <c r="X60" s="48"/>
       <c r="Y60" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z60" s="102">
         <v>4000000</v>
@@ -18961,7 +18958,7 @@
       <c r="W61" s="48"/>
       <c r="X61" s="48"/>
       <c r="Y61" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z61" s="102">
         <v>4000000</v>
@@ -19050,7 +19047,7 @@
       <c r="W62" s="48"/>
       <c r="X62" s="48"/>
       <c r="Y62" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="Z62" s="102">
         <v>4000000</v>
@@ -19139,7 +19136,7 @@
       <c r="W63" s="48"/>
       <c r="X63" s="48"/>
       <c r="Y63" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="Z63" s="102">
         <v>5500000</v>
@@ -19211,7 +19208,7 @@
         <v>901</v>
       </c>
       <c r="I64" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="J64" s="125">
         <v>45402</v>
@@ -19234,7 +19231,7 @@
       <c r="W64" s="48"/>
       <c r="X64" s="48"/>
       <c r="Y64" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="Z64" s="102">
         <v>5000000</v>
@@ -19329,7 +19326,7 @@
       <c r="W65" s="48"/>
       <c r="X65" s="48"/>
       <c r="Y65" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z65" s="102">
         <v>7500000</v>
@@ -19424,7 +19421,7 @@
       <c r="W66" s="48"/>
       <c r="X66" s="48"/>
       <c r="Y66" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="Z66" s="102">
         <v>5000000</v>
@@ -19494,7 +19491,7 @@
         <v>901</v>
       </c>
       <c r="I67" s="34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="J67" s="125">
         <v>45397</v>
@@ -19517,7 +19514,7 @@
       <c r="W67" s="48"/>
       <c r="X67" s="48"/>
       <c r="Y67" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="Z67" s="102">
         <v>5000000</v>
@@ -19612,7 +19609,7 @@
       <c r="W68" s="48"/>
       <c r="X68" s="48"/>
       <c r="Y68" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z68" s="102">
         <v>4000000</v>
@@ -19707,7 +19704,7 @@
       <c r="W69" s="48"/>
       <c r="X69" s="48"/>
       <c r="Y69" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="Z69" s="102">
         <v>5000000</v>
@@ -19798,7 +19795,7 @@
       <c r="W70" s="48"/>
       <c r="X70" s="48"/>
       <c r="Y70" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z70" s="102">
         <v>4500000</v>
@@ -19887,7 +19884,7 @@
       <c r="W71" s="48"/>
       <c r="X71" s="48"/>
       <c r="Y71" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z71" s="102">
         <v>5500000</v>
@@ -19980,7 +19977,7 @@
       <c r="W72" s="48"/>
       <c r="X72" s="48"/>
       <c r="Y72" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z72" s="102">
         <v>5000000</v>
@@ -20073,7 +20070,7 @@
       <c r="W73" s="48"/>
       <c r="X73" s="48"/>
       <c r="Y73" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z73" s="102">
         <v>4000000</v>
@@ -20162,7 +20159,7 @@
       <c r="W74" s="48"/>
       <c r="X74" s="48"/>
       <c r="Y74" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z74" s="102">
         <v>5500000</v>
@@ -20251,7 +20248,7 @@
       <c r="W75" s="48"/>
       <c r="X75" s="48"/>
       <c r="Y75" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z75" s="102">
         <v>6000000</v>
@@ -20326,10 +20323,10 @@
         <v>901</v>
       </c>
       <c r="J76" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K76" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L76" s="34"/>
       <c r="M76" s="98"/>
@@ -20345,7 +20342,7 @@
       <c r="W76" s="48"/>
       <c r="X76" s="48"/>
       <c r="Y76" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z76" s="102">
         <v>4000000</v>
@@ -20440,7 +20437,7 @@
       <c r="W77" s="48"/>
       <c r="X77" s="48"/>
       <c r="Y77" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z77" s="102">
         <v>7000000</v>
@@ -20535,7 +20532,7 @@
       <c r="W78" s="48"/>
       <c r="X78" s="48"/>
       <c r="Y78" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z78" s="102">
         <v>4000000</v>
@@ -20610,10 +20607,10 @@
         <v>901</v>
       </c>
       <c r="J79" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K79" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L79" s="34"/>
       <c r="M79" s="98"/>
@@ -20629,7 +20626,7 @@
       <c r="W79" s="48"/>
       <c r="X79" s="48"/>
       <c r="Y79" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z79" s="102">
         <v>4000000</v>
@@ -20724,7 +20721,7 @@
       <c r="W80" s="48"/>
       <c r="X80" s="48"/>
       <c r="Y80" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z80" s="102">
         <v>5000000</v>
@@ -20788,7 +20785,7 @@
         <v>481</v>
       </c>
       <c r="G81" s="34" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H81" s="27" t="s">
         <v>901</v>
@@ -20797,10 +20794,10 @@
         <v>901</v>
       </c>
       <c r="J81" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K81" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L81" s="34"/>
       <c r="M81" s="98"/>
@@ -20816,7 +20813,7 @@
       <c r="W81" s="48"/>
       <c r="X81" s="48"/>
       <c r="Y81" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z81" s="102">
         <v>0</v>
@@ -20833,20 +20830,20 @@
       </c>
       <c r="AE81" s="87"/>
       <c r="AF81" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AG81" s="120"/>
       <c r="AH81" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AI81" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AJ81" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AK81" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AL81" s="2"/>
       <c r="AM81" s="2"/>
@@ -20876,7 +20873,7 @@
         <v>481</v>
       </c>
       <c r="G82" s="34" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H82" s="27" t="s">
         <v>901</v>
@@ -20885,10 +20882,10 @@
         <v>901</v>
       </c>
       <c r="J82" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K82" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L82" s="34"/>
       <c r="M82" s="98"/>
@@ -20904,7 +20901,7 @@
       <c r="W82" s="48"/>
       <c r="X82" s="48"/>
       <c r="Y82" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z82" s="102">
         <v>0</v>
@@ -20921,20 +20918,20 @@
       </c>
       <c r="AE82" s="87"/>
       <c r="AF82" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AG82" s="120"/>
       <c r="AH82" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AI82" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AJ82" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AK82" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AL82" s="2"/>
       <c r="AM82" s="2"/>
@@ -20964,7 +20961,7 @@
         <v>481</v>
       </c>
       <c r="G83" s="34" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H83" s="27" t="s">
         <v>901</v>
@@ -20973,10 +20970,10 @@
         <v>901</v>
       </c>
       <c r="J83" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K83" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L83" s="34"/>
       <c r="M83" s="98"/>
@@ -20992,7 +20989,7 @@
       <c r="W83" s="48"/>
       <c r="X83" s="48"/>
       <c r="Y83" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z83" s="102">
         <v>0</v>
@@ -21009,20 +21006,20 @@
       </c>
       <c r="AE83" s="87"/>
       <c r="AF83" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AG83" s="120"/>
       <c r="AH83" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AI83" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AJ83" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AK83" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AL83" s="2"/>
       <c r="AM83" s="2"/>
@@ -21052,7 +21049,7 @@
         <v>481</v>
       </c>
       <c r="G84" s="34" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H84" s="27" t="s">
         <v>901</v>
@@ -21061,10 +21058,10 @@
         <v>901</v>
       </c>
       <c r="J84" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K84" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L84" s="34"/>
       <c r="M84" s="98"/>
@@ -21080,7 +21077,7 @@
       <c r="W84" s="48"/>
       <c r="X84" s="48"/>
       <c r="Y84" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z84" s="102">
         <v>0</v>
@@ -21097,20 +21094,20 @@
       </c>
       <c r="AE84" s="87"/>
       <c r="AF84" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AG84" s="120"/>
       <c r="AH84" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AI84" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AJ84" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AK84" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AL84" s="2"/>
       <c r="AM84" s="2"/>
@@ -21140,7 +21137,7 @@
         <v>481</v>
       </c>
       <c r="G85" s="34" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H85" s="27" t="s">
         <v>901</v>
@@ -21149,10 +21146,10 @@
         <v>901</v>
       </c>
       <c r="J85" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K85" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L85" s="34"/>
       <c r="M85" s="98"/>
@@ -21168,7 +21165,7 @@
       <c r="W85" s="48"/>
       <c r="X85" s="48"/>
       <c r="Y85" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z85" s="102">
         <v>0</v>
@@ -21185,20 +21182,20 @@
       </c>
       <c r="AE85" s="87"/>
       <c r="AF85" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AG85" s="120"/>
       <c r="AH85" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AI85" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AJ85" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AK85" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AL85" s="2"/>
       <c r="AM85" s="2"/>
@@ -21228,7 +21225,7 @@
         <v>481</v>
       </c>
       <c r="G86" s="34" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H86" s="27" t="s">
         <v>901</v>
@@ -21237,10 +21234,10 @@
         <v>901</v>
       </c>
       <c r="J86" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K86" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L86" s="34"/>
       <c r="M86" s="98"/>
@@ -21256,7 +21253,7 @@
       <c r="W86" s="48"/>
       <c r="X86" s="48"/>
       <c r="Y86" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z86" s="102">
         <v>0</v>
@@ -21273,20 +21270,20 @@
       </c>
       <c r="AE86" s="87"/>
       <c r="AF86" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AG86" s="120"/>
       <c r="AH86" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AI86" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AJ86" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AK86" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AL86" s="2"/>
       <c r="AM86" s="2"/>
@@ -21316,7 +21313,7 @@
         <v>481</v>
       </c>
       <c r="G87" s="34" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H87" s="27" t="s">
         <v>901</v>
@@ -21325,10 +21322,10 @@
         <v>901</v>
       </c>
       <c r="J87" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K87" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L87" s="34"/>
       <c r="M87" s="98"/>
@@ -21344,7 +21341,7 @@
       <c r="W87" s="48"/>
       <c r="X87" s="48"/>
       <c r="Y87" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z87" s="102">
         <v>0</v>
@@ -21361,20 +21358,20 @@
       </c>
       <c r="AE87" s="87"/>
       <c r="AF87" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AG87" s="120"/>
       <c r="AH87" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AI87" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AJ87" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AK87" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AL87" s="2"/>
       <c r="AM87" s="2"/>
@@ -21404,7 +21401,7 @@
         <v>481</v>
       </c>
       <c r="G88" s="34" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H88" s="27" t="s">
         <v>901</v>
@@ -21413,10 +21410,10 @@
         <v>901</v>
       </c>
       <c r="J88" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K88" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L88" s="34"/>
       <c r="M88" s="98"/>
@@ -21432,7 +21429,7 @@
       <c r="W88" s="48"/>
       <c r="X88" s="48"/>
       <c r="Y88" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z88" s="102">
         <v>0</v>
@@ -21449,20 +21446,20 @@
       </c>
       <c r="AE88" s="87"/>
       <c r="AF88" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AG88" s="120"/>
       <c r="AH88" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AI88" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AJ88" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AK88" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AL88" s="2"/>
       <c r="AM88" s="2"/>
@@ -21492,7 +21489,7 @@
         <v>835</v>
       </c>
       <c r="G89" s="34" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H89" s="27" t="s">
         <v>901</v>
@@ -21501,10 +21498,10 @@
         <v>901</v>
       </c>
       <c r="J89" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K89" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L89" s="34"/>
       <c r="M89" s="98"/>
@@ -21520,7 +21517,7 @@
       <c r="W89" s="48"/>
       <c r="X89" s="48"/>
       <c r="Y89" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z89" s="102" t="s">
         <v>839</v>
@@ -21537,20 +21534,20 @@
       </c>
       <c r="AE89" s="87"/>
       <c r="AF89" s="121" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="AG89" s="120"/>
       <c r="AH89" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AI89" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AJ89" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AK89" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AL89" s="2"/>
       <c r="AM89" s="2"/>
@@ -21580,7 +21577,7 @@
         <v>836</v>
       </c>
       <c r="G90" s="34" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H90" s="27" t="s">
         <v>901</v>
@@ -21589,10 +21586,10 @@
         <v>901</v>
       </c>
       <c r="J90" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K90" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L90" s="34"/>
       <c r="M90" s="98"/>
@@ -21608,7 +21605,7 @@
       <c r="W90" s="48"/>
       <c r="X90" s="48"/>
       <c r="Y90" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z90" s="102" t="s">
         <v>839</v>
@@ -21625,20 +21622,20 @@
       </c>
       <c r="AE90" s="87"/>
       <c r="AF90" s="121" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="AG90" s="120"/>
       <c r="AH90" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AI90" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AJ90" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AK90" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AL90" s="2"/>
       <c r="AM90" s="2"/>
@@ -21668,7 +21665,7 @@
         <v>837</v>
       </c>
       <c r="G91" s="34" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H91" s="27" t="s">
         <v>901</v>
@@ -21677,10 +21674,10 @@
         <v>901</v>
       </c>
       <c r="J91" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K91" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L91" s="34"/>
       <c r="M91" s="98"/>
@@ -21696,7 +21693,7 @@
       <c r="W91" s="48"/>
       <c r="X91" s="48"/>
       <c r="Y91" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z91" s="102" t="s">
         <v>839</v>
@@ -21713,20 +21710,20 @@
       </c>
       <c r="AE91" s="87"/>
       <c r="AF91" s="121" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="AG91" s="120"/>
       <c r="AH91" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AI91" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AJ91" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AK91" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AL91" s="2"/>
       <c r="AM91" s="2"/>
@@ -21756,7 +21753,7 @@
         <v>838</v>
       </c>
       <c r="G92" s="34" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H92" s="27" t="s">
         <v>901</v>
@@ -21765,10 +21762,10 @@
         <v>901</v>
       </c>
       <c r="J92" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K92" s="125" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L92" s="34"/>
       <c r="M92" s="98"/>
@@ -21784,7 +21781,7 @@
       <c r="W92" s="48"/>
       <c r="X92" s="48"/>
       <c r="Y92" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z92" s="102" t="s">
         <v>839</v>
@@ -21801,20 +21798,20 @@
       </c>
       <c r="AE92" s="87"/>
       <c r="AF92" s="121" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="AG92" s="120"/>
       <c r="AH92" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AI92" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AJ92" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AK92" s="121" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="AL92" s="2"/>
       <c r="AM92" s="2"/>
@@ -21873,7 +21870,7 @@
       <c r="W93" s="48"/>
       <c r="X93" s="48"/>
       <c r="Y93" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="Z93" s="102">
         <v>5000000</v>
@@ -21968,7 +21965,7 @@
       <c r="W94" s="48"/>
       <c r="X94" s="48"/>
       <c r="Y94" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z94" s="102">
         <v>5000000</v>
@@ -22061,7 +22058,7 @@
       <c r="W95" s="48"/>
       <c r="X95" s="48"/>
       <c r="Y95" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z95" s="102">
         <v>4000000</v>
@@ -22110,7 +22107,7 @@
         <v>93</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>66</v>
@@ -22154,7 +22151,7 @@
       <c r="W96" s="48"/>
       <c r="X96" s="48"/>
       <c r="Y96" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z96" s="102">
         <v>4000000</v>
@@ -22247,7 +22244,7 @@
       <c r="W97" s="48"/>
       <c r="X97" s="48"/>
       <c r="Y97" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="Z97" s="102">
         <v>3000000</v>
@@ -22345,7 +22342,7 @@
       <c r="W98" s="48"/>
       <c r="X98" s="48"/>
       <c r="Y98" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z98" s="102">
         <v>5000000</v>
@@ -22438,7 +22435,7 @@
       <c r="W99" s="48"/>
       <c r="X99" s="48"/>
       <c r="Y99" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Z99" s="102">
         <v>4000000</v>
@@ -22574,7 +22571,7 @@
         <v>98</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>402</v>
@@ -22586,7 +22583,7 @@
         <v>10.977980000000001</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G101" s="34" t="s">
         <v>356</v>
@@ -22620,7 +22617,7 @@
       <c r="W101" s="48"/>
       <c r="X101" s="48"/>
       <c r="Y101" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="Z101" s="102">
         <v>4500000</v>
@@ -22637,16 +22634,16 @@
       </c>
       <c r="AG101" s="120"/>
       <c r="AH101" s="18" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="AI101" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="AJ101" s="2" t="s">
         <v>406</v>
       </c>
       <c r="AK101" s="2" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="AL101" s="2">
         <v>0</v>
@@ -22664,7 +22661,7 @@
         <v>99</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>15</v>
@@ -22676,7 +22673,7 @@
         <v>10.901565</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G102" s="34" t="s">
         <v>356</v>
@@ -22714,7 +22711,7 @@
       <c r="W102" s="48"/>
       <c r="X102" s="48"/>
       <c r="Y102" s="2" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="Z102" s="102">
         <v>6000000</v>
@@ -22731,16 +22728,16 @@
       </c>
       <c r="AG102" s="120"/>
       <c r="AH102" s="42" t="s">
+        <v>1147</v>
+      </c>
+      <c r="AI102" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="AJ102" s="41" t="s">
         <v>1148</v>
       </c>
-      <c r="AI102" s="2" t="s">
-        <v>1147</v>
-      </c>
-      <c r="AJ102" s="41" t="s">
+      <c r="AK102" s="2" t="s">
         <v>1149</v>
-      </c>
-      <c r="AK102" s="2" t="s">
-        <v>1150</v>
       </c>
       <c r="AL102" s="2">
         <v>14</v>
@@ -26064,10 +26061,10 @@
         <v>366</v>
       </c>
       <c r="C1" s="157" t="s">
+        <v>928</v>
+      </c>
+      <c r="D1" s="157" t="s">
         <v>929</v>
-      </c>
-      <c r="D1" s="157" t="s">
-        <v>930</v>
       </c>
       <c r="E1" s="158" t="s">
         <v>80</v>
@@ -26082,85 +26079,85 @@
         <v>68</v>
       </c>
       <c r="I1" s="157" t="s">
+        <v>930</v>
+      </c>
+      <c r="J1" s="157" t="s">
+        <v>993</v>
+      </c>
+      <c r="K1" s="157" t="s">
         <v>931</v>
       </c>
-      <c r="J1" s="157" t="s">
-        <v>994</v>
-      </c>
-      <c r="K1" s="157" t="s">
+      <c r="L1" s="157" t="s">
         <v>932</v>
       </c>
-      <c r="L1" s="157" t="s">
+      <c r="M1" s="157" t="s">
         <v>933</v>
       </c>
-      <c r="M1" s="157" t="s">
+      <c r="N1" s="157" t="s">
         <v>934</v>
       </c>
-      <c r="N1" s="157" t="s">
+      <c r="O1" s="157" t="s">
         <v>935</v>
       </c>
-      <c r="O1" s="157" t="s">
+      <c r="P1" s="157" t="s">
         <v>936</v>
       </c>
-      <c r="P1" s="157" t="s">
+      <c r="Q1" s="157" t="s">
         <v>937</v>
       </c>
-      <c r="Q1" s="157" t="s">
+      <c r="R1" s="157" t="s">
         <v>938</v>
       </c>
-      <c r="R1" s="157" t="s">
+      <c r="S1" s="157" t="s">
         <v>939</v>
       </c>
-      <c r="S1" s="157" t="s">
+      <c r="T1" s="159" t="s">
         <v>940</v>
       </c>
-      <c r="T1" s="159" t="s">
+      <c r="U1" s="159" t="s">
         <v>941</v>
       </c>
-      <c r="U1" s="159" t="s">
+      <c r="V1" s="159" t="s">
         <v>942</v>
       </c>
-      <c r="V1" s="159" t="s">
+      <c r="W1" s="159" t="s">
         <v>943</v>
       </c>
-      <c r="W1" s="159" t="s">
+      <c r="X1" s="159" t="s">
         <v>944</v>
       </c>
-      <c r="X1" s="159" t="s">
+      <c r="Y1" s="159" t="s">
         <v>945</v>
       </c>
-      <c r="Y1" s="159" t="s">
+      <c r="Z1" s="159" t="s">
         <v>946</v>
       </c>
-      <c r="Z1" s="159" t="s">
+      <c r="AA1" s="159" t="s">
         <v>947</v>
       </c>
-      <c r="AA1" s="159" t="s">
+      <c r="AB1" s="159" t="s">
+        <v>947</v>
+      </c>
+      <c r="AC1" s="159" t="s">
+        <v>988</v>
+      </c>
+      <c r="AD1" s="159" t="s">
+        <v>989</v>
+      </c>
+      <c r="AE1" s="159" t="s">
+        <v>990</v>
+      </c>
+      <c r="AF1" s="159" t="s">
+        <v>991</v>
+      </c>
+      <c r="AG1" s="159" t="s">
+        <v>992</v>
+      </c>
+      <c r="AH1" s="160" t="s">
         <v>948</v>
       </c>
-      <c r="AB1" s="159" t="s">
-        <v>948</v>
-      </c>
-      <c r="AC1" s="159" t="s">
-        <v>989</v>
-      </c>
-      <c r="AD1" s="159" t="s">
-        <v>990</v>
-      </c>
-      <c r="AE1" s="159" t="s">
-        <v>991</v>
-      </c>
-      <c r="AF1" s="159" t="s">
-        <v>992</v>
-      </c>
-      <c r="AG1" s="159" t="s">
-        <v>993</v>
-      </c>
-      <c r="AH1" s="160" t="s">
+      <c r="AI1" s="157" t="s">
         <v>949</v>
-      </c>
-      <c r="AI1" s="157" t="s">
-        <v>950</v>
       </c>
       <c r="AJ1" s="157" t="s">
         <v>173</v>
@@ -26547,14 +26544,14 @@
       </c>
       <c r="AH4" s="171">
         <f ca="1">AA4-TODAY()</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AI4" s="172">
         <f>3*D4</f>
         <v>19500000</v>
       </c>
       <c r="AJ4" s="164" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.2">
@@ -26682,14 +26679,14 @@
       </c>
       <c r="AH5" s="181">
         <f ca="1">AB5-TODAY()</f>
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AI5" s="175">
         <f>3*D5</f>
         <v>21000000</v>
       </c>
       <c r="AJ5" s="173" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.2">
@@ -26817,14 +26814,14 @@
       </c>
       <c r="AH6" s="171">
         <f ca="1">Z6-TODAY()</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI6" s="172">
         <f>3*D6</f>
         <v>17625000</v>
       </c>
       <c r="AJ6" s="164" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.2">
@@ -26832,7 +26829,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="173" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C7" s="165" t="s">
         <v>32</v>
@@ -26952,14 +26949,14 @@
       </c>
       <c r="AH7" s="181">
         <f ca="1">R7-TODAY()</f>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI7" s="175">
         <f>6*D7</f>
         <v>24000000</v>
       </c>
       <c r="AJ7" s="173" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
@@ -27087,14 +27084,14 @@
       </c>
       <c r="AH8" s="188">
         <f ca="1">Z8-TODAY()</f>
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AI8" s="166">
         <f>3*D8</f>
         <v>14250000</v>
       </c>
       <c r="AJ8" s="164" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.2">
@@ -27222,14 +27219,14 @@
       </c>
       <c r="AH9" s="171">
         <f ca="1">Z9-TODAY()</f>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AI9" s="166">
         <f>3*D9</f>
         <v>24900000</v>
       </c>
       <c r="AJ9" s="164" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.2">
@@ -27357,14 +27354,14 @@
       </c>
       <c r="AH10" s="171">
         <f ca="1">Z10-TODAY()</f>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI10" s="166">
         <f>D10*3</f>
         <v>18000000</v>
       </c>
       <c r="AJ10" s="164" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.2">
@@ -27492,14 +27489,14 @@
       </c>
       <c r="AH11" s="171">
         <f ca="1">Z11-TODAY()</f>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AI11" s="189">
         <f>D11*3</f>
         <v>21000000</v>
       </c>
       <c r="AJ11" s="165" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.2">
@@ -27627,14 +27624,14 @@
       </c>
       <c r="AH12" s="171">
         <f ca="1">Y12-TODAY()</f>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI12" s="166">
         <f>3*D12</f>
         <v>19500000</v>
       </c>
       <c r="AJ12" s="164" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.2">
@@ -27651,7 +27648,7 @@
         <v>7000000</v>
       </c>
       <c r="E13" s="190" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F13" s="166" t="s">
         <v>170</v>
@@ -27762,14 +27759,14 @@
       </c>
       <c r="AH13" s="171">
         <f ca="1">Z13-TODAY()</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="166">
         <f>3*7000000</f>
         <v>21000000</v>
       </c>
       <c r="AJ13" s="164" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.2">
@@ -27897,14 +27894,14 @@
       </c>
       <c r="AH14" s="188">
         <f ca="1">Y14-TODAY()</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI14" s="166">
         <f>3*D14</f>
         <v>18000000</v>
       </c>
       <c r="AJ14" s="164" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.2">
@@ -28032,14 +28029,14 @@
       </c>
       <c r="AH15" s="188">
         <f ca="1">R15-TODAY()</f>
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AI15" s="166">
         <f>6*D15</f>
         <v>42000000</v>
       </c>
       <c r="AJ15" s="164" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.2">
@@ -28166,14 +28163,14 @@
       </c>
       <c r="AH16" s="171">
         <f ca="1">R16-TODAY()</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AI16" s="166">
         <f>6*D16</f>
         <v>39600000</v>
       </c>
       <c r="AJ16" s="164" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.2">
@@ -28190,7 +28187,7 @@
         <v>7000000</v>
       </c>
       <c r="E17" s="166" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F17" s="166" t="s">
         <v>233</v>
@@ -28301,14 +28298,14 @@
       </c>
       <c r="AH17" s="188">
         <f ca="1">Z17-TODAY()</f>
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AI17" s="166">
         <f>3*D17</f>
         <v>21000000</v>
       </c>
       <c r="AJ17" s="164" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.2">
@@ -28436,14 +28433,14 @@
       </c>
       <c r="AH18" s="188">
         <f ca="1">R18-TODAY()</f>
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AI18" s="166">
         <f>6*D18</f>
         <v>31800000</v>
       </c>
       <c r="AJ18" s="164" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.2">
@@ -28571,19 +28568,19 @@
       </c>
       <c r="AH19" s="188">
         <f ca="1">Y19-TODAY()</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI19" s="166">
         <f>3*D19</f>
         <v>18000000</v>
       </c>
       <c r="AJ19" s="164" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="164" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B20" s="174" t="s">
         <v>427</v>
@@ -28706,14 +28703,14 @@
       </c>
       <c r="AH20" s="194">
         <f ca="1">R20-TODAY()</f>
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AI20" s="175">
         <f>6*D20</f>
         <v>30000000</v>
       </c>
       <c r="AJ20" s="173" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.2">
@@ -28841,14 +28838,14 @@
       </c>
       <c r="AH21" s="188">
         <f ca="1">Z21-TODAY()</f>
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AI21" s="166">
         <f>3*D21</f>
         <v>19500000</v>
       </c>
       <c r="AJ21" s="164" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.2">
@@ -28977,14 +28974,14 @@
       </c>
       <c r="AH22" s="188">
         <f ca="1">R22-TODAY()</f>
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AI22" s="166">
         <f>6*D22</f>
         <v>24000000</v>
       </c>
       <c r="AJ22" s="164" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.2">
@@ -29001,7 +28998,7 @@
         <v>6000000</v>
       </c>
       <c r="E23" s="197" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="F23" s="166" t="s">
         <v>293</v>
@@ -29112,14 +29109,14 @@
       </c>
       <c r="AH23" s="188">
         <f ca="1">R23-TODAY()</f>
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AI23" s="166">
         <f>D23*6</f>
         <v>36000000</v>
       </c>
       <c r="AJ23" s="164" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.2">
@@ -29247,14 +29244,14 @@
       </c>
       <c r="AH24" s="188">
         <f ca="1">X24-TODAY()</f>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AI24" s="189">
         <f>3*D24</f>
         <v>15000000</v>
       </c>
       <c r="AJ24" s="164" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.2">
@@ -29271,10 +29268,10 @@
         <v>6500000</v>
       </c>
       <c r="E25" s="198" t="s">
+        <v>960</v>
+      </c>
+      <c r="F25" s="175" t="s">
         <v>961</v>
-      </c>
-      <c r="F25" s="175" t="s">
-        <v>962</v>
       </c>
       <c r="G25" s="175" t="s">
         <v>406</v>
@@ -29382,14 +29379,14 @@
       </c>
       <c r="AH25" s="194">
         <f ca="1">Y25-TODAY()</f>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AI25" s="175">
         <f>3*D25</f>
         <v>19500000</v>
       </c>
       <c r="AJ25" s="173" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.2">
@@ -29517,14 +29514,14 @@
       </c>
       <c r="AH26" s="188">
         <f ca="1">Q26-TODAY()</f>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI26" s="166">
         <f>6*D26</f>
         <v>36000000</v>
       </c>
       <c r="AJ26" s="164" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.2">
@@ -29541,7 +29538,7 @@
         <v>5000000</v>
       </c>
       <c r="E27" s="197" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F27" s="166" t="s">
         <v>393</v>
@@ -29652,14 +29649,14 @@
       </c>
       <c r="AH27" s="188">
         <f ca="1">Y27-TODAY()</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AI27" s="166">
         <f>3*D27</f>
         <v>15000000</v>
       </c>
       <c r="AJ27" s="164" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.2">
@@ -29787,14 +29784,14 @@
       </c>
       <c r="AH28" s="194">
         <f ca="1">R28-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AI28" s="175">
         <f>6*D28</f>
         <v>34500000</v>
       </c>
       <c r="AJ28" s="173" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.2">
@@ -29853,7 +29850,7 @@
         <v>45931</v>
       </c>
       <c r="Q29" s="169" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="R29" s="202">
         <v>46023</v>
@@ -29920,14 +29917,14 @@
       </c>
       <c r="AH29" s="188">
         <f ca="1">S29-TODAY()</f>
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AI29" s="203">
         <f>D29*6</f>
         <v>42000000</v>
       </c>
       <c r="AJ29" s="164" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.2">
@@ -30055,14 +30052,14 @@
       </c>
       <c r="AH30" s="188">
         <f ca="1">X30-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AI30" s="203">
         <f>D30*3</f>
         <v>9000000</v>
       </c>
       <c r="AJ30" s="164" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.2">
@@ -30190,14 +30187,14 @@
       </c>
       <c r="AH31" s="194">
         <f ca="1">R31-TODAY()</f>
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AI31" s="196">
         <f>D31*6</f>
         <v>51000000</v>
       </c>
       <c r="AJ31" s="173" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.2">
@@ -30325,14 +30322,14 @@
       </c>
       <c r="AH32" s="188">
         <f ca="1">X32-TODAY()</f>
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AI32" s="203">
         <f t="shared" ref="AI32:AI36" si="40">D32*3</f>
         <v>15000000</v>
       </c>
       <c r="AJ32" s="164" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.2">
@@ -30460,14 +30457,14 @@
       </c>
       <c r="AH33" s="188">
         <f ca="1">X33-TODAY()</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI33" s="207">
         <f t="shared" si="40"/>
         <v>21000000</v>
       </c>
       <c r="AJ33" s="164" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.2">
@@ -30595,14 +30592,14 @@
       </c>
       <c r="AH34" s="194">
         <f ca="1">X34-TODAY()</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AI34" s="196">
         <f t="shared" si="40"/>
         <v>15000000</v>
       </c>
       <c r="AJ34" s="173" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.2">
@@ -30730,14 +30727,14 @@
       </c>
       <c r="AH35" s="188">
         <f ca="1">X35-TODAY()</f>
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AI35" s="203">
         <f t="shared" si="40"/>
         <v>15000000</v>
       </c>
       <c r="AJ35" s="164" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.2">
@@ -30865,14 +30862,14 @@
       </c>
       <c r="AH36" s="188">
         <f ca="1">X36-TODAY()</f>
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AI36" s="203">
         <f t="shared" si="40"/>
         <v>16500000</v>
       </c>
       <c r="AJ36" s="164" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.2">
@@ -30999,14 +30996,14 @@
       </c>
       <c r="AH37" s="188">
         <f ca="1">Q37-TODAY()</f>
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AI37" s="203">
         <f>D37*6</f>
         <v>46200000</v>
       </c>
       <c r="AJ37" s="164" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.2">
@@ -31134,14 +31131,14 @@
       </c>
       <c r="AH38" s="188">
         <f ca="1">Q38-TODAY()</f>
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AI38" s="203">
         <f>D38*6</f>
         <v>36000000</v>
       </c>
       <c r="AJ38" s="164" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.2">
@@ -31269,14 +31266,14 @@
       </c>
       <c r="AH39" s="188">
         <f ca="1">Q39-TODAY()</f>
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AI39" s="203">
         <f>D39*6</f>
         <v>42000000</v>
       </c>
       <c r="AJ39" s="164" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.2">
@@ -31404,14 +31401,14 @@
       </c>
       <c r="AH40" s="188">
         <f ca="1">X40-TODAY()</f>
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AI40" s="203">
         <f>D40*3</f>
         <v>24000000</v>
       </c>
       <c r="AJ40" s="164" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.2">
@@ -31539,14 +31536,14 @@
       </c>
       <c r="AH41" s="188">
         <f ca="1">W41-TODAY()</f>
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AI41" s="203">
         <f>D41*3</f>
         <v>21000000</v>
       </c>
       <c r="AJ41" s="164" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.2">
@@ -31674,14 +31671,14 @@
       </c>
       <c r="AH42" s="188">
         <f ca="1">V42-TODAY()</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AI42" s="203">
         <f t="shared" ref="AI42:AI43" si="49">D42*3</f>
         <v>19500000</v>
       </c>
       <c r="AJ42" s="164" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.2">
@@ -31809,22 +31806,22 @@
       </c>
       <c r="AH43" s="194">
         <f ca="1">V43-TODAY()</f>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AI43" s="196">
         <f t="shared" si="49"/>
         <v>18000000</v>
       </c>
       <c r="AJ43" s="173" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A44" s="164" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B44" s="164" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C44" s="165" t="s">
         <v>32</v>
@@ -31848,13 +31845,13 @@
         <v>79</v>
       </c>
       <c r="J44" s="169" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="K44" s="169" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L44" s="169" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="M44" s="201">
         <v>45047</v>
@@ -31941,14 +31938,14 @@
       </c>
       <c r="AH44" s="188">
         <f ca="1">S44-TODAY()</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AI44" s="203">
         <f>D44*6</f>
         <v>36000000</v>
       </c>
       <c r="AJ44" s="164" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.2">
@@ -32076,14 +32073,14 @@
       </c>
       <c r="AH45" s="194">
         <f ca="1">P45-TODAY()</f>
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AI45" s="196">
         <f>D45*6</f>
         <v>25800000</v>
       </c>
       <c r="AJ45" s="173" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.2">
@@ -32211,14 +32208,14 @@
       </c>
       <c r="AH46" s="188">
         <f ca="1">W46-TODAY()</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI46" s="203">
         <f>D46*1</f>
         <v>6000000</v>
       </c>
       <c r="AJ46" s="164" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.2">
@@ -32346,13 +32343,13 @@
       </c>
       <c r="AH47" s="188">
         <f ca="1">P47-TODAY()</f>
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AI47" s="203">
         <v>24000000</v>
       </c>
       <c r="AJ47" s="164" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.2">
@@ -32480,13 +32477,13 @@
       </c>
       <c r="AH48" s="188">
         <f ca="1">P48-TODAY()</f>
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AI48" s="203">
         <v>24000000</v>
       </c>
       <c r="AJ48" s="164" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.2">
@@ -32614,14 +32611,14 @@
       </c>
       <c r="AH49" s="188">
         <f ca="1">P49-TODAY()</f>
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AI49" s="203">
         <f>D49*6</f>
         <v>39000000</v>
       </c>
       <c r="AJ49" s="164" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.2">
@@ -32749,14 +32746,14 @@
       </c>
       <c r="AH50" s="188">
         <f t="shared" ref="AH50:AH54" ca="1" si="55">O50-TODAY()</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AI50" s="203">
         <f>D50*6</f>
         <v>36000000</v>
       </c>
       <c r="AJ50" s="164" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.2">
@@ -32773,16 +32770,16 @@
         <v>6000000</v>
       </c>
       <c r="E51" s="198" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F51" s="175" t="s">
         <v>629</v>
       </c>
       <c r="G51" s="175" t="s">
+        <v>973</v>
+      </c>
+      <c r="H51" s="175" t="s">
         <v>974</v>
-      </c>
-      <c r="H51" s="175" t="s">
-        <v>975</v>
       </c>
       <c r="I51" s="173" t="s">
         <v>79</v>
@@ -32884,14 +32881,14 @@
       </c>
       <c r="AH51" s="188">
         <f t="shared" ca="1" si="55"/>
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AI51" s="196">
         <f t="shared" ref="AI51:AI60" si="56">D51*6</f>
         <v>36000000</v>
       </c>
       <c r="AJ51" s="173" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.2">
@@ -32917,7 +32914,7 @@
         <v>406</v>
       </c>
       <c r="H52" s="166" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="I52" s="210" t="s">
         <v>79</v>
@@ -33019,14 +33016,14 @@
       </c>
       <c r="AH52" s="188">
         <f t="shared" ca="1" si="55"/>
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AI52" s="203">
         <f>D52*6</f>
         <v>39000000</v>
       </c>
       <c r="AJ52" s="164" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.2">
@@ -33037,7 +33034,7 @@
         <v>645</v>
       </c>
       <c r="C53" s="165" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D53" s="203">
         <v>4500000</v>
@@ -33154,14 +33151,14 @@
       </c>
       <c r="AH53" s="188">
         <f t="shared" ca="1" si="55"/>
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AI53" s="203">
         <f t="shared" si="56"/>
         <v>27000000</v>
       </c>
       <c r="AJ53" s="164" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.2">
@@ -33289,14 +33286,14 @@
       </c>
       <c r="AH54" s="188">
         <f t="shared" ca="1" si="55"/>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AI54" s="203">
         <f t="shared" si="56"/>
         <v>24000000</v>
       </c>
       <c r="AJ54" s="164" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.2">
@@ -33424,14 +33421,14 @@
       </c>
       <c r="AH55" s="188">
         <f ca="1">P55-TODAY()</f>
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AI55" s="203">
         <f t="shared" si="56"/>
         <v>33000000</v>
       </c>
       <c r="AJ55" s="164" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.2">
@@ -33559,14 +33556,14 @@
       </c>
       <c r="AH56" s="188">
         <f t="shared" ref="AH56:AH67" ca="1" si="58">N56-TODAY()</f>
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="AI56" s="203">
         <f t="shared" si="56"/>
         <v>24000000</v>
       </c>
       <c r="AJ56" s="164" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.2">
@@ -33694,14 +33691,14 @@
       </c>
       <c r="AH57" s="188">
         <f t="shared" ca="1" si="58"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI57" s="203">
         <f t="shared" si="56"/>
         <v>24000000</v>
       </c>
       <c r="AJ57" s="164" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.2">
@@ -33829,14 +33826,14 @@
       </c>
       <c r="AH58" s="188">
         <f ca="1">O58-TODAY()</f>
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AI58" s="203">
         <f t="shared" si="56"/>
         <v>24000000</v>
       </c>
       <c r="AJ58" s="164" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.2">
@@ -33964,14 +33961,14 @@
       </c>
       <c r="AH59" s="188">
         <f t="shared" ca="1" si="58"/>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AI59" s="203">
         <f t="shared" si="56"/>
         <v>24000000</v>
       </c>
       <c r="AJ59" s="164" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.2">
@@ -34099,14 +34096,14 @@
       </c>
       <c r="AH60" s="188">
         <f t="shared" ca="1" si="58"/>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AI60" s="203">
         <f t="shared" si="56"/>
         <v>24000000</v>
       </c>
       <c r="AJ60" s="164" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="61" spans="1:36" x14ac:dyDescent="0.2">
@@ -34234,14 +34231,14 @@
       </c>
       <c r="AH61" s="188">
         <f t="shared" ca="1" si="58"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI61" s="203">
         <f>D61*6</f>
         <v>24000000</v>
       </c>
       <c r="AJ61" s="164" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="62" spans="1:36" x14ac:dyDescent="0.2">
@@ -34264,7 +34261,7 @@
         <v>740</v>
       </c>
       <c r="G62" s="166" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H62" s="166" t="s">
         <v>744</v>
@@ -34369,14 +34366,14 @@
       </c>
       <c r="AH62" s="188">
         <f t="shared" ca="1" si="58"/>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AI62" s="203">
         <f t="shared" ref="AI62:AI85" si="61">D62*6</f>
         <v>24000000</v>
       </c>
       <c r="AJ62" s="164" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.2">
@@ -34504,14 +34501,14 @@
       </c>
       <c r="AH63" s="188">
         <f t="shared" ca="1" si="58"/>
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AI63" s="203">
         <f t="shared" si="61"/>
         <v>30000000</v>
       </c>
       <c r="AJ63" s="164" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.2">
@@ -34639,14 +34636,14 @@
       </c>
       <c r="AH64" s="188">
         <f t="shared" ca="1" si="58"/>
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AI64" s="203">
         <f>D64*6</f>
         <v>33000000</v>
       </c>
       <c r="AJ64" s="164" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="65" spans="1:36" x14ac:dyDescent="0.2">
@@ -34774,14 +34771,14 @@
       </c>
       <c r="AH65" s="188">
         <f t="shared" ca="1" si="58"/>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AI65" s="203">
         <f t="shared" si="61"/>
         <v>42000000</v>
       </c>
       <c r="AJ65" s="164" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="66" spans="1:36" x14ac:dyDescent="0.2">
@@ -34804,7 +34801,7 @@
         <v>736</v>
       </c>
       <c r="G66" s="166" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H66" s="166" t="s">
         <v>718</v>
@@ -34909,14 +34906,14 @@
       </c>
       <c r="AH66" s="188">
         <f t="shared" ca="1" si="58"/>
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AI66" s="203">
         <f>D66*6</f>
         <v>45000000</v>
       </c>
       <c r="AJ66" s="173" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="67" spans="1:36" x14ac:dyDescent="0.2">
@@ -35044,14 +35041,14 @@
       </c>
       <c r="AH67" s="188">
         <f t="shared" ca="1" si="58"/>
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AI67" s="203">
         <f t="shared" si="61"/>
         <v>30000000</v>
       </c>
       <c r="AJ67" s="164" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="68" spans="1:36" x14ac:dyDescent="0.2">
@@ -35179,14 +35176,14 @@
       </c>
       <c r="AH68" s="188">
         <f ca="1">N68-TODAY()</f>
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AI68" s="203">
         <f t="shared" si="61"/>
         <v>33000000</v>
       </c>
       <c r="AJ68" s="164" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="69" spans="1:36" x14ac:dyDescent="0.2">
@@ -35314,14 +35311,14 @@
       </c>
       <c r="AH69" s="188">
         <f ca="1">N69-TODAY()</f>
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AI69" s="203">
         <f t="shared" si="61"/>
         <v>30000000</v>
       </c>
       <c r="AJ69" s="164" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="70" spans="1:36" x14ac:dyDescent="0.2">
@@ -35449,14 +35446,14 @@
       </c>
       <c r="AH70" s="188">
         <f t="shared" ref="AH70:AH73" ca="1" si="64">M70-TODAY()</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI70" s="203">
         <f t="shared" si="61"/>
         <v>30000000</v>
       </c>
       <c r="AJ70" s="164" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="71" spans="1:36" x14ac:dyDescent="0.2">
@@ -35584,14 +35581,14 @@
       </c>
       <c r="AH71" s="188">
         <f ca="1">N71-TODAY()</f>
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AI71" s="203">
         <f t="shared" si="61"/>
         <v>27000000</v>
       </c>
       <c r="AJ71" s="164" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="72" spans="1:36" x14ac:dyDescent="0.2">
@@ -35719,14 +35716,14 @@
       </c>
       <c r="AH72" s="188">
         <f t="shared" ca="1" si="64"/>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AI72" s="203">
         <f t="shared" si="61"/>
         <v>36000000</v>
       </c>
       <c r="AJ72" s="164" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="73" spans="1:36" x14ac:dyDescent="0.2">
@@ -35854,14 +35851,14 @@
       </c>
       <c r="AH73" s="188">
         <f t="shared" ca="1" si="64"/>
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AI73" s="203">
         <f t="shared" si="61"/>
         <v>24000000</v>
       </c>
       <c r="AJ73" s="164" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="74" spans="1:36" x14ac:dyDescent="0.2">
@@ -35989,14 +35986,14 @@
       </c>
       <c r="AH74" s="188">
         <f ca="1">M74-TODAY()</f>
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI74" s="203">
         <f t="shared" si="61"/>
         <v>42000000</v>
       </c>
       <c r="AJ74" s="164" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="75" spans="1:36" x14ac:dyDescent="0.2">
@@ -36124,14 +36121,14 @@
       </c>
       <c r="AH75" s="188">
         <f ca="1">M75-TODAY()</f>
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AI75" s="203">
         <f t="shared" si="61"/>
         <v>24000000</v>
       </c>
       <c r="AJ75" s="164" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="76" spans="1:36" x14ac:dyDescent="0.2">
@@ -36259,14 +36256,14 @@
       </c>
       <c r="AH76" s="188">
         <f ca="1">M76-TODAY()</f>
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AI76" s="203">
         <f t="shared" si="61"/>
         <v>24000000</v>
       </c>
       <c r="AJ76" s="164" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="77" spans="1:36" x14ac:dyDescent="0.2">
@@ -36394,14 +36391,14 @@
       </c>
       <c r="AH77" s="188">
         <f ca="1">M77-TODAY()</f>
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AI77" s="203">
         <f t="shared" si="61"/>
         <v>30000000</v>
       </c>
       <c r="AJ77" s="164" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="78" spans="1:36" x14ac:dyDescent="0.2">
@@ -36427,7 +36424,7 @@
         <v>171</v>
       </c>
       <c r="H78" s="164" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="I78" s="192" t="s">
         <v>79</v>
@@ -36529,14 +36526,14 @@
       </c>
       <c r="AH78" s="188">
         <f t="shared" ref="AH78:AH79" ca="1" si="65">L78-TODAY()</f>
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AI78" s="203">
         <f t="shared" si="61"/>
         <v>18000000</v>
       </c>
       <c r="AJ78" s="164" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="79" spans="1:36" x14ac:dyDescent="0.2">
@@ -36544,7 +36541,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="164" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C79" s="165" t="s">
         <v>66</v>
@@ -36559,7 +36556,7 @@
         <v>820</v>
       </c>
       <c r="G79" s="165" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H79" s="164" t="s">
         <v>822</v>
@@ -36664,14 +36661,14 @@
       </c>
       <c r="AH79" s="188">
         <f t="shared" ca="1" si="65"/>
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AI79" s="203">
         <f t="shared" si="61"/>
         <v>24000000</v>
       </c>
       <c r="AJ79" s="164" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="80" spans="1:36" x14ac:dyDescent="0.2">
@@ -36799,14 +36796,14 @@
       </c>
       <c r="AH80" s="188">
         <f ca="1">L80-TODAY()</f>
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI80" s="203">
         <f t="shared" si="61"/>
         <v>30000000</v>
       </c>
       <c r="AJ80" s="222" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="81" spans="1:36" x14ac:dyDescent="0.2">
@@ -36934,14 +36931,14 @@
       </c>
       <c r="AH81" s="188">
         <f ca="1">L81-TODAY()</f>
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AI81" s="203">
         <f t="shared" si="61"/>
         <v>30000000</v>
       </c>
       <c r="AJ81" s="164" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="82" spans="1:36" x14ac:dyDescent="0.2">
@@ -37069,14 +37066,14 @@
       </c>
       <c r="AH82" s="188">
         <f ca="1">L82-TODAY()</f>
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AI82" s="203">
         <f t="shared" si="61"/>
         <v>24000000</v>
       </c>
       <c r="AJ82" s="222" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="83" spans="1:36" x14ac:dyDescent="0.2">
@@ -37204,14 +37201,14 @@
       </c>
       <c r="AH83" s="188">
         <f ca="1">L83-TODAY()</f>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AI83" s="203">
         <f t="shared" si="61"/>
         <v>30000000</v>
       </c>
       <c r="AJ83" s="164" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="84" spans="1:36" x14ac:dyDescent="0.2">
@@ -37339,14 +37336,14 @@
       </c>
       <c r="AH84" s="188">
         <f ca="1">L84-TODAY()</f>
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AI84" s="203">
         <f t="shared" si="61"/>
         <v>24000000</v>
       </c>
       <c r="AJ84" s="164" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="85" spans="1:36" x14ac:dyDescent="0.2">
@@ -37474,14 +37471,14 @@
       </c>
       <c r="AH85" s="188">
         <f ca="1">K85-TODAY()</f>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI85" s="203">
         <f t="shared" si="61"/>
         <v>36000000</v>
       </c>
       <c r="AJ85" s="164" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
   </sheetData>
@@ -37969,76 +37966,76 @@
         <v>366</v>
       </c>
       <c r="C1" s="157" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D1" s="157" t="s">
+        <v>994</v>
+      </c>
+      <c r="E1" s="157" t="s">
+        <v>995</v>
+      </c>
+      <c r="F1" s="157" t="s">
         <v>1062</v>
       </c>
-      <c r="D1" s="157" t="s">
-        <v>995</v>
-      </c>
-      <c r="E1" s="157" t="s">
+      <c r="G1" s="230" t="s">
         <v>996</v>
       </c>
-      <c r="F1" s="157" t="s">
-        <v>1063</v>
-      </c>
-      <c r="G1" s="230" t="s">
+      <c r="H1" s="230" t="s">
         <v>997</v>
       </c>
-      <c r="H1" s="230" t="s">
+      <c r="I1" s="230" t="s">
         <v>998</v>
       </c>
-      <c r="I1" s="230" t="s">
+      <c r="J1" s="230" t="s">
         <v>999</v>
       </c>
-      <c r="J1" s="230" t="s">
+      <c r="K1" s="230" t="s">
         <v>1000</v>
       </c>
-      <c r="K1" s="230" t="s">
+      <c r="L1" s="230" t="s">
         <v>1001</v>
       </c>
-      <c r="L1" s="230" t="s">
+      <c r="M1" s="230" t="s">
         <v>1002</v>
       </c>
-      <c r="M1" s="230" t="s">
+      <c r="N1" s="230" t="s">
         <v>1003</v>
       </c>
-      <c r="N1" s="230" t="s">
+      <c r="O1" s="230" t="s">
+        <v>1003</v>
+      </c>
+      <c r="P1" s="230" t="s">
         <v>1004</v>
       </c>
-      <c r="O1" s="230" t="s">
+      <c r="Q1" s="230" t="s">
         <v>1004</v>
       </c>
-      <c r="P1" s="230" t="s">
+      <c r="R1" s="230" t="s">
+        <v>1053</v>
+      </c>
+      <c r="S1" s="230" t="s">
+        <v>1054</v>
+      </c>
+      <c r="T1" s="230" t="s">
+        <v>1055</v>
+      </c>
+      <c r="U1" s="230" t="s">
+        <v>1056</v>
+      </c>
+      <c r="V1" s="230" t="s">
+        <v>1057</v>
+      </c>
+      <c r="W1" s="230" t="s">
+        <v>1058</v>
+      </c>
+      <c r="X1" s="230" t="s">
+        <v>1059</v>
+      </c>
+      <c r="Y1" s="230" t="s">
+        <v>1060</v>
+      </c>
+      <c r="Z1" s="231" t="s">
         <v>1005</v>
-      </c>
-      <c r="Q1" s="230" t="s">
-        <v>1005</v>
-      </c>
-      <c r="R1" s="230" t="s">
-        <v>1054</v>
-      </c>
-      <c r="S1" s="230" t="s">
-        <v>1055</v>
-      </c>
-      <c r="T1" s="230" t="s">
-        <v>1056</v>
-      </c>
-      <c r="U1" s="230" t="s">
-        <v>1057</v>
-      </c>
-      <c r="V1" s="230" t="s">
-        <v>1058</v>
-      </c>
-      <c r="W1" s="230" t="s">
-        <v>1059</v>
-      </c>
-      <c r="X1" s="230" t="s">
-        <v>1060</v>
-      </c>
-      <c r="Y1" s="230" t="s">
-        <v>1061</v>
-      </c>
-      <c r="Z1" s="231" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
@@ -38239,7 +38236,7 @@
       </c>
       <c r="D4" s="189"/>
       <c r="E4" s="164" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F4" s="233">
         <v>44594</v>
@@ -38337,7 +38334,7 @@
       </c>
       <c r="D5" s="189"/>
       <c r="E5" s="164" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F5" s="233">
         <v>44594</v>
@@ -38435,7 +38432,7 @@
       </c>
       <c r="D6" s="208"/>
       <c r="E6" s="173" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F6" s="234">
         <v>44678</v>
@@ -38526,14 +38523,14 @@
         <v>4</v>
       </c>
       <c r="B7" s="235" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C7" s="189">
         <v>6300000</v>
       </c>
       <c r="D7" s="189"/>
       <c r="E7" s="164" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F7" s="233">
         <v>44630</v>
@@ -38621,7 +38618,7 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" s="164" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B8" s="165" t="s">
         <v>95</v>
@@ -38631,7 +38628,7 @@
       </c>
       <c r="D8" s="189"/>
       <c r="E8" s="164" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F8" s="233">
         <v>44655</v>
@@ -38729,7 +38726,7 @@
       </c>
       <c r="D9" s="189"/>
       <c r="E9" s="164" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F9" s="233">
         <v>44752</v>
@@ -38827,7 +38824,7 @@
       </c>
       <c r="D10" s="208"/>
       <c r="E10" s="173" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F10" s="234">
         <v>44678</v>
@@ -38924,10 +38921,10 @@
         <v>8640000</v>
       </c>
       <c r="D11" s="237" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E11" s="164" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F11" s="233">
         <v>44729</v>
@@ -39025,7 +39022,7 @@
       </c>
       <c r="D12" s="189"/>
       <c r="E12" s="164" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F12" s="233">
         <v>44662</v>
@@ -39123,7 +39120,7 @@
       </c>
       <c r="D13" s="189"/>
       <c r="E13" s="164" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F13" s="233">
         <v>44701</v>
@@ -39221,7 +39218,7 @@
       </c>
       <c r="D14" s="208"/>
       <c r="E14" s="173" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="F14" s="234">
         <v>44676</v>
@@ -39319,7 +39316,7 @@
       </c>
       <c r="D15" s="189"/>
       <c r="E15" s="164" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F15" s="233">
         <v>44780</v>
@@ -39417,7 +39414,7 @@
       </c>
       <c r="D16" s="189"/>
       <c r="E16" s="164" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F16" s="233">
         <v>44801</v>
@@ -39515,7 +39512,7 @@
       </c>
       <c r="D17" s="208"/>
       <c r="E17" s="173" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F17" s="234">
         <v>44707</v>
@@ -39613,7 +39610,7 @@
       </c>
       <c r="D18" s="189"/>
       <c r="E18" s="164" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F18" s="233">
         <v>44749</v>
@@ -39710,10 +39707,10 @@
         <v>8800000</v>
       </c>
       <c r="D19" s="239" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E19" s="173" t="s">
         <v>1012</v>
-      </c>
-      <c r="E19" s="173" t="s">
-        <v>1013</v>
       </c>
       <c r="F19" s="234">
         <v>44719</v>
@@ -39811,7 +39808,7 @@
       </c>
       <c r="D20" s="189"/>
       <c r="E20" s="164" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F20" s="233">
         <v>44783</v>
@@ -39909,7 +39906,7 @@
       </c>
       <c r="D21" s="189"/>
       <c r="E21" s="164" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F21" s="233">
         <v>44781</v>
@@ -40007,7 +40004,7 @@
       </c>
       <c r="D22" s="242"/>
       <c r="E22" s="217" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F22" s="234">
         <v>44813</v>
@@ -40104,10 +40101,10 @@
         <v>12600000</v>
       </c>
       <c r="D23" s="237" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E23" s="164" t="s">
         <v>1017</v>
-      </c>
-      <c r="E23" s="164" t="s">
-        <v>1018</v>
       </c>
       <c r="F23" s="233">
         <v>44904</v>
@@ -40205,7 +40202,7 @@
       </c>
       <c r="D24" s="189"/>
       <c r="E24" s="164" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F24" s="233">
         <v>44785</v>
@@ -40303,7 +40300,7 @@
       </c>
       <c r="D25" s="208"/>
       <c r="E25" s="173" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F25" s="234">
         <v>44816</v>
@@ -40401,7 +40398,7 @@
       </c>
       <c r="D26" s="189"/>
       <c r="E26" s="164" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F26" s="233">
         <v>44837</v>
@@ -40694,10 +40691,10 @@
         <v>10000000</v>
       </c>
       <c r="D29" s="237" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E29" s="164" t="s">
         <v>1022</v>
-      </c>
-      <c r="E29" s="164" t="s">
-        <v>1023</v>
       </c>
       <c r="F29" s="233">
         <v>44908</v>
@@ -40990,10 +40987,10 @@
         <v>10600000</v>
       </c>
       <c r="D32" s="239" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E32" s="173" t="s">
         <v>1024</v>
-      </c>
-      <c r="E32" s="173" t="s">
-        <v>1025</v>
       </c>
       <c r="F32" s="234">
         <v>44911</v>
@@ -41090,7 +41087,7 @@
         <v>11000000</v>
       </c>
       <c r="D33" s="237" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E33" s="164" t="s">
         <v>17</v>
@@ -41288,7 +41285,7 @@
         <v>11000000</v>
       </c>
       <c r="D35" s="237" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E35" s="164" t="s">
         <v>17</v>
@@ -41388,10 +41385,10 @@
         <v>11700000</v>
       </c>
       <c r="D36" s="239" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E36" s="173" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F36" s="234">
         <v>44908</v>
@@ -41488,10 +41485,10 @@
         <v>12600000</v>
       </c>
       <c r="D37" s="239" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E37" s="164" t="s">
         <v>1029</v>
-      </c>
-      <c r="E37" s="164" t="s">
-        <v>1030</v>
       </c>
       <c r="F37" s="233">
         <v>44909</v>
@@ -41579,17 +41576,17 @@
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A38" s="164" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B38" s="212" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C38" s="189">
         <v>8030000</v>
       </c>
       <c r="D38" s="189"/>
       <c r="E38" s="164" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F38" s="233">
         <v>44748</v>
@@ -41785,7 +41782,7 @@
       </c>
       <c r="D40" s="189"/>
       <c r="E40" s="164" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F40" s="233">
         <v>44940</v>
@@ -41873,26 +41870,26 @@
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A41" s="164" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B41" s="241" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C41" s="208">
         <v>10700000</v>
       </c>
       <c r="D41" s="208"/>
       <c r="E41" s="173" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="F41" s="234" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G41" s="234" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H41" s="234" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="I41" s="234">
         <v>45061</v>
@@ -41977,7 +41974,7 @@
       </c>
       <c r="D42" s="189"/>
       <c r="E42" s="164" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F42" s="233">
         <v>45074</v>
@@ -42074,10 +42071,10 @@
         <v>11000000</v>
       </c>
       <c r="D43" s="239" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E43" s="173" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F43" s="234">
         <v>45095</v>
@@ -42165,7 +42162,7 @@
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A44" s="164" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B44" s="235" t="s">
         <v>565</v>
@@ -42175,7 +42172,7 @@
       </c>
       <c r="D44" s="189"/>
       <c r="E44" s="164" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F44" s="233">
         <v>45073</v>
@@ -42273,7 +42270,7 @@
       </c>
       <c r="D45" s="189"/>
       <c r="E45" s="164" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F45" s="233">
         <v>45128</v>
@@ -42371,7 +42368,7 @@
       </c>
       <c r="D46" s="189"/>
       <c r="E46" s="164" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="F46" s="233">
         <v>45163</v>
@@ -42469,7 +42466,7 @@
       </c>
       <c r="D47" s="189"/>
       <c r="E47" s="164" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F47" s="233">
         <v>45121</v>
@@ -42567,7 +42564,7 @@
       </c>
       <c r="D48" s="189"/>
       <c r="E48" s="164" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F48" s="233">
         <v>45121</v>
@@ -42665,7 +42662,7 @@
       </c>
       <c r="D49" s="208"/>
       <c r="E49" s="176" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F49" s="234">
         <v>45174</v>
@@ -42763,7 +42760,7 @@
       </c>
       <c r="D50" s="189"/>
       <c r="E50" s="164" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F50" s="233">
         <v>45161</v>
@@ -42851,17 +42848,17 @@
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A51" s="164" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B51" s="165" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C51" s="189">
         <v>8000000</v>
       </c>
       <c r="D51" s="189"/>
       <c r="E51" s="164" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F51" s="233">
         <v>45133</v>
@@ -43056,7 +43053,7 @@
         <v>6600000</v>
       </c>
       <c r="D53" s="237" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E53" s="222" t="s">
         <v>17</v>
@@ -43156,7 +43153,7 @@
         <v>6700000</v>
       </c>
       <c r="D54" s="237" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E54" s="222" t="s">
         <v>17</v>
@@ -43257,7 +43254,7 @@
       </c>
       <c r="D55" s="189"/>
       <c r="E55" s="222" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F55" s="233">
         <v>45326</v>
@@ -43932,17 +43929,17 @@
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A62" s="164" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B62" s="236" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C62" s="189">
         <v>12000000</v>
       </c>
       <c r="D62" s="189"/>
       <c r="E62" s="222" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F62" s="233">
         <v>45449</v>
@@ -44137,10 +44134,10 @@
         <v>9800000</v>
       </c>
       <c r="D64" s="237" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E64" s="222" t="s">
         <v>1048</v>
-      </c>
-      <c r="E64" s="222" t="s">
-        <v>1049</v>
       </c>
       <c r="F64" s="233">
         <v>45463</v>
@@ -44433,10 +44430,10 @@
         <v>9500000</v>
       </c>
       <c r="D67" s="237" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E67" s="222" t="s">
         <v>1050</v>
-      </c>
-      <c r="E67" s="222" t="s">
-        <v>1051</v>
       </c>
       <c r="F67" s="233">
         <v>45454</v>
@@ -45120,7 +45117,7 @@
       </c>
       <c r="D74" s="189"/>
       <c r="E74" s="222" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F74" s="233">
         <v>45633</v>
@@ -45595,7 +45592,7 @@
         <v>76</v>
       </c>
       <c r="B79" s="248" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C79" s="189">
         <v>12000000</v>
@@ -46078,14 +46075,14 @@
         <v>81</v>
       </c>
       <c r="B84" s="165" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C84" s="189">
         <v>6400000</v>
       </c>
       <c r="D84" s="189"/>
       <c r="E84" s="222" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F84" s="233">
         <v>45873</v>
@@ -46369,7 +46366,7 @@
     </row>
     <row r="87" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A87" s="164" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B87" s="165" t="s">
         <v>400</v>
@@ -46568,7 +46565,7 @@
         <v>86</v>
       </c>
       <c r="B89" s="236" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C89" s="189">
         <v>8800000</v>
@@ -46666,7 +46663,7 @@
         <v>87</v>
       </c>
       <c r="B90" s="236" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C90" s="189">
         <v>9000000</v>
@@ -46771,7 +46768,7 @@
       </c>
       <c r="D91" s="189"/>
       <c r="E91" s="222" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F91" s="233">
         <v>45977</v>
@@ -46888,94 +46885,94 @@
         <v>366</v>
       </c>
       <c r="C1" s="225" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D1" s="225" t="s">
         <v>1064</v>
       </c>
-      <c r="D1" s="225" t="s">
+      <c r="E1" s="225" t="s">
         <v>1065</v>
       </c>
-      <c r="E1" s="225" t="s">
-        <v>1066</v>
-      </c>
       <c r="F1" s="225" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G1" s="225" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H1" s="225" t="s">
         <v>1097</v>
       </c>
-      <c r="G1" s="225" t="s">
-        <v>1096</v>
-      </c>
-      <c r="H1" s="225" t="s">
+      <c r="I1" s="225" t="s">
+        <v>996</v>
+      </c>
+      <c r="J1" s="225" t="s">
+        <v>997</v>
+      </c>
+      <c r="K1" s="225" t="s">
+        <v>998</v>
+      </c>
+      <c r="L1" s="225" t="s">
+        <v>999</v>
+      </c>
+      <c r="M1" s="225" t="s">
+        <v>1000</v>
+      </c>
+      <c r="N1" s="225" t="s">
+        <v>1001</v>
+      </c>
+      <c r="O1" s="225" t="s">
+        <v>1002</v>
+      </c>
+      <c r="P1" s="225" t="s">
+        <v>1003</v>
+      </c>
+      <c r="Q1" s="225" t="s">
+        <v>1004</v>
+      </c>
+      <c r="R1" s="225" t="s">
+        <v>1053</v>
+      </c>
+      <c r="S1" s="225" t="s">
+        <v>1054</v>
+      </c>
+      <c r="T1" s="225" t="s">
+        <v>1055</v>
+      </c>
+      <c r="U1" s="225" t="s">
+        <v>1056</v>
+      </c>
+      <c r="V1" s="225" t="s">
+        <v>1057</v>
+      </c>
+      <c r="W1" s="225" t="s">
+        <v>1057</v>
+      </c>
+      <c r="X1" s="225" t="s">
+        <v>1058</v>
+      </c>
+      <c r="Y1" s="225" t="s">
+        <v>1059</v>
+      </c>
+      <c r="Z1" s="225" t="s">
+        <v>1060</v>
+      </c>
+      <c r="AA1" s="225" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AB1" s="225" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AC1" s="225" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AD1" s="225" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AE1" s="225" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AF1" s="249" t="s">
         <v>1098</v>
-      </c>
-      <c r="I1" s="225" t="s">
-        <v>997</v>
-      </c>
-      <c r="J1" s="225" t="s">
-        <v>998</v>
-      </c>
-      <c r="K1" s="225" t="s">
-        <v>999</v>
-      </c>
-      <c r="L1" s="225" t="s">
-        <v>1000</v>
-      </c>
-      <c r="M1" s="225" t="s">
-        <v>1001</v>
-      </c>
-      <c r="N1" s="225" t="s">
-        <v>1002</v>
-      </c>
-      <c r="O1" s="225" t="s">
-        <v>1003</v>
-      </c>
-      <c r="P1" s="225" t="s">
-        <v>1004</v>
-      </c>
-      <c r="Q1" s="225" t="s">
-        <v>1005</v>
-      </c>
-      <c r="R1" s="225" t="s">
-        <v>1054</v>
-      </c>
-      <c r="S1" s="225" t="s">
-        <v>1055</v>
-      </c>
-      <c r="T1" s="225" t="s">
-        <v>1056</v>
-      </c>
-      <c r="U1" s="225" t="s">
-        <v>1057</v>
-      </c>
-      <c r="V1" s="225" t="s">
-        <v>1058</v>
-      </c>
-      <c r="W1" s="225" t="s">
-        <v>1058</v>
-      </c>
-      <c r="X1" s="225" t="s">
-        <v>1059</v>
-      </c>
-      <c r="Y1" s="225" t="s">
-        <v>1060</v>
-      </c>
-      <c r="Z1" s="225" t="s">
-        <v>1061</v>
-      </c>
-      <c r="AA1" s="225" t="s">
-        <v>1100</v>
-      </c>
-      <c r="AB1" s="225" t="s">
-        <v>1101</v>
-      </c>
-      <c r="AC1" s="225" t="s">
-        <v>1102</v>
-      </c>
-      <c r="AD1" s="225" t="s">
-        <v>1103</v>
-      </c>
-      <c r="AE1" s="225" t="s">
-        <v>1104</v>
-      </c>
-      <c r="AF1" s="249" t="s">
-        <v>1099</v>
       </c>
       <c r="AG1" s="225" t="s">
         <v>53</v>
@@ -47200,19 +47197,19 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="226" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B4" s="226" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C4" s="226" t="s">
         <v>1067</v>
       </c>
-      <c r="C4" s="226" t="s">
+      <c r="D4" s="226" t="s">
         <v>1068</v>
       </c>
-      <c r="D4" s="226" t="s">
+      <c r="E4" s="250" t="s">
         <v>1069</v>
-      </c>
-      <c r="E4" s="250" t="s">
-        <v>1070</v>
       </c>
       <c r="F4" s="227">
         <v>6820000</v>
@@ -47319,7 +47316,7 @@
         <v>20460000</v>
       </c>
       <c r="AG4" s="17" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
@@ -47330,13 +47327,13 @@
         <v>190</v>
       </c>
       <c r="C5" s="226" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D5" s="226" t="s">
         <v>1071</v>
       </c>
-      <c r="D5" s="226" t="s">
+      <c r="E5" s="250" t="s">
         <v>1072</v>
-      </c>
-      <c r="E5" s="250" t="s">
-        <v>1073</v>
       </c>
       <c r="F5" s="227">
         <v>6985000</v>
@@ -47453,13 +47450,13 @@
         <v>260</v>
       </c>
       <c r="C6" s="226" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D6" s="226" t="s">
         <v>1074</v>
       </c>
-      <c r="D6" s="226" t="s">
+      <c r="E6" s="250" t="s">
         <v>1075</v>
-      </c>
-      <c r="E6" s="250" t="s">
-        <v>1076</v>
       </c>
       <c r="F6" s="227">
         <v>10736000</v>
@@ -47571,16 +47568,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="226" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C7" s="226" t="s">
         <v>1077</v>
       </c>
-      <c r="C7" s="226" t="s">
+      <c r="D7" s="226" t="s">
         <v>1078</v>
       </c>
-      <c r="D7" s="226" t="s">
+      <c r="E7" s="250" t="s">
         <v>1079</v>
-      </c>
-      <c r="E7" s="250" t="s">
-        <v>1080</v>
       </c>
       <c r="F7" s="227">
         <v>11000000</v>
@@ -47693,16 +47690,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="226" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C8" s="226" t="s">
         <v>385</v>
       </c>
       <c r="D8" s="226" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E8" s="250" t="s">
         <v>1082</v>
-      </c>
-      <c r="E8" s="250" t="s">
-        <v>1083</v>
       </c>
       <c r="F8" s="227">
         <v>11550000</v>
@@ -47815,16 +47812,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="226" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C9" s="226" t="s">
         <v>386</v>
       </c>
       <c r="D9" s="226" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E9" s="250" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F9" s="227">
         <v>11330000</v>
@@ -47833,7 +47830,7 @@
         <v>77</v>
       </c>
       <c r="H9" s="250" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="I9" s="251">
         <v>44835</v>
@@ -47934,19 +47931,19 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="226" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B10" s="226" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C10" s="226" t="s">
         <v>427</v>
       </c>
       <c r="D10" s="226" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E10" s="250" t="s">
         <v>1088</v>
-      </c>
-      <c r="E10" s="250" t="s">
-        <v>1089</v>
       </c>
       <c r="F10" s="227">
         <v>7920000.0000000009</v>
@@ -48053,7 +48050,7 @@
         <v>23760000.000000004</v>
       </c>
       <c r="AG10" s="17" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
@@ -48064,13 +48061,13 @@
         <v>316</v>
       </c>
       <c r="C11" s="226" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D11" s="226" t="s">
         <v>1090</v>
       </c>
-      <c r="D11" s="226" t="s">
+      <c r="E11" s="250" t="s">
         <v>1091</v>
-      </c>
-      <c r="E11" s="250" t="s">
-        <v>1092</v>
       </c>
       <c r="F11" s="227">
         <v>6050000</v>
@@ -48186,13 +48183,13 @@
         <v>14</v>
       </c>
       <c r="C12" s="226" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D12" s="226" t="s">
         <v>1093</v>
       </c>
-      <c r="D12" s="226" t="s">
+      <c r="E12" s="250" t="s">
         <v>1094</v>
-      </c>
-      <c r="E12" s="250" t="s">
-        <v>1095</v>
       </c>
       <c r="F12" s="227">
         <v>5500000</v>
@@ -48333,73 +48330,73 @@
         <v>366</v>
       </c>
       <c r="C1" s="225" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D1" s="225" t="s">
         <v>1105</v>
       </c>
-      <c r="D1" s="225" t="s">
-        <v>1106</v>
-      </c>
       <c r="E1" s="225" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F1" s="225" t="s">
         <v>366</v>
       </c>
       <c r="G1" s="225" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H1" s="225" t="s">
+        <v>1139</v>
+      </c>
+      <c r="I1" s="225" t="s">
         <v>1107</v>
       </c>
-      <c r="H1" s="225" t="s">
-        <v>1140</v>
-      </c>
-      <c r="I1" s="225" t="s">
+      <c r="J1" s="225" t="s">
         <v>1108</v>
       </c>
-      <c r="J1" s="225" t="s">
+      <c r="K1" s="225" t="s">
+        <v>996</v>
+      </c>
+      <c r="L1" s="225" t="s">
+        <v>997</v>
+      </c>
+      <c r="M1" s="225" t="s">
+        <v>998</v>
+      </c>
+      <c r="N1" s="225" t="s">
+        <v>999</v>
+      </c>
+      <c r="O1" s="225" t="s">
+        <v>1000</v>
+      </c>
+      <c r="P1" s="225" t="s">
+        <v>1001</v>
+      </c>
+      <c r="Q1" s="225" t="s">
+        <v>1001</v>
+      </c>
+      <c r="R1" s="225" t="s">
+        <v>1001</v>
+      </c>
+      <c r="S1" s="225" t="s">
+        <v>1002</v>
+      </c>
+      <c r="T1" s="225" t="s">
+        <v>1002</v>
+      </c>
+      <c r="U1" s="225" t="s">
+        <v>1003</v>
+      </c>
+      <c r="V1" s="225" t="s">
+        <v>1004</v>
+      </c>
+      <c r="W1" s="225" t="s">
+        <v>1053</v>
+      </c>
+      <c r="X1" s="225" t="s">
+        <v>1054</v>
+      </c>
+      <c r="Y1" s="254" t="s">
         <v>1109</v>
-      </c>
-      <c r="K1" s="225" t="s">
-        <v>997</v>
-      </c>
-      <c r="L1" s="225" t="s">
-        <v>998</v>
-      </c>
-      <c r="M1" s="225" t="s">
-        <v>999</v>
-      </c>
-      <c r="N1" s="225" t="s">
-        <v>1000</v>
-      </c>
-      <c r="O1" s="225" t="s">
-        <v>1001</v>
-      </c>
-      <c r="P1" s="225" t="s">
-        <v>1002</v>
-      </c>
-      <c r="Q1" s="225" t="s">
-        <v>1002</v>
-      </c>
-      <c r="R1" s="225" t="s">
-        <v>1002</v>
-      </c>
-      <c r="S1" s="225" t="s">
-        <v>1003</v>
-      </c>
-      <c r="T1" s="225" t="s">
-        <v>1003</v>
-      </c>
-      <c r="U1" s="225" t="s">
-        <v>1004</v>
-      </c>
-      <c r="V1" s="225" t="s">
-        <v>1005</v>
-      </c>
-      <c r="W1" s="225" t="s">
-        <v>1054</v>
-      </c>
-      <c r="X1" s="225" t="s">
-        <v>1055</v>
-      </c>
-      <c r="Y1" s="254" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
@@ -48579,16 +48576,16 @@
         <v>257</v>
       </c>
       <c r="C4" s="226" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D4" s="41" t="s">
         <v>1111</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="E4" s="255" t="s">
         <v>1112</v>
       </c>
-      <c r="E4" s="255" t="s">
-        <v>1113</v>
-      </c>
       <c r="F4" s="226" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G4" s="41"/>
       <c r="H4" s="256">
@@ -48672,10 +48669,10 @@
         <v>18</v>
       </c>
       <c r="D5" s="41" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E5" s="255" t="s">
         <v>1114</v>
-      </c>
-      <c r="E5" s="255" t="s">
-        <v>1115</v>
       </c>
       <c r="F5" s="226" t="s">
         <v>18</v>
@@ -48759,19 +48756,19 @@
         <v>436</v>
       </c>
       <c r="C6" s="226" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D6" s="41" t="s">
         <v>1116</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="E6" s="41" t="s">
         <v>1117</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="F6" s="226" t="s">
         <v>1118</v>
       </c>
-      <c r="F6" s="226" t="s">
-        <v>1119</v>
-      </c>
       <c r="G6" s="41" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H6" s="256">
         <v>7000000</v>
@@ -48850,19 +48847,19 @@
         <v>492</v>
       </c>
       <c r="C7" s="226" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D7" s="41" t="s">
         <v>1120</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="E7" s="255" t="s">
         <v>1121</v>
       </c>
-      <c r="E7" s="255" t="s">
+      <c r="F7" s="226" t="s">
         <v>1122</v>
       </c>
-      <c r="F7" s="226" t="s">
-        <v>1123</v>
-      </c>
       <c r="G7" s="41" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H7" s="256">
         <v>6500000</v>
@@ -48939,19 +48936,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="41" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C8" s="226" t="s">
         <v>1124</v>
       </c>
-      <c r="C8" s="226" t="s">
+      <c r="D8" s="41" t="s">
         <v>1125</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="E8" s="255" t="s">
         <v>1126</v>
       </c>
-      <c r="E8" s="255" t="s">
-        <v>1127</v>
-      </c>
       <c r="F8" s="226" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G8" s="41"/>
       <c r="H8" s="256">
@@ -49032,19 +49029,19 @@
         <v>254</v>
       </c>
       <c r="C9" s="226" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D9" s="41" t="s">
         <v>1128</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="E9" s="255" t="s">
         <v>1129</v>
       </c>
-      <c r="E9" s="255" t="s">
+      <c r="F9" s="226" t="s">
         <v>1130</v>
       </c>
-      <c r="F9" s="226" t="s">
-        <v>1131</v>
-      </c>
       <c r="G9" s="41" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H9" s="256">
         <v>7000000</v>
@@ -49123,17 +49120,17 @@
         <v>713</v>
       </c>
       <c r="C10" s="226" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D10" s="41" t="s">
         <v>1132</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="E10" s="255" t="s">
         <v>1133</v>
-      </c>
-      <c r="E10" s="255" t="s">
-        <v>1134</v>
       </c>
       <c r="F10" s="226"/>
       <c r="G10" s="41" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H10" s="256">
         <v>8000000</v>
@@ -49207,20 +49204,20 @@
         <v>8</v>
       </c>
       <c r="B11" s="41" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C11" s="226" t="s">
         <v>1135</v>
       </c>
-      <c r="C11" s="226" t="s">
+      <c r="D11" s="41" t="s">
         <v>1136</v>
       </c>
-      <c r="D11" s="41" t="s">
-        <v>1137</v>
-      </c>
       <c r="E11" s="255" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="F11" s="226"/>
       <c r="G11" s="41" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H11" s="256">
         <v>7400000</v>
@@ -49297,17 +49294,17 @@
         <v>423</v>
       </c>
       <c r="C12" s="226" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D12" s="41" t="s">
         <v>1138</v>
       </c>
-      <c r="D12" s="41" t="s">
-        <v>1139</v>
-      </c>
       <c r="E12" s="255" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="F12" s="226"/>
       <c r="G12" s="41" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H12" s="256">
         <v>6400000</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB9BA6E-5C95-4084-92B1-487EE61C4F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105355CE-26CD-499A-B1D2-D4A9D6F3D789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="912" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4811,7 +4811,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="279">
+  <cellXfs count="276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5545,27 +5545,6 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5593,12 +5572,6 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5608,8 +5581,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -23673,10 +23664,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A5" s="257" t="s">
+      <c r="A5" s="269" t="s">
         <v>671</v>
       </c>
-      <c r="B5" s="258"/>
+      <c r="B5" s="270"/>
       <c r="C5" s="148">
         <f>SUM(C2:C4)</f>
         <v>9</v>
@@ -25358,7 +25349,7 @@
         <v>24000000</v>
       </c>
       <c r="E3" s="76"/>
-      <c r="F3" s="259" t="s">
+      <c r="F3" s="271" t="s">
         <v>269</v>
       </c>
     </row>
@@ -25374,7 +25365,7 @@
         <v>11000000</v>
       </c>
       <c r="E4" s="76"/>
-      <c r="F4" s="260"/>
+      <c r="F4" s="272"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="75">
@@ -25388,7 +25379,7 @@
         <v>18600000</v>
       </c>
       <c r="E5" s="76"/>
-      <c r="F5" s="260"/>
+      <c r="F5" s="272"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="70">
@@ -25403,7 +25394,7 @@
       <c r="E6" s="71" t="s">
         <v>278</v>
       </c>
-      <c r="F6" s="260"/>
+      <c r="F6" s="272"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="75">
@@ -25417,7 +25408,7 @@
         <v>18000000</v>
       </c>
       <c r="E7" s="76"/>
-      <c r="F7" s="260"/>
+      <c r="F7" s="272"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="70">
@@ -25432,7 +25423,7 @@
       <c r="E8" s="71" t="s">
         <v>278</v>
       </c>
-      <c r="F8" s="260"/>
+      <c r="F8" s="272"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="70">
@@ -25447,7 +25438,7 @@
       <c r="E9" s="71" t="s">
         <v>278</v>
       </c>
-      <c r="F9" s="260"/>
+      <c r="F9" s="272"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="70">
@@ -25462,7 +25453,7 @@
       <c r="E10" s="71" t="s">
         <v>278</v>
       </c>
-      <c r="F10" s="260"/>
+      <c r="F10" s="272"/>
     </row>
     <row r="11" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="B11" s="55"/>
@@ -25474,7 +25465,7 @@
         <v>535239920</v>
       </c>
       <c r="E11" s="72"/>
-      <c r="F11" s="260"/>
+      <c r="F11" s="272"/>
       <c r="J11"/>
     </row>
     <row r="12" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
@@ -25488,7 +25479,7 @@
         <v>5786705</v>
       </c>
       <c r="E12" s="73"/>
-      <c r="F12" s="260"/>
+      <c r="F12" s="272"/>
     </row>
     <row r="13" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="B13" s="60">
@@ -25502,7 +25493,7 @@
         <v>18900000</v>
       </c>
       <c r="E13" s="74"/>
-      <c r="F13" s="261"/>
+      <c r="F13" s="273"/>
     </row>
     <row r="14" spans="2:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="B14" s="60"/>
@@ -37719,20 +37710,20 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="262" t="s">
+      <c r="L1" s="274" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="262"/>
-      <c r="N1" s="262"/>
-      <c r="O1" s="262"/>
-      <c r="P1" s="262"/>
-      <c r="Q1" s="263" t="s">
+      <c r="M1" s="274"/>
+      <c r="N1" s="274"/>
+      <c r="O1" s="274"/>
+      <c r="P1" s="274"/>
+      <c r="Q1" s="275" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="263"/>
-      <c r="S1" s="263"/>
-      <c r="T1" s="263"/>
-      <c r="U1" s="263"/>
+      <c r="R1" s="275"/>
+      <c r="S1" s="275"/>
+      <c r="T1" s="275"/>
+      <c r="U1" s="275"/>
     </row>
     <row r="2" spans="1:22" ht="48" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -49653,132 +49644,133 @@
     <col min="16" max="16" width="25.5546875" customWidth="1"/>
     <col min="17" max="17" width="22" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.77734375" customWidth="1"/>
+    <col min="19" max="19" width="22.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="264" t="s">
+      <c r="A1" s="257" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="264" t="s">
+      <c r="B1" s="257" t="s">
         <v>366</v>
       </c>
-      <c r="C1" s="265" t="s">
+      <c r="C1" s="258" t="s">
         <v>1167</v>
       </c>
-      <c r="D1" s="265" t="s">
+      <c r="D1" s="258" t="s">
         <v>1153</v>
       </c>
-      <c r="E1" s="266" t="s">
+      <c r="E1" s="259" t="s">
         <v>1154</v>
       </c>
-      <c r="F1" s="266" t="s">
+      <c r="F1" s="259" t="s">
         <v>1155</v>
       </c>
-      <c r="G1" s="267" t="s">
+      <c r="G1" s="260" t="s">
         <v>1168</v>
       </c>
-      <c r="H1" s="266" t="s">
+      <c r="H1" s="259" t="s">
         <v>1156</v>
       </c>
-      <c r="I1" s="266" t="s">
+      <c r="I1" s="259" t="s">
         <v>1157</v>
       </c>
-      <c r="J1" s="266" t="s">
+      <c r="J1" s="259" t="s">
         <v>1169</v>
       </c>
-      <c r="K1" s="264" t="s">
+      <c r="K1" s="257" t="s">
         <v>1158</v>
       </c>
-      <c r="L1" s="264" t="s">
+      <c r="L1" s="257" t="s">
         <v>1159</v>
       </c>
-      <c r="M1" s="264" t="s">
+      <c r="M1" s="257" t="s">
         <v>1160</v>
       </c>
-      <c r="N1" s="264" t="s">
+      <c r="N1" s="257" t="s">
         <v>1161</v>
       </c>
-      <c r="O1" s="264" t="s">
+      <c r="O1" s="257" t="s">
         <v>1162</v>
       </c>
-      <c r="P1" s="264" t="s">
+      <c r="P1" s="257" t="s">
         <v>1163</v>
       </c>
-      <c r="Q1" s="268" t="s">
+      <c r="Q1" s="261" t="s">
         <v>1170</v>
       </c>
-      <c r="R1" s="264" t="s">
+      <c r="R1" s="257" t="s">
         <v>1164</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="264"/>
-      <c r="B2" s="264" t="s">
+      <c r="A2" s="257"/>
+      <c r="B2" s="257" t="s">
         <v>1165</v>
       </c>
-      <c r="C2" s="265">
-        <f>SUBTOTAL(9,C4:C197)</f>
+      <c r="C2" s="258">
+        <f t="shared" ref="C2:Q2" si="0">SUBTOTAL(9,C4:C197)</f>
         <v>8690100143.0370846</v>
       </c>
-      <c r="D2" s="265">
-        <f>SUBTOTAL(9,D4:D197)</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="265">
-        <f>SUBTOTAL(9,E4:E197)</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="265">
-        <f>SUBTOTAL(9,F4:F197)</f>
-        <v>54458027.893325217</v>
-      </c>
-      <c r="G2" s="265">
-        <f>SUBTOTAL(9,G4:G197)</f>
-        <v>8744558170.9304123</v>
-      </c>
-      <c r="H2" s="265">
-        <f>SUBTOTAL(9,H4:H197)</f>
+      <c r="D2" s="258">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E2" s="258">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F2" s="258">
+        <f t="shared" si="0"/>
+        <v>65175751.072778143</v>
+      </c>
+      <c r="G2" s="258">
+        <f t="shared" si="0"/>
+        <v>8755275894.1098633</v>
+      </c>
+      <c r="H2" s="258">
+        <f t="shared" si="0"/>
         <v>383116909.09090906</v>
       </c>
-      <c r="I2" s="265">
-        <f>SUBTOTAL(9,I4:I197)</f>
+      <c r="I2" s="258">
+        <f t="shared" si="0"/>
         <v>667080000</v>
       </c>
-      <c r="J2" s="265">
-        <f>SUBTOTAL(9,J4:J197)</f>
-        <v>9794755080.0213165</v>
-      </c>
-      <c r="K2" s="265">
-        <f>SUBTOTAL(9,K4:K197)</f>
-        <v>421750000</v>
-      </c>
-      <c r="L2" s="265">
-        <f>SUBTOTAL(9,L4:L197)</f>
+      <c r="J2" s="258">
+        <f t="shared" si="0"/>
+        <v>9805472803.2007713</v>
+      </c>
+      <c r="K2" s="258">
+        <f t="shared" si="0"/>
+        <v>426075000</v>
+      </c>
+      <c r="L2" s="258">
+        <f t="shared" si="0"/>
         <v>704380000</v>
       </c>
-      <c r="M2" s="265">
-        <f>SUBTOTAL(9,M4:M197)</f>
+      <c r="M2" s="258">
+        <f t="shared" si="0"/>
         <v>70238100</v>
       </c>
-      <c r="N2" s="265">
-        <f>SUBTOTAL(9,N4:N197)</f>
+      <c r="N2" s="258">
+        <f t="shared" si="0"/>
         <v>74120000</v>
       </c>
-      <c r="O2" s="265">
-        <f>SUBTOTAL(9,O4:O197)</f>
+      <c r="O2" s="258">
+        <f t="shared" si="0"/>
         <v>848738100</v>
       </c>
-      <c r="P2" s="265">
-        <f>SUBTOTAL(9,P4:P197)</f>
+      <c r="P2" s="258">
+        <f t="shared" si="0"/>
         <v>771580090.909091</v>
       </c>
-      <c r="Q2" s="265">
-        <f>SUBTOTAL(9,Q4:Q197)</f>
-        <v>349830090.909091</v>
-      </c>
-      <c r="R2" s="269">
+      <c r="Q2" s="258">
+        <f t="shared" si="0"/>
+        <v>345505090.909091</v>
+      </c>
+      <c r="R2" s="262">
         <f>J2/Q2</f>
-        <v>27.998606565170068</v>
+        <v>28.380110919351921</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -49839,40 +49831,40 @@
       <c r="A4" s="120">
         <v>1</v>
       </c>
-      <c r="B4" s="270" t="s">
+      <c r="B4" s="263" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="271">
+      <c r="C4" s="264">
         <v>131973797.76886031</v>
       </c>
-      <c r="D4" s="271">
+      <c r="D4" s="264">
         <v>0</v>
       </c>
       <c r="E4" s="156">
         <v>0</v>
       </c>
       <c r="F4" s="156">
-        <f t="shared" ref="F4" si="0">(C4*12%+(C4/2)*12%)/24</f>
+        <f t="shared" ref="F4:F67" si="1">(C4*12%+(C4/2)*12%)/24</f>
         <v>989803.48326645233</v>
       </c>
       <c r="G4" s="156">
-        <f t="shared" ref="G4:G10" si="1">SUM(C4:F4)</f>
+        <f t="shared" ref="G4:G67" si="2">SUM(C4:F4)</f>
         <v>132963601.25212677</v>
       </c>
       <c r="H4" s="156">
-        <f t="shared" ref="H4:H5" si="2">M4*6/1.1</f>
+        <f t="shared" ref="H4:H67" si="3">M4*6/1.1</f>
         <v>26963999.999999996</v>
       </c>
       <c r="I4" s="156">
-        <f t="shared" ref="I4:I67" si="3">N4*9</f>
+        <f t="shared" ref="I4:I67" si="4">N4*9</f>
         <v>0</v>
       </c>
       <c r="J4" s="156">
-        <f t="shared" ref="J4:J67" si="4">G4+H4+I4</f>
+        <f t="shared" ref="J4:J67" si="5">G4+H4+I4</f>
         <v>159927601.25212675</v>
       </c>
       <c r="K4" s="156">
-        <v>5000000</v>
+        <v>7000000</v>
       </c>
       <c r="L4" s="156">
         <v>7120000</v>
@@ -49893,49 +49885,49 @@
       </c>
       <c r="Q4" s="156">
         <f>P4-K4</f>
-        <v>5966727.2727272715</v>
+        <v>3966727.2727272715</v>
       </c>
       <c r="R4" s="156">
-        <f t="shared" ref="R4:R67" si="5">J4/Q4</f>
-        <v>26.803236337468302</v>
+        <f t="shared" ref="R4:R67" si="6">J4/Q4</f>
+        <v>40.317266667584789</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="120">
         <v>2</v>
       </c>
-      <c r="B5" s="270" t="s">
+      <c r="B5" s="263" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="271">
+      <c r="C5" s="264">
         <f>103604978.276535+70000000</f>
         <v>173604978.276535</v>
       </c>
-      <c r="D5" s="271">
+      <c r="D5" s="264">
         <v>0</v>
       </c>
       <c r="E5" s="156">
         <v>0</v>
       </c>
       <c r="F5" s="156">
-        <f>(C5*12%+(C5/2)*12%)/28</f>
-        <v>1116032.0032062964</v>
+        <f t="shared" si="1"/>
+        <v>1302037.3370740125</v>
       </c>
       <c r="G5" s="156">
-        <f t="shared" si="1"/>
-        <v>174721010.27974129</v>
+        <f t="shared" si="2"/>
+        <v>174907015.61360902</v>
       </c>
       <c r="H5" s="156">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>29999999.999999996</v>
       </c>
       <c r="I5" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>49500000</v>
       </c>
       <c r="J5" s="156">
-        <f t="shared" si="4"/>
-        <v>254221010.27974129</v>
+        <f t="shared" si="5"/>
+        <v>254407015.61360902</v>
       </c>
       <c r="K5" s="156">
         <v>6500000</v>
@@ -49951,60 +49943,60 @@
         <v>5500000</v>
       </c>
       <c r="O5" s="156">
-        <f t="shared" ref="O5:O42" si="6">SUM(L5:N5)</f>
+        <f t="shared" ref="O5:O68" si="7">SUM(L5:N5)</f>
         <v>16810000</v>
       </c>
       <c r="P5" s="156">
-        <f t="shared" ref="P5:P68" si="7">O5/1.1</f>
+        <f t="shared" ref="P5:P68" si="8">O5/1.1</f>
         <v>15281818.18181818</v>
       </c>
       <c r="Q5" s="156">
-        <f t="shared" ref="Q5:Q68" si="8">P5-K5</f>
+        <f t="shared" ref="Q5:Q68" si="9">P5-K5</f>
         <v>8781818.1818181798</v>
       </c>
       <c r="R5" s="156">
-        <f t="shared" si="5"/>
-        <v>28.948562247175516</v>
+        <f t="shared" si="6"/>
+        <v>28.969742978775361</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="120">
         <v>3</v>
       </c>
-      <c r="B6" s="270" t="s">
+      <c r="B6" s="263" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="271">
+      <c r="C6" s="264">
         <v>95327892.000000015</v>
       </c>
-      <c r="D6" s="272">
+      <c r="D6" s="265">
         <v>0</v>
       </c>
       <c r="E6" s="156">
         <v>0</v>
       </c>
-      <c r="F6" s="273">
-        <f>(C6*12%+(C6/2)*12%)/38</f>
-        <v>451553.17263157899</v>
-      </c>
-      <c r="G6" s="273">
+      <c r="F6" s="156">
         <f t="shared" si="1"/>
-        <v>95779445.172631592</v>
-      </c>
-      <c r="H6" s="273">
-        <f t="shared" ref="H6:H10" si="9">M6*6</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="273">
+        <v>714959.19000000006</v>
+      </c>
+      <c r="G6" s="156">
+        <f t="shared" si="2"/>
+        <v>96042851.190000013</v>
+      </c>
+      <c r="H6" s="156">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J6" s="273">
+      <c r="I6" s="156">
         <f t="shared" si="4"/>
-        <v>95779445.172631592</v>
+        <v>0</v>
+      </c>
+      <c r="J6" s="156">
+        <f t="shared" si="5"/>
+        <v>96042851.190000013</v>
       </c>
       <c r="K6" s="156">
-        <v>5250000</v>
+        <v>5875000</v>
       </c>
       <c r="L6" s="156">
         <v>8300000</v>
@@ -50015,21 +50007,21 @@
       <c r="N6" s="156">
         <v>0</v>
       </c>
-      <c r="O6" s="273">
+      <c r="O6" s="156">
+        <f t="shared" si="7"/>
+        <v>8300000</v>
+      </c>
+      <c r="P6" s="156">
+        <f t="shared" si="8"/>
+        <v>7545454.5454545449</v>
+      </c>
+      <c r="Q6" s="156">
+        <f t="shared" si="9"/>
+        <v>1670454.5454545449</v>
+      </c>
+      <c r="R6" s="156">
         <f t="shared" si="6"/>
-        <v>8300000</v>
-      </c>
-      <c r="P6" s="273">
-        <f>O6/1.1</f>
-        <v>7545454.5454545449</v>
-      </c>
-      <c r="Q6" s="273">
-        <f t="shared" si="8"/>
-        <v>2295454.5454545449</v>
-      </c>
-      <c r="R6" s="274">
-        <f t="shared" si="5"/>
-        <v>41.725698887087042</v>
+        <v>57.495040168163293</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="24" x14ac:dyDescent="0.3">
@@ -50039,34 +50031,34 @@
       <c r="B7" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="C7" s="271">
+      <c r="C7" s="264">
         <v>37000000</v>
       </c>
-      <c r="D7" s="271">
+      <c r="D7" s="264">
         <v>0</v>
       </c>
       <c r="E7" s="156">
         <v>0</v>
       </c>
       <c r="F7" s="156">
-        <f>(C7*12%+(C7/2)*12%)/23</f>
-        <v>289565.21739130432</v>
+        <f t="shared" si="1"/>
+        <v>277500</v>
       </c>
       <c r="G7" s="156">
-        <f t="shared" si="1"/>
-        <v>37289565.217391305</v>
+        <f t="shared" si="2"/>
+        <v>37277500</v>
       </c>
       <c r="H7" s="156">
-        <f>M7*9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I7" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J7" s="156">
-        <f t="shared" si="4"/>
-        <v>37289565.217391305</v>
+        <f t="shared" si="5"/>
+        <v>37277500</v>
       </c>
       <c r="K7" s="156">
         <v>4000000</v>
@@ -50081,122 +50073,122 @@
         <v>0</v>
       </c>
       <c r="O7" s="156">
+        <f t="shared" si="7"/>
+        <v>6300000</v>
+      </c>
+      <c r="P7" s="156">
+        <f t="shared" si="8"/>
+        <v>5727272.7272727266</v>
+      </c>
+      <c r="Q7" s="156">
+        <f t="shared" si="9"/>
+        <v>1727272.7272727266</v>
+      </c>
+      <c r="R7" s="156">
         <f t="shared" si="6"/>
-        <v>6300000</v>
-      </c>
-      <c r="P7" s="156">
-        <f t="shared" si="7"/>
-        <v>5727272.7272727266</v>
-      </c>
-      <c r="Q7" s="156">
-        <f t="shared" si="8"/>
-        <v>1727272.7272727266</v>
-      </c>
-      <c r="R7" s="156">
-        <f t="shared" si="5"/>
-        <v>21.588695652173922</v>
+        <v>21.581710526315799</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="120">
         <v>5</v>
       </c>
-      <c r="B8" s="270" t="s">
+      <c r="B8" s="263" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="271">
+      <c r="C8" s="264">
         <v>152151951.134</v>
       </c>
-      <c r="D8" s="272">
-        <v>0</v>
-      </c>
-      <c r="E8" s="271">
-        <v>0</v>
-      </c>
-      <c r="F8" s="272">
-        <f>(C8*12%+(C8/2)*12%)/39</f>
-        <v>702239.7744646155</v>
-      </c>
-      <c r="G8" s="272">
+      <c r="D8" s="265">
+        <v>0</v>
+      </c>
+      <c r="E8" s="264">
+        <v>0</v>
+      </c>
+      <c r="F8" s="156">
         <f t="shared" si="1"/>
-        <v>152854190.90846461</v>
-      </c>
-      <c r="H8" s="272">
+        <v>1141139.633505</v>
+      </c>
+      <c r="G8" s="156">
+        <f t="shared" si="2"/>
+        <v>153293090.76750499</v>
+      </c>
+      <c r="H8" s="156">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="156">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="156">
+        <f t="shared" si="5"/>
+        <v>153293090.76750499</v>
+      </c>
+      <c r="K8" s="156">
+        <v>4750000</v>
+      </c>
+      <c r="L8" s="264">
+        <v>9600000</v>
+      </c>
+      <c r="M8" s="264">
+        <v>0</v>
+      </c>
+      <c r="N8" s="264">
+        <v>0</v>
+      </c>
+      <c r="O8" s="156">
+        <f t="shared" si="7"/>
+        <v>9600000</v>
+      </c>
+      <c r="P8" s="156">
+        <f t="shared" si="8"/>
+        <v>8727272.7272727266</v>
+      </c>
+      <c r="Q8" s="156">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="272">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="272">
-        <f t="shared" si="4"/>
-        <v>152854190.90846461</v>
-      </c>
-      <c r="K8" s="271">
-        <v>4750000</v>
-      </c>
-      <c r="L8" s="271">
-        <v>9600000</v>
-      </c>
-      <c r="M8" s="271">
-        <v>0</v>
-      </c>
-      <c r="N8" s="271">
-        <v>0</v>
-      </c>
-      <c r="O8" s="272">
+        <v>3977272.7272727266</v>
+      </c>
+      <c r="R8" s="156">
         <f t="shared" si="6"/>
-        <v>9600000</v>
-      </c>
-      <c r="P8" s="272">
-        <f t="shared" si="7"/>
-        <v>8727272.7272727266</v>
-      </c>
-      <c r="Q8" s="272">
-        <f t="shared" si="8"/>
-        <v>3977272.7272727266</v>
-      </c>
-      <c r="R8" s="272">
-        <f t="shared" si="5"/>
-        <v>38.431910856985397</v>
+        <v>38.542262821544121</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="120">
         <v>6</v>
       </c>
-      <c r="B9" s="270" t="s">
+      <c r="B9" s="263" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="271">
+      <c r="C9" s="264">
         <v>95700000.000000015</v>
       </c>
-      <c r="D9" s="271">
+      <c r="D9" s="264">
         <v>0</v>
       </c>
       <c r="E9" s="156">
         <v>0</v>
       </c>
       <c r="F9" s="156">
-        <f>(C9*12%+(C9/2)*12%)/31</f>
-        <v>555677.41935483878</v>
+        <f t="shared" si="1"/>
+        <v>717750.00000000012</v>
       </c>
       <c r="G9" s="156">
-        <f t="shared" si="1"/>
-        <v>96255677.419354856</v>
+        <f t="shared" si="2"/>
+        <v>96417750.000000015</v>
       </c>
       <c r="H9" s="156">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I9" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J9" s="156">
-        <f t="shared" si="4"/>
-        <v>96255677.419354856</v>
+        <f t="shared" si="5"/>
+        <v>96417750.000000015</v>
       </c>
       <c r="K9" s="156">
         <v>7000000</v>
@@ -50211,57 +50203,57 @@
         <v>0</v>
       </c>
       <c r="O9" s="156">
+        <f t="shared" si="7"/>
+        <v>10900000</v>
+      </c>
+      <c r="P9" s="156">
+        <f t="shared" si="8"/>
+        <v>9909090.9090909082</v>
+      </c>
+      <c r="Q9" s="156">
+        <f t="shared" si="9"/>
+        <v>2909090.9090909082</v>
+      </c>
+      <c r="R9" s="156">
         <f t="shared" si="6"/>
-        <v>10900000</v>
-      </c>
-      <c r="P9" s="156">
-        <f t="shared" si="7"/>
-        <v>9909090.9090909082</v>
-      </c>
-      <c r="Q9" s="156">
-        <f t="shared" si="8"/>
-        <v>2909090.9090909082</v>
-      </c>
-      <c r="R9" s="156">
-        <f t="shared" si="5"/>
-        <v>33.087889112903241</v>
+        <v>33.143601562500017</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="120">
         <v>7</v>
       </c>
-      <c r="B10" s="270" t="s">
+      <c r="B10" s="263" t="s">
         <v>257</v>
       </c>
-      <c r="C10" s="271">
+      <c r="C10" s="264">
         <v>208947674.09999999</v>
       </c>
-      <c r="D10" s="271">
+      <c r="D10" s="264">
         <v>0</v>
       </c>
       <c r="E10" s="156">
         <v>0</v>
       </c>
       <c r="F10" s="156">
-        <f t="shared" ref="F10" si="10">(C10*12%+(C10/2)*12%)/54</f>
-        <v>696492.24699999997</v>
+        <f t="shared" si="1"/>
+        <v>1567107.5557500001</v>
       </c>
       <c r="G10" s="156">
-        <f t="shared" si="1"/>
-        <v>209644166.347</v>
+        <f t="shared" si="2"/>
+        <v>210514781.65575001</v>
       </c>
       <c r="H10" s="156">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I10" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>58500000</v>
       </c>
       <c r="J10" s="156">
-        <f t="shared" si="4"/>
-        <v>268144166.347</v>
+        <f t="shared" si="5"/>
+        <v>269014781.65575004</v>
       </c>
       <c r="K10" s="156">
         <v>6000000</v>
@@ -50277,57 +50269,57 @@
         <v>6500000</v>
       </c>
       <c r="O10" s="156">
+        <f t="shared" si="7"/>
+        <v>15140000</v>
+      </c>
+      <c r="P10" s="156">
+        <f t="shared" si="8"/>
+        <v>13763636.363636363</v>
+      </c>
+      <c r="Q10" s="156">
+        <f t="shared" si="9"/>
+        <v>7763636.3636363633</v>
+      </c>
+      <c r="R10" s="156">
         <f t="shared" si="6"/>
-        <v>15140000</v>
-      </c>
-      <c r="P10" s="156">
-        <f t="shared" si="7"/>
-        <v>13763636.363636363</v>
-      </c>
-      <c r="Q10" s="156">
-        <f t="shared" si="8"/>
-        <v>7763636.3636363633</v>
-      </c>
-      <c r="R10" s="156">
-        <f t="shared" si="5"/>
-        <v>34.538475758981264</v>
+        <v>34.650615904136423</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="120">
         <v>8</v>
       </c>
-      <c r="B11" s="270" t="s">
+      <c r="B11" s="263" t="s">
         <v>260</v>
       </c>
-      <c r="C11" s="271">
+      <c r="C11" s="264">
         <v>106595511.00000001</v>
       </c>
-      <c r="D11" s="271">
+      <c r="D11" s="264">
         <v>0</v>
       </c>
       <c r="E11" s="156">
         <v>0</v>
       </c>
       <c r="F11" s="156">
-        <f>(C11*12%+(C11/2)*12%)/54</f>
-        <v>355318.37000000005</v>
+        <f t="shared" si="1"/>
+        <v>799466.33250000014</v>
       </c>
       <c r="G11" s="156">
-        <f t="shared" ref="G11:G42" si="11">SUM(C11:F11)</f>
-        <v>106950829.37000002</v>
+        <f t="shared" si="2"/>
+        <v>107394977.33250001</v>
       </c>
       <c r="H11" s="156">
-        <f t="shared" ref="H11:H13" si="12">M11*6/1.1</f>
+        <f t="shared" si="3"/>
         <v>61090909.090909086</v>
       </c>
       <c r="I11" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J11" s="156">
-        <f t="shared" si="4"/>
-        <v>168041738.4609091</v>
+        <f t="shared" si="5"/>
+        <v>168485886.4234091</v>
       </c>
       <c r="K11" s="156">
         <v>7000000</v>
@@ -50343,60 +50335,60 @@
         <v>0</v>
       </c>
       <c r="O11" s="156">
+        <f t="shared" si="7"/>
+        <v>17120000</v>
+      </c>
+      <c r="P11" s="156">
+        <f t="shared" si="8"/>
+        <v>15563636.363636363</v>
+      </c>
+      <c r="Q11" s="156">
+        <f t="shared" si="9"/>
+        <v>8563636.3636363633</v>
+      </c>
+      <c r="R11" s="156">
         <f t="shared" si="6"/>
-        <v>17120000</v>
-      </c>
-      <c r="P11" s="156">
-        <f t="shared" si="7"/>
-        <v>15563636.363636363</v>
-      </c>
-      <c r="Q11" s="156">
-        <f t="shared" si="8"/>
-        <v>8563636.3636363633</v>
-      </c>
-      <c r="R11" s="156">
-        <f t="shared" si="5"/>
-        <v>19.622708312845013</v>
+        <v>19.674572724601912</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="120">
         <v>9</v>
       </c>
-      <c r="B12" s="270" t="s">
+      <c r="B12" s="263" t="s">
         <v>190</v>
       </c>
-      <c r="C12" s="271">
+      <c r="C12" s="264">
         <v>182384107.40000001</v>
       </c>
-      <c r="D12" s="271">
+      <c r="D12" s="264">
         <v>0</v>
       </c>
       <c r="E12" s="156">
         <v>0</v>
       </c>
       <c r="F12" s="156">
-        <f>(C12*12%+(C12/2)*12%)/54</f>
-        <v>607947.02466666675</v>
+        <f t="shared" si="1"/>
+        <v>1367880.8055</v>
       </c>
       <c r="G12" s="156">
-        <f t="shared" si="11"/>
-        <v>182992054.42466667</v>
+        <f t="shared" si="2"/>
+        <v>183751988.20550001</v>
       </c>
       <c r="H12" s="156">
-        <f t="shared" si="12"/>
+        <f t="shared" si="3"/>
         <v>38100000</v>
       </c>
       <c r="I12" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J12" s="156">
-        <f t="shared" si="4"/>
-        <v>221092054.42466667</v>
+        <f t="shared" si="5"/>
+        <v>221851988.20550001</v>
       </c>
       <c r="K12" s="156">
-        <v>5500000</v>
+        <v>6600000</v>
       </c>
       <c r="L12" s="156">
         <f>9900000*80%</f>
@@ -50409,123 +50401,123 @@
         <v>0</v>
       </c>
       <c r="O12" s="156">
+        <f t="shared" si="7"/>
+        <v>14905000</v>
+      </c>
+      <c r="P12" s="156">
+        <f t="shared" si="8"/>
+        <v>13549999.999999998</v>
+      </c>
+      <c r="Q12" s="156">
+        <f t="shared" si="9"/>
+        <v>6949999.9999999981</v>
+      </c>
+      <c r="R12" s="156">
         <f t="shared" si="6"/>
-        <v>14905000</v>
-      </c>
-      <c r="P12" s="156">
-        <f t="shared" si="7"/>
-        <v>13549999.999999998</v>
-      </c>
-      <c r="Q12" s="156">
-        <f t="shared" si="8"/>
-        <v>8049999.9999999981</v>
-      </c>
-      <c r="R12" s="156">
-        <f t="shared" si="5"/>
-        <v>27.464851481325059</v>
+        <v>31.921149382086341</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="120">
         <v>10</v>
       </c>
-      <c r="B13" s="270" t="s">
+      <c r="B13" s="263" t="s">
         <v>423</v>
       </c>
-      <c r="C13" s="271">
+      <c r="C13" s="264">
         <v>201637909.856765</v>
       </c>
-      <c r="D13" s="271">
-        <v>0</v>
-      </c>
-      <c r="E13" s="271">
-        <v>0</v>
-      </c>
-      <c r="F13" s="271">
-        <f>(C13*12%+(C13/2)*12%)/54</f>
-        <v>672126.36618921673</v>
-      </c>
-      <c r="G13" s="271">
-        <f t="shared" si="11"/>
-        <v>202310036.22295421</v>
+      <c r="D13" s="264">
+        <v>0</v>
+      </c>
+      <c r="E13" s="264">
+        <v>0</v>
+      </c>
+      <c r="F13" s="156">
+        <f t="shared" si="1"/>
+        <v>1512284.3239257375</v>
+      </c>
+      <c r="G13" s="156">
+        <f t="shared" si="2"/>
+        <v>203150194.18069074</v>
       </c>
       <c r="H13" s="156">
-        <f t="shared" si="12"/>
+        <f t="shared" si="3"/>
         <v>25541999.999999996</v>
       </c>
-      <c r="I13" s="271">
-        <f t="shared" si="3"/>
+      <c r="I13" s="156">
+        <f t="shared" si="4"/>
         <v>57600000</v>
       </c>
-      <c r="J13" s="271">
-        <f t="shared" si="4"/>
-        <v>285452036.22295421</v>
-      </c>
-      <c r="K13" s="271">
+      <c r="J13" s="156">
+        <f t="shared" si="5"/>
+        <v>286292194.18069077</v>
+      </c>
+      <c r="K13" s="156">
         <v>6000000</v>
       </c>
-      <c r="L13" s="271">
+      <c r="L13" s="264">
         <f>11500000*0.7</f>
         <v>8049999.9999999991</v>
       </c>
-      <c r="M13" s="271">
+      <c r="M13" s="264">
         <v>4682700</v>
       </c>
-      <c r="N13" s="271">
+      <c r="N13" s="264">
         <v>6400000</v>
       </c>
-      <c r="O13" s="271">
-        <f>SUM(L13:N13)</f>
+      <c r="O13" s="156">
+        <f t="shared" si="7"/>
         <v>19132700</v>
       </c>
-      <c r="P13" s="271">
-        <f t="shared" si="7"/>
+      <c r="P13" s="156">
+        <f t="shared" si="8"/>
         <v>17393363.636363637</v>
       </c>
-      <c r="Q13" s="271">
-        <f>P13-K13</f>
+      <c r="Q13" s="156">
+        <f t="shared" si="9"/>
         <v>11393363.636363637</v>
       </c>
-      <c r="R13" s="271">
-        <f t="shared" si="5"/>
-        <v>25.054237302835752</v>
+      <c r="R13" s="156">
+        <f t="shared" si="6"/>
+        <v>25.12797829667668</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="120">
         <v>11</v>
       </c>
-      <c r="B14" s="270" t="s">
+      <c r="B14" s="263" t="s">
         <v>156</v>
       </c>
-      <c r="C14" s="271">
+      <c r="C14" s="264">
         <v>142238995.09999999</v>
       </c>
-      <c r="D14" s="271">
+      <c r="D14" s="264">
         <v>0</v>
       </c>
       <c r="E14" s="156">
         <v>0</v>
       </c>
       <c r="F14" s="156">
-        <f>(C14*12%+(C14/2)*12%)/54</f>
-        <v>474129.98366666667</v>
+        <f t="shared" si="1"/>
+        <v>1066792.46325</v>
       </c>
       <c r="G14" s="156">
-        <f t="shared" si="11"/>
-        <v>142713125.08366665</v>
+        <f t="shared" si="2"/>
+        <v>143305787.56325001</v>
       </c>
       <c r="H14" s="156">
-        <f t="shared" ref="H14:H77" si="13">M14*6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I14" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J14" s="156">
-        <f t="shared" si="4"/>
-        <v>142713125.08366665</v>
+        <f t="shared" si="5"/>
+        <v>143305787.56325001</v>
       </c>
       <c r="K14" s="156">
         <v>6500000</v>
@@ -50540,57 +50532,57 @@
         <v>0</v>
       </c>
       <c r="O14" s="156">
+        <f t="shared" si="7"/>
+        <v>11500000</v>
+      </c>
+      <c r="P14" s="156">
+        <f t="shared" si="8"/>
+        <v>10454545.454545453</v>
+      </c>
+      <c r="Q14" s="156">
+        <f t="shared" si="9"/>
+        <v>3954545.4545454532</v>
+      </c>
+      <c r="R14" s="156">
         <f t="shared" si="6"/>
-        <v>11500000</v>
-      </c>
-      <c r="P14" s="156">
-        <f t="shared" si="7"/>
-        <v>10454545.454545453</v>
-      </c>
-      <c r="Q14" s="156">
-        <f t="shared" si="8"/>
-        <v>3954545.4545454532</v>
-      </c>
-      <c r="R14" s="156">
-        <f t="shared" si="5"/>
-        <v>36.088376457938708</v>
+        <v>36.238245130936797</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="120">
         <v>12</v>
       </c>
-      <c r="B15" s="270" t="s">
+      <c r="B15" s="263" t="s">
         <v>185</v>
       </c>
-      <c r="C15" s="271">
+      <c r="C15" s="264">
         <v>171960657</v>
       </c>
-      <c r="D15" s="271">
+      <c r="D15" s="264">
         <v>0</v>
       </c>
       <c r="E15" s="156">
         <v>0</v>
       </c>
       <c r="F15" s="156">
-        <f>(C15*12%+(C15/2)*12%)/54</f>
-        <v>573202.18999999994</v>
+        <f t="shared" si="1"/>
+        <v>1289704.9275</v>
       </c>
       <c r="G15" s="156">
-        <f t="shared" si="11"/>
-        <v>172533859.19</v>
+        <f t="shared" si="2"/>
+        <v>173250361.92750001</v>
       </c>
       <c r="H15" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I15" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J15" s="156">
-        <f t="shared" si="4"/>
-        <v>172533859.19</v>
+        <f t="shared" si="5"/>
+        <v>173250361.92750001</v>
       </c>
       <c r="K15" s="156">
         <v>7000000</v>
@@ -50606,57 +50598,57 @@
         <v>0</v>
       </c>
       <c r="O15" s="156">
+        <f t="shared" si="7"/>
+        <v>11500000</v>
+      </c>
+      <c r="P15" s="156">
+        <f t="shared" si="8"/>
+        <v>10454545.454545453</v>
+      </c>
+      <c r="Q15" s="156">
+        <f t="shared" si="9"/>
+        <v>3454545.4545454532</v>
+      </c>
+      <c r="R15" s="156">
         <f t="shared" si="6"/>
-        <v>11500000</v>
-      </c>
-      <c r="P15" s="156">
-        <f t="shared" si="7"/>
-        <v>10454545.454545453</v>
-      </c>
-      <c r="Q15" s="156">
-        <f t="shared" si="8"/>
-        <v>3454545.4545454532</v>
-      </c>
-      <c r="R15" s="156">
-        <f t="shared" si="5"/>
-        <v>49.944011870789495</v>
+        <v>50.151420557960549</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="120">
         <v>13</v>
       </c>
-      <c r="B16" s="270" t="s">
+      <c r="B16" s="263" t="s">
         <v>229</v>
       </c>
-      <c r="C16" s="271">
+      <c r="C16" s="264">
         <v>143378936</v>
       </c>
-      <c r="D16" s="271">
+      <c r="D16" s="264">
         <v>0</v>
       </c>
       <c r="E16" s="156">
         <v>0</v>
       </c>
       <c r="F16" s="156">
-        <f>(C16*12%+(C16/2)*12%)/28</f>
-        <v>921721.73142857139</v>
+        <f t="shared" si="1"/>
+        <v>1075342.02</v>
       </c>
       <c r="G16" s="156">
-        <f t="shared" si="11"/>
-        <v>144300657.73142856</v>
+        <f t="shared" si="2"/>
+        <v>144454278.02000001</v>
       </c>
       <c r="H16" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I16" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J16" s="156">
-        <f t="shared" si="4"/>
-        <v>144300657.73142856</v>
+        <f t="shared" si="5"/>
+        <v>144454278.02000001</v>
       </c>
       <c r="K16" s="156">
         <v>7000000</v>
@@ -50671,20 +50663,20 @@
         <v>0</v>
       </c>
       <c r="O16" s="156">
+        <f t="shared" si="7"/>
+        <v>11700000</v>
+      </c>
+      <c r="P16" s="156">
+        <f t="shared" si="8"/>
+        <v>10636363.636363635</v>
+      </c>
+      <c r="Q16" s="156">
+        <f t="shared" si="9"/>
+        <v>3636363.6363636348</v>
+      </c>
+      <c r="R16" s="156">
         <f t="shared" si="6"/>
-        <v>11700000</v>
-      </c>
-      <c r="P16" s="156">
-        <f t="shared" si="7"/>
-        <v>10636363.636363635</v>
-      </c>
-      <c r="Q16" s="156">
-        <f t="shared" si="8"/>
-        <v>3636363.6363636348</v>
-      </c>
-      <c r="R16" s="156">
-        <f t="shared" si="5"/>
-        <v>39.682680876142875</v>
+        <v>39.724926455500018</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -50694,33 +50686,33 @@
       <c r="B17" s="50" t="s">
         <v>290</v>
       </c>
-      <c r="C17" s="271">
+      <c r="C17" s="264">
         <v>160823909.40000001</v>
       </c>
-      <c r="D17" s="271">
+      <c r="D17" s="264">
         <v>0</v>
       </c>
       <c r="E17" s="156">
         <v>0</v>
       </c>
       <c r="F17" s="156">
-        <f t="shared" ref="F17:F72" si="14">(C17*12%+(C17/2)*12%)/24</f>
+        <f t="shared" si="1"/>
         <v>1206179.3204999999</v>
       </c>
       <c r="G17" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>162030088.72049999</v>
       </c>
       <c r="H17" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I17" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J17" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>162030088.72049999</v>
       </c>
       <c r="K17" s="156">
@@ -50736,19 +50728,19 @@
         <v>0</v>
       </c>
       <c r="O17" s="156">
+        <f t="shared" si="7"/>
+        <v>8800000</v>
+      </c>
+      <c r="P17" s="156">
+        <f t="shared" si="8"/>
+        <v>7999999.9999999991</v>
+      </c>
+      <c r="Q17" s="156">
+        <f t="shared" si="9"/>
+        <v>2699999.9999999991</v>
+      </c>
+      <c r="R17" s="156">
         <f t="shared" si="6"/>
-        <v>8800000</v>
-      </c>
-      <c r="P17" s="156">
-        <f t="shared" si="7"/>
-        <v>7999999.9999999991</v>
-      </c>
-      <c r="Q17" s="156">
-        <f t="shared" si="8"/>
-        <v>2699999.9999999991</v>
-      </c>
-      <c r="R17" s="156">
-        <f t="shared" si="5"/>
         <v>60.011143970555572</v>
       </c>
     </row>
@@ -50759,37 +50751,37 @@
       <c r="B18" s="50" t="s">
         <v>316</v>
       </c>
-      <c r="C18" s="271">
+      <c r="C18" s="264">
         <v>172113955.20000002</v>
       </c>
-      <c r="D18" s="271">
+      <c r="D18" s="264">
         <v>0</v>
       </c>
       <c r="E18" s="156">
         <v>0</v>
       </c>
       <c r="F18" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>1290854.6640000001</v>
       </c>
       <c r="G18" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>173404809.86400002</v>
       </c>
       <c r="H18" s="156">
-        <f>M18*6/1.1</f>
+        <f t="shared" si="3"/>
         <v>32999999.999999996</v>
       </c>
       <c r="I18" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J18" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>206404809.86400002</v>
       </c>
       <c r="K18" s="156">
-        <v>5700000</v>
+        <v>6000000</v>
       </c>
       <c r="L18" s="156">
         <f>9800000*80%</f>
@@ -50802,20 +50794,20 @@
         <v>0</v>
       </c>
       <c r="O18" s="156">
+        <f t="shared" si="7"/>
+        <v>13890000</v>
+      </c>
+      <c r="P18" s="156">
+        <f t="shared" si="8"/>
+        <v>12627272.727272727</v>
+      </c>
+      <c r="Q18" s="156">
+        <f t="shared" si="9"/>
+        <v>6627272.7272727266</v>
+      </c>
+      <c r="R18" s="156">
         <f t="shared" si="6"/>
-        <v>13890000</v>
-      </c>
-      <c r="P18" s="156">
-        <f t="shared" si="7"/>
-        <v>12627272.727272727</v>
-      </c>
-      <c r="Q18" s="156">
-        <f t="shared" si="8"/>
-        <v>6927272.7272727266</v>
-      </c>
-      <c r="R18" s="156">
-        <f t="shared" si="5"/>
-        <v>29.795969927874022</v>
+        <v>31.144758690041158</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -50825,33 +50817,33 @@
       <c r="B19" s="50" t="s">
         <v>347</v>
       </c>
-      <c r="C19" s="271">
+      <c r="C19" s="264">
         <v>39693130</v>
       </c>
-      <c r="D19" s="271">
+      <c r="D19" s="264">
         <v>0</v>
       </c>
       <c r="E19" s="156">
         <v>0</v>
       </c>
       <c r="F19" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>297698.47499999998</v>
       </c>
       <c r="G19" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>39990828.475000001</v>
       </c>
       <c r="H19" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I19" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J19" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39990828.475000001</v>
       </c>
       <c r="K19" s="156">
@@ -50867,19 +50859,19 @@
         <v>0</v>
       </c>
       <c r="O19" s="156">
+        <f t="shared" si="7"/>
+        <v>5800000</v>
+      </c>
+      <c r="P19" s="156">
+        <f t="shared" si="8"/>
+        <v>5272727.2727272725</v>
+      </c>
+      <c r="Q19" s="156">
+        <f t="shared" si="9"/>
+        <v>1272727.2727272725</v>
+      </c>
+      <c r="R19" s="156">
         <f t="shared" si="6"/>
-        <v>5800000</v>
-      </c>
-      <c r="P19" s="156">
-        <f t="shared" si="7"/>
-        <v>5272727.2727272725</v>
-      </c>
-      <c r="Q19" s="156">
-        <f t="shared" si="8"/>
-        <v>1272727.2727272725</v>
-      </c>
-      <c r="R19" s="156">
-        <f t="shared" si="5"/>
         <v>31.42136523035715</v>
       </c>
     </row>
@@ -50890,34 +50882,34 @@
       <c r="B20" s="50" t="s">
         <v>649</v>
       </c>
-      <c r="C20" s="271">
+      <c r="C20" s="264">
         <f>94974000+36000000</f>
         <v>130974000</v>
       </c>
-      <c r="D20" s="271">
+      <c r="D20" s="264">
         <v>0</v>
       </c>
       <c r="E20" s="156">
         <v>0</v>
       </c>
       <c r="F20" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>982305</v>
       </c>
       <c r="G20" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>131956305</v>
       </c>
       <c r="H20" s="156">
-        <f t="shared" ref="H20:H21" si="15">M20*6/1.1</f>
+        <f t="shared" si="3"/>
         <v>59999999.999999993</v>
       </c>
       <c r="I20" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J20" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>191956305</v>
       </c>
       <c r="K20" s="156">
@@ -50933,19 +50925,19 @@
         <v>0</v>
       </c>
       <c r="O20" s="156">
+        <f t="shared" si="7"/>
+        <v>19000000</v>
+      </c>
+      <c r="P20" s="156">
+        <f t="shared" si="8"/>
+        <v>17272727.27272727</v>
+      </c>
+      <c r="Q20" s="156">
+        <f t="shared" si="9"/>
+        <v>10772727.27272727</v>
+      </c>
+      <c r="R20" s="156">
         <f t="shared" si="6"/>
-        <v>19000000</v>
-      </c>
-      <c r="P20" s="156">
-        <f t="shared" si="7"/>
-        <v>17272727.27272727</v>
-      </c>
-      <c r="Q20" s="156">
-        <f t="shared" si="8"/>
-        <v>10772727.27272727</v>
-      </c>
-      <c r="R20" s="156">
-        <f t="shared" si="5"/>
         <v>17.81872873417722</v>
       </c>
     </row>
@@ -50956,36 +50948,36 @@
       <c r="B21" s="50" t="s">
         <v>196</v>
       </c>
-      <c r="C21" s="271">
+      <c r="C21" s="264">
         <v>172211316</v>
       </c>
-      <c r="D21" s="271">
+      <c r="D21" s="264">
         <v>0</v>
       </c>
       <c r="E21" s="156">
         <v>0</v>
       </c>
       <c r="F21" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>1291584.8699999999</v>
       </c>
       <c r="G21" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>173502900.87</v>
       </c>
       <c r="H21" s="156">
-        <f t="shared" si="15"/>
+        <f t="shared" si="3"/>
         <v>30419999.999999996</v>
       </c>
       <c r="I21" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J21" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>203922900.87</v>
       </c>
-      <c r="K21" s="275">
+      <c r="K21" s="156">
         <v>6000000</v>
       </c>
       <c r="L21" s="156">
@@ -50993,26 +50985,25 @@
         <v>8240000</v>
       </c>
       <c r="M21" s="156">
-        <f>5070000*1.1</f>
         <v>5577000</v>
       </c>
       <c r="N21" s="156">
         <v>0</v>
       </c>
       <c r="O21" s="156">
+        <f t="shared" si="7"/>
+        <v>13817000</v>
+      </c>
+      <c r="P21" s="156">
+        <f t="shared" si="8"/>
+        <v>12560909.09090909</v>
+      </c>
+      <c r="Q21" s="156">
+        <f t="shared" si="9"/>
+        <v>6560909.0909090899</v>
+      </c>
+      <c r="R21" s="156">
         <f t="shared" si="6"/>
-        <v>13817000</v>
-      </c>
-      <c r="P21" s="156">
-        <f t="shared" si="7"/>
-        <v>12560909.09090909</v>
-      </c>
-      <c r="Q21" s="156">
-        <f t="shared" si="8"/>
-        <v>6560909.0909090899</v>
-      </c>
-      <c r="R21" s="156">
-        <f t="shared" si="5"/>
         <v>31.081500756131362</v>
       </c>
     </row>
@@ -51023,36 +51014,36 @@
       <c r="B22" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="271">
+      <c r="C22" s="264">
         <v>112039400.00000001</v>
       </c>
-      <c r="D22" s="271">
+      <c r="D22" s="264">
         <v>0</v>
       </c>
       <c r="E22" s="156">
         <v>0</v>
       </c>
       <c r="F22" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>840295.50000000012</v>
       </c>
       <c r="G22" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>112879695.50000001</v>
       </c>
       <c r="H22" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I22" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J22" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>112879695.50000001</v>
       </c>
-      <c r="K22" s="275">
+      <c r="K22" s="156">
         <v>6500000</v>
       </c>
       <c r="L22" s="156">
@@ -51065,19 +51056,19 @@
         <v>0</v>
       </c>
       <c r="O22" s="156">
+        <f t="shared" si="7"/>
+        <v>11200000</v>
+      </c>
+      <c r="P22" s="156">
+        <f t="shared" si="8"/>
+        <v>10181818.181818182</v>
+      </c>
+      <c r="Q22" s="156">
+        <f t="shared" si="9"/>
+        <v>3681818.1818181816</v>
+      </c>
+      <c r="R22" s="156">
         <f t="shared" si="6"/>
-        <v>11200000</v>
-      </c>
-      <c r="P22" s="156">
-        <f t="shared" si="7"/>
-        <v>10181818.181818182</v>
-      </c>
-      <c r="Q22" s="156">
-        <f t="shared" si="8"/>
-        <v>3681818.1818181816</v>
-      </c>
-      <c r="R22" s="156">
-        <f t="shared" si="5"/>
         <v>30.658682728395068</v>
       </c>
     </row>
@@ -51088,36 +51079,36 @@
       <c r="B23" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="C23" s="271">
+      <c r="C23" s="264">
         <v>166879967</v>
       </c>
-      <c r="D23" s="271">
+      <c r="D23" s="264">
         <v>0</v>
       </c>
       <c r="E23" s="156">
         <v>0</v>
       </c>
       <c r="F23" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>1251599.7524999999</v>
       </c>
       <c r="G23" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>168131566.7525</v>
       </c>
       <c r="H23" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I23" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J23" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>168131566.7525</v>
       </c>
-      <c r="K23" s="275">
+      <c r="K23" s="156">
         <v>5750000</v>
       </c>
       <c r="L23" s="156">
@@ -51130,19 +51121,19 @@
         <v>0</v>
       </c>
       <c r="O23" s="156">
+        <f t="shared" si="7"/>
+        <v>10700000</v>
+      </c>
+      <c r="P23" s="156">
+        <f t="shared" si="8"/>
+        <v>9727272.7272727266</v>
+      </c>
+      <c r="Q23" s="156">
+        <f t="shared" si="9"/>
+        <v>3977272.7272727266</v>
+      </c>
+      <c r="R23" s="156">
         <f t="shared" si="6"/>
-        <v>10700000</v>
-      </c>
-      <c r="P23" s="156">
-        <f t="shared" si="7"/>
-        <v>9727272.7272727266</v>
-      </c>
-      <c r="Q23" s="156">
-        <f t="shared" si="8"/>
-        <v>3977272.7272727266</v>
-      </c>
-      <c r="R23" s="156">
-        <f t="shared" si="5"/>
         <v>42.27307964062858</v>
       </c>
     </row>
@@ -51153,36 +51144,36 @@
       <c r="B24" s="50" t="s">
         <v>1166</v>
       </c>
-      <c r="C24" s="271">
+      <c r="C24" s="264">
         <v>373000000</v>
       </c>
-      <c r="D24" s="271">
+      <c r="D24" s="264">
         <v>0</v>
       </c>
       <c r="E24" s="156">
         <v>0</v>
       </c>
       <c r="F24" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>2797500</v>
       </c>
       <c r="G24" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>375797500</v>
       </c>
       <c r="H24" s="156">
-        <f>M24*6/1.1</f>
+        <f t="shared" si="3"/>
         <v>42000000</v>
       </c>
       <c r="I24" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>66600000</v>
       </c>
       <c r="J24" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>484397500</v>
       </c>
-      <c r="K24" s="275">
+      <c r="K24" s="266">
         <v>5000000</v>
       </c>
       <c r="L24" s="156">
@@ -51190,26 +51181,25 @@
         <v>8820000</v>
       </c>
       <c r="M24" s="156">
-        <f>7000000*1.1</f>
         <v>7700000.0000000009</v>
       </c>
       <c r="N24" s="156">
         <v>7400000</v>
       </c>
       <c r="O24" s="156">
+        <f t="shared" si="7"/>
+        <v>23920000</v>
+      </c>
+      <c r="P24" s="156">
+        <f t="shared" si="8"/>
+        <v>21745454.545454543</v>
+      </c>
+      <c r="Q24" s="156">
+        <f t="shared" si="9"/>
+        <v>16745454.545454543</v>
+      </c>
+      <c r="R24" s="156">
         <f t="shared" si="6"/>
-        <v>23920000</v>
-      </c>
-      <c r="P24" s="156">
-        <f t="shared" si="7"/>
-        <v>21745454.545454543</v>
-      </c>
-      <c r="Q24" s="156">
-        <f t="shared" si="8"/>
-        <v>16745454.545454543</v>
-      </c>
-      <c r="R24" s="156">
-        <f t="shared" si="5"/>
         <v>28.927103691639527</v>
       </c>
     </row>
@@ -51220,37 +51210,37 @@
       <c r="B25" s="50" t="s">
         <v>428</v>
       </c>
-      <c r="C25" s="271">
+      <c r="C25" s="264">
         <v>176000000</v>
       </c>
-      <c r="D25" s="271">
+      <c r="D25" s="264">
         <v>0</v>
       </c>
       <c r="E25" s="156">
         <v>0</v>
       </c>
       <c r="F25" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>1320000</v>
       </c>
       <c r="G25" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>177320000</v>
       </c>
       <c r="H25" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I25" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J25" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>177320000</v>
       </c>
-      <c r="K25" s="275">
-        <v>5000000</v>
+      <c r="K25" s="156">
+        <v>7000000</v>
       </c>
       <c r="L25" s="156">
         <f>12600000</f>
@@ -51263,20 +51253,20 @@
         <v>0</v>
       </c>
       <c r="O25" s="156">
+        <f t="shared" si="7"/>
+        <v>12600000</v>
+      </c>
+      <c r="P25" s="156">
+        <f t="shared" si="8"/>
+        <v>11454545.454545453</v>
+      </c>
+      <c r="Q25" s="156">
+        <f t="shared" si="9"/>
+        <v>4454545.4545454532</v>
+      </c>
+      <c r="R25" s="156">
         <f t="shared" si="6"/>
-        <v>12600000</v>
-      </c>
-      <c r="P25" s="156">
-        <f t="shared" si="7"/>
-        <v>11454545.454545453</v>
-      </c>
-      <c r="Q25" s="156">
-        <f t="shared" si="8"/>
-        <v>6454545.4545454532</v>
-      </c>
-      <c r="R25" s="156">
-        <f t="shared" si="5"/>
-        <v>27.472112676056344</v>
+        <v>39.806530612244913</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -51286,36 +51276,36 @@
       <c r="B26" s="50" t="s">
         <v>434</v>
       </c>
-      <c r="C26" s="271">
+      <c r="C26" s="264">
         <v>43000000</v>
       </c>
-      <c r="D26" s="271">
+      <c r="D26" s="264">
         <v>0</v>
       </c>
       <c r="E26" s="156">
         <v>0</v>
       </c>
       <c r="F26" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>322500</v>
       </c>
       <c r="G26" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>43322500</v>
       </c>
       <c r="H26" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I26" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J26" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>43322500</v>
       </c>
-      <c r="K26" s="275">
+      <c r="K26" s="156">
         <v>3000000</v>
       </c>
       <c r="L26" s="156">
@@ -51328,19 +51318,19 @@
         <v>0</v>
       </c>
       <c r="O26" s="156">
+        <f t="shared" si="7"/>
+        <v>5700000</v>
+      </c>
+      <c r="P26" s="156">
+        <f t="shared" si="8"/>
+        <v>5181818.1818181816</v>
+      </c>
+      <c r="Q26" s="156">
+        <f t="shared" si="9"/>
+        <v>2181818.1818181816</v>
+      </c>
+      <c r="R26" s="156">
         <f t="shared" si="6"/>
-        <v>5700000</v>
-      </c>
-      <c r="P26" s="156">
-        <f t="shared" si="7"/>
-        <v>5181818.1818181816</v>
-      </c>
-      <c r="Q26" s="156">
-        <f t="shared" si="8"/>
-        <v>2181818.1818181816</v>
-      </c>
-      <c r="R26" s="156">
-        <f t="shared" si="5"/>
         <v>19.856145833333336</v>
       </c>
     </row>
@@ -51351,37 +51341,37 @@
       <c r="B27" s="50" t="s">
         <v>436</v>
       </c>
-      <c r="C27" s="271">
+      <c r="C27" s="264">
         <v>171000000</v>
       </c>
-      <c r="D27" s="271">
+      <c r="D27" s="264">
         <v>0</v>
       </c>
       <c r="E27" s="156">
         <v>0</v>
       </c>
       <c r="F27" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>1282500</v>
       </c>
       <c r="G27" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>172282500</v>
       </c>
       <c r="H27" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I27" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>63000000</v>
       </c>
       <c r="J27" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>235282500</v>
       </c>
-      <c r="K27" s="275">
-        <v>9000000</v>
+      <c r="K27" s="156">
+        <v>8500000</v>
       </c>
       <c r="L27" s="156">
         <f>12600000*0.8</f>
@@ -51394,20 +51384,20 @@
         <v>7000000</v>
       </c>
       <c r="O27" s="156">
+        <f t="shared" si="7"/>
+        <v>17080000</v>
+      </c>
+      <c r="P27" s="156">
+        <f t="shared" si="8"/>
+        <v>15527272.727272727</v>
+      </c>
+      <c r="Q27" s="156">
+        <f t="shared" si="9"/>
+        <v>7027272.7272727266</v>
+      </c>
+      <c r="R27" s="156">
         <f t="shared" si="6"/>
-        <v>17080000</v>
-      </c>
-      <c r="P27" s="156">
-        <f t="shared" si="7"/>
-        <v>15527272.727272727</v>
-      </c>
-      <c r="Q27" s="156">
-        <f t="shared" si="8"/>
-        <v>6527272.7272727266</v>
-      </c>
-      <c r="R27" s="156">
-        <f t="shared" si="5"/>
-        <v>36.046065459610034</v>
+        <v>33.481338939197933</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -51417,36 +51407,36 @@
       <c r="B28" s="50" t="s">
         <v>343</v>
       </c>
-      <c r="C28" s="271">
+      <c r="C28" s="264">
         <v>162000000</v>
       </c>
-      <c r="D28" s="271">
+      <c r="D28" s="264">
         <v>0</v>
       </c>
       <c r="E28" s="156">
         <v>0</v>
       </c>
       <c r="F28" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>1215000</v>
       </c>
       <c r="G28" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>163215000</v>
       </c>
       <c r="H28" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I28" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J28" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>163215000</v>
       </c>
-      <c r="K28" s="275">
+      <c r="K28" s="156">
         <v>5000000</v>
       </c>
       <c r="L28" s="156">
@@ -51459,19 +51449,19 @@
         <v>0</v>
       </c>
       <c r="O28" s="156">
+        <f t="shared" si="7"/>
+        <v>10000000</v>
+      </c>
+      <c r="P28" s="156">
+        <f t="shared" si="8"/>
+        <v>9090909.0909090899</v>
+      </c>
+      <c r="Q28" s="156">
+        <f t="shared" si="9"/>
+        <v>4090909.0909090899</v>
+      </c>
+      <c r="R28" s="156">
         <f t="shared" si="6"/>
-        <v>10000000</v>
-      </c>
-      <c r="P28" s="156">
-        <f t="shared" si="7"/>
-        <v>9090909.0909090899</v>
-      </c>
-      <c r="Q28" s="156">
-        <f t="shared" si="8"/>
-        <v>4090909.0909090899</v>
-      </c>
-      <c r="R28" s="156">
-        <f t="shared" si="5"/>
         <v>39.897000000000013</v>
       </c>
     </row>
@@ -51482,36 +51472,36 @@
       <c r="B29" s="50" t="s">
         <v>457</v>
       </c>
-      <c r="C29" s="271">
+      <c r="C29" s="264">
         <v>118000000</v>
       </c>
-      <c r="D29" s="271">
+      <c r="D29" s="264">
         <v>0</v>
       </c>
       <c r="E29" s="156">
         <v>0</v>
       </c>
       <c r="F29" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>885000</v>
       </c>
       <c r="G29" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>118885000</v>
       </c>
       <c r="H29" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I29" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J29" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>118885000</v>
       </c>
-      <c r="K29" s="275">
+      <c r="K29" s="156">
         <v>7000000</v>
       </c>
       <c r="L29" s="156">
@@ -51524,19 +51514,19 @@
         <v>0</v>
       </c>
       <c r="O29" s="156">
+        <f t="shared" si="7"/>
+        <v>12000000</v>
+      </c>
+      <c r="P29" s="156">
+        <f t="shared" si="8"/>
+        <v>10909090.909090908</v>
+      </c>
+      <c r="Q29" s="156">
+        <f t="shared" si="9"/>
+        <v>3909090.9090909082</v>
+      </c>
+      <c r="R29" s="156">
         <f t="shared" si="6"/>
-        <v>12000000</v>
-      </c>
-      <c r="P29" s="156">
-        <f t="shared" si="7"/>
-        <v>10909090.909090908</v>
-      </c>
-      <c r="Q29" s="156">
-        <f t="shared" si="8"/>
-        <v>3909090.9090909082</v>
-      </c>
-      <c r="R29" s="156">
-        <f t="shared" si="5"/>
         <v>30.412441860465123</v>
       </c>
     </row>
@@ -51547,36 +51537,36 @@
       <c r="B30" s="50" t="s">
         <v>463</v>
       </c>
-      <c r="C30" s="271">
+      <c r="C30" s="264">
         <v>85000000</v>
       </c>
-      <c r="D30" s="271">
+      <c r="D30" s="264">
         <v>0</v>
       </c>
       <c r="E30" s="156">
         <v>0</v>
       </c>
       <c r="F30" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>637500</v>
       </c>
       <c r="G30" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>85637500</v>
       </c>
       <c r="H30" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I30" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>61380000.000000007</v>
       </c>
       <c r="J30" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>147017500</v>
       </c>
-      <c r="K30" s="275">
+      <c r="K30" s="156">
         <v>5000000</v>
       </c>
       <c r="L30" s="156">
@@ -51585,23 +51575,23 @@
       <c r="M30" s="156">
         <v>0</v>
       </c>
-      <c r="N30" s="276">
+      <c r="N30" s="267">
         <v>6820000.0000000009</v>
       </c>
       <c r="O30" s="156">
+        <f t="shared" si="7"/>
+        <v>14720000</v>
+      </c>
+      <c r="P30" s="156">
+        <f t="shared" si="8"/>
+        <v>13381818.181818182</v>
+      </c>
+      <c r="Q30" s="156">
+        <f t="shared" si="9"/>
+        <v>8381818.1818181816</v>
+      </c>
+      <c r="R30" s="156">
         <f t="shared" si="6"/>
-        <v>14720000</v>
-      </c>
-      <c r="P30" s="156">
-        <f t="shared" si="7"/>
-        <v>13381818.181818182</v>
-      </c>
-      <c r="Q30" s="156">
-        <f t="shared" si="8"/>
-        <v>8381818.1818181816</v>
-      </c>
-      <c r="R30" s="156">
-        <f t="shared" si="5"/>
         <v>17.540048806941432</v>
       </c>
     </row>
@@ -51612,36 +51602,36 @@
       <c r="B31" s="50" t="s">
         <v>469</v>
       </c>
-      <c r="C31" s="271">
+      <c r="C31" s="264">
         <v>156000000</v>
       </c>
-      <c r="D31" s="271">
+      <c r="D31" s="264">
         <v>0</v>
       </c>
       <c r="E31" s="156">
         <v>0</v>
       </c>
       <c r="F31" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>1170000</v>
       </c>
       <c r="G31" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>157170000</v>
       </c>
       <c r="H31" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I31" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J31" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>157170000</v>
       </c>
-      <c r="K31" s="275">
+      <c r="K31" s="156">
         <v>5000000</v>
       </c>
       <c r="L31" s="156">
@@ -51654,19 +51644,19 @@
         <v>0</v>
       </c>
       <c r="O31" s="156">
+        <f t="shared" si="7"/>
+        <v>10500000</v>
+      </c>
+      <c r="P31" s="156">
+        <f t="shared" si="8"/>
+        <v>9545454.5454545449</v>
+      </c>
+      <c r="Q31" s="156">
+        <f t="shared" si="9"/>
+        <v>4545454.5454545449</v>
+      </c>
+      <c r="R31" s="156">
         <f t="shared" si="6"/>
-        <v>10500000</v>
-      </c>
-      <c r="P31" s="156">
-        <f t="shared" si="7"/>
-        <v>9545454.5454545449</v>
-      </c>
-      <c r="Q31" s="156">
-        <f t="shared" si="8"/>
-        <v>4545454.5454545449</v>
-      </c>
-      <c r="R31" s="156">
-        <f t="shared" si="5"/>
         <v>34.577400000000004</v>
       </c>
     </row>
@@ -51677,36 +51667,36 @@
       <c r="B32" s="50" t="s">
         <v>475</v>
       </c>
-      <c r="C32" s="271">
+      <c r="C32" s="264">
         <v>163000000</v>
       </c>
-      <c r="D32" s="271">
+      <c r="D32" s="264">
         <v>0</v>
       </c>
       <c r="E32" s="156">
         <v>0</v>
       </c>
       <c r="F32" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>1222500</v>
       </c>
       <c r="G32" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>164222500</v>
       </c>
       <c r="H32" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I32" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J32" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>164222500</v>
       </c>
-      <c r="K32" s="275">
+      <c r="K32" s="156">
         <v>5500000</v>
       </c>
       <c r="L32" s="156">
@@ -51719,19 +51709,19 @@
         <v>0</v>
       </c>
       <c r="O32" s="156">
+        <f t="shared" si="7"/>
+        <v>11000000</v>
+      </c>
+      <c r="P32" s="156">
+        <f t="shared" si="8"/>
+        <v>10000000</v>
+      </c>
+      <c r="Q32" s="156">
+        <f t="shared" si="9"/>
+        <v>4500000</v>
+      </c>
+      <c r="R32" s="156">
         <f t="shared" si="6"/>
-        <v>11000000</v>
-      </c>
-      <c r="P32" s="156">
-        <f t="shared" si="7"/>
-        <v>10000000</v>
-      </c>
-      <c r="Q32" s="156">
-        <f t="shared" si="8"/>
-        <v>4500000</v>
-      </c>
-      <c r="R32" s="156">
-        <f t="shared" si="5"/>
         <v>36.49388888888889</v>
       </c>
     </row>
@@ -51742,36 +51732,36 @@
       <c r="B33" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="271">
+      <c r="C33" s="264">
         <v>93000000</v>
       </c>
-      <c r="D33" s="271">
+      <c r="D33" s="264">
         <v>0</v>
       </c>
       <c r="E33" s="156">
         <v>0</v>
       </c>
       <c r="F33" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>697500</v>
       </c>
       <c r="G33" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>93697500</v>
       </c>
       <c r="H33" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I33" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>66600000</v>
       </c>
       <c r="J33" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>160297500</v>
       </c>
-      <c r="K33" s="275">
+      <c r="K33" s="156">
         <v>7700000</v>
       </c>
       <c r="L33" s="156">
@@ -51785,19 +51775,19 @@
         <v>7400000</v>
       </c>
       <c r="O33" s="156">
+        <f t="shared" si="7"/>
+        <v>16520000</v>
+      </c>
+      <c r="P33" s="156">
+        <f t="shared" si="8"/>
+        <v>15018181.818181816</v>
+      </c>
+      <c r="Q33" s="156">
+        <f t="shared" si="9"/>
+        <v>7318181.8181818165</v>
+      </c>
+      <c r="R33" s="156">
         <f t="shared" si="6"/>
-        <v>16520000</v>
-      </c>
-      <c r="P33" s="156">
-        <f t="shared" si="7"/>
-        <v>15018181.818181816</v>
-      </c>
-      <c r="Q33" s="156">
-        <f t="shared" si="8"/>
-        <v>7318181.8181818165</v>
-      </c>
-      <c r="R33" s="156">
-        <f t="shared" si="5"/>
         <v>21.904006211180128</v>
       </c>
     </row>
@@ -51808,36 +51798,36 @@
       <c r="B34" s="50" t="s">
         <v>486</v>
       </c>
-      <c r="C34" s="271">
+      <c r="C34" s="264">
         <v>190000000</v>
       </c>
-      <c r="D34" s="271">
+      <c r="D34" s="264">
         <v>0</v>
       </c>
       <c r="E34" s="156">
         <v>0</v>
       </c>
       <c r="F34" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>1425000</v>
       </c>
       <c r="G34" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>191425000</v>
       </c>
       <c r="H34" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I34" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J34" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>191425000</v>
       </c>
-      <c r="K34" s="275">
+      <c r="K34" s="156">
         <v>6000000</v>
       </c>
       <c r="L34" s="156">
@@ -51850,19 +51840,19 @@
         <v>0</v>
       </c>
       <c r="O34" s="156">
+        <f t="shared" si="7"/>
+        <v>12100000</v>
+      </c>
+      <c r="P34" s="156">
+        <f t="shared" si="8"/>
+        <v>11000000</v>
+      </c>
+      <c r="Q34" s="156">
+        <f t="shared" si="9"/>
+        <v>5000000</v>
+      </c>
+      <c r="R34" s="156">
         <f t="shared" si="6"/>
-        <v>12100000</v>
-      </c>
-      <c r="P34" s="156">
-        <f t="shared" si="7"/>
-        <v>11000000</v>
-      </c>
-      <c r="Q34" s="156">
-        <f t="shared" si="8"/>
-        <v>5000000</v>
-      </c>
-      <c r="R34" s="156">
-        <f t="shared" si="5"/>
         <v>38.284999999999997</v>
       </c>
     </row>
@@ -51873,36 +51863,36 @@
       <c r="B35" s="50" t="s">
         <v>501</v>
       </c>
-      <c r="C35" s="271">
+      <c r="C35" s="264">
         <v>89000000</v>
       </c>
-      <c r="D35" s="271">
+      <c r="D35" s="264">
         <v>0</v>
       </c>
       <c r="E35" s="156">
         <v>0</v>
       </c>
       <c r="F35" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>667500</v>
       </c>
       <c r="G35" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>89667500</v>
       </c>
       <c r="H35" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I35" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J35" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>89667500</v>
       </c>
-      <c r="K35" s="275">
+      <c r="K35" s="156">
         <v>7000000</v>
       </c>
       <c r="L35" s="156">
@@ -51915,19 +51905,19 @@
         <v>0</v>
       </c>
       <c r="O35" s="156">
+        <f t="shared" si="7"/>
+        <v>11900000</v>
+      </c>
+      <c r="P35" s="156">
+        <f t="shared" si="8"/>
+        <v>10818181.818181816</v>
+      </c>
+      <c r="Q35" s="156">
+        <f t="shared" si="9"/>
+        <v>3818181.8181818165</v>
+      </c>
+      <c r="R35" s="156">
         <f t="shared" si="6"/>
-        <v>11900000</v>
-      </c>
-      <c r="P35" s="156">
-        <f t="shared" si="7"/>
-        <v>10818181.818181816</v>
-      </c>
-      <c r="Q35" s="156">
-        <f t="shared" si="8"/>
-        <v>3818181.8181818165</v>
-      </c>
-      <c r="R35" s="156">
-        <f t="shared" si="5"/>
         <v>23.484345238095248</v>
       </c>
     </row>
@@ -51938,36 +51928,36 @@
       <c r="B36" s="50" t="s">
         <v>500</v>
       </c>
-      <c r="C36" s="271">
+      <c r="C36" s="264">
         <v>118000000</v>
       </c>
-      <c r="D36" s="271">
+      <c r="D36" s="264">
         <v>0</v>
       </c>
       <c r="E36" s="156">
         <v>0</v>
       </c>
       <c r="F36" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>885000</v>
       </c>
       <c r="G36" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>118885000</v>
       </c>
       <c r="H36" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I36" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J36" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>118885000</v>
       </c>
-      <c r="K36" s="275">
+      <c r="K36" s="156">
         <v>8000000</v>
       </c>
       <c r="L36" s="156">
@@ -51980,19 +51970,19 @@
         <v>0</v>
       </c>
       <c r="O36" s="156">
+        <f t="shared" si="7"/>
+        <v>12600000</v>
+      </c>
+      <c r="P36" s="156">
+        <f t="shared" si="8"/>
+        <v>11454545.454545453</v>
+      </c>
+      <c r="Q36" s="156">
+        <f t="shared" si="9"/>
+        <v>3454545.4545454532</v>
+      </c>
+      <c r="R36" s="156">
         <f t="shared" si="6"/>
-        <v>12600000</v>
-      </c>
-      <c r="P36" s="156">
-        <f t="shared" si="7"/>
-        <v>11454545.454545453</v>
-      </c>
-      <c r="Q36" s="156">
-        <f t="shared" si="8"/>
-        <v>3454545.4545454532</v>
-      </c>
-      <c r="R36" s="156">
-        <f t="shared" si="5"/>
         <v>34.414078947368438</v>
       </c>
     </row>
@@ -52003,36 +51993,36 @@
       <c r="B37" s="50" t="s">
         <v>492</v>
       </c>
-      <c r="C37" s="271">
+      <c r="C37" s="264">
         <v>57000000</v>
       </c>
-      <c r="D37" s="271">
+      <c r="D37" s="264">
         <v>0</v>
       </c>
       <c r="E37" s="156">
         <v>0</v>
       </c>
       <c r="F37" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>427500</v>
       </c>
       <c r="G37" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>57427500</v>
       </c>
       <c r="H37" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I37" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>58500000</v>
       </c>
       <c r="J37" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>115927500</v>
       </c>
-      <c r="K37" s="275">
+      <c r="K37" s="156">
         <v>7000000</v>
       </c>
       <c r="L37" s="156">
@@ -52046,19 +52036,19 @@
         <v>6500000</v>
       </c>
       <c r="O37" s="156">
+        <f t="shared" si="7"/>
+        <v>12900000</v>
+      </c>
+      <c r="P37" s="156">
+        <f t="shared" si="8"/>
+        <v>11727272.727272727</v>
+      </c>
+      <c r="Q37" s="156">
+        <f t="shared" si="9"/>
+        <v>4727272.7272727266</v>
+      </c>
+      <c r="R37" s="156">
         <f t="shared" si="6"/>
-        <v>12900000</v>
-      </c>
-      <c r="P37" s="156">
-        <f t="shared" si="7"/>
-        <v>11727272.727272727</v>
-      </c>
-      <c r="Q37" s="156">
-        <f t="shared" si="8"/>
-        <v>4727272.7272727266</v>
-      </c>
-      <c r="R37" s="156">
-        <f t="shared" si="5"/>
         <v>24.523125000000004</v>
       </c>
     </row>
@@ -52069,36 +52059,36 @@
       <c r="B38" s="50" t="s">
         <v>549</v>
       </c>
-      <c r="C38" s="271">
+      <c r="C38" s="264">
         <v>126580850</v>
       </c>
-      <c r="D38" s="271">
+      <c r="D38" s="264">
         <v>0</v>
       </c>
       <c r="E38" s="156">
         <v>0</v>
       </c>
       <c r="F38" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>949356.375</v>
       </c>
       <c r="G38" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>127530206.375</v>
       </c>
       <c r="H38" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I38" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J38" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>127530206.375</v>
       </c>
-      <c r="K38" s="275">
+      <c r="K38" s="156">
         <v>6500000</v>
       </c>
       <c r="L38" s="156">
@@ -52111,19 +52101,19 @@
         <v>0</v>
       </c>
       <c r="O38" s="156">
+        <f t="shared" si="7"/>
+        <v>11400000</v>
+      </c>
+      <c r="P38" s="156">
+        <f t="shared" si="8"/>
+        <v>10363636.363636363</v>
+      </c>
+      <c r="Q38" s="156">
+        <f t="shared" si="9"/>
+        <v>3863636.3636363633</v>
+      </c>
+      <c r="R38" s="156">
         <f t="shared" si="6"/>
-        <v>11400000</v>
-      </c>
-      <c r="P38" s="156">
-        <f t="shared" si="7"/>
-        <v>10363636.363636363</v>
-      </c>
-      <c r="Q38" s="156">
-        <f t="shared" si="8"/>
-        <v>3863636.3636363633</v>
-      </c>
-      <c r="R38" s="156">
-        <f t="shared" si="5"/>
         <v>33.00781812058824</v>
       </c>
     </row>
@@ -52134,36 +52124,36 @@
       <c r="B39" s="50" t="s">
         <v>558</v>
       </c>
-      <c r="C39" s="271">
+      <c r="C39" s="264">
         <v>149839228</v>
       </c>
-      <c r="D39" s="271">
+      <c r="D39" s="264">
         <v>0</v>
       </c>
       <c r="E39" s="156">
         <v>0</v>
       </c>
       <c r="F39" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>1123794.21</v>
       </c>
       <c r="G39" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>150963022.21000001</v>
       </c>
       <c r="H39" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I39" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J39" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>150963022.21000001</v>
       </c>
-      <c r="K39" s="275">
+      <c r="K39" s="156">
         <v>6000000</v>
       </c>
       <c r="L39" s="156">
@@ -52176,19 +52166,19 @@
         <v>0</v>
       </c>
       <c r="O39" s="156">
+        <f t="shared" si="7"/>
+        <v>11000000</v>
+      </c>
+      <c r="P39" s="156">
+        <f t="shared" si="8"/>
+        <v>10000000</v>
+      </c>
+      <c r="Q39" s="156">
+        <f t="shared" si="9"/>
+        <v>4000000</v>
+      </c>
+      <c r="R39" s="156">
         <f t="shared" si="6"/>
-        <v>11000000</v>
-      </c>
-      <c r="P39" s="156">
-        <f t="shared" si="7"/>
-        <v>10000000</v>
-      </c>
-      <c r="Q39" s="156">
-        <f t="shared" si="8"/>
-        <v>4000000</v>
-      </c>
-      <c r="R39" s="156">
-        <f t="shared" si="5"/>
         <v>37.740755552500005</v>
       </c>
     </row>
@@ -52199,36 +52189,36 @@
       <c r="B40" s="50" t="s">
         <v>577</v>
       </c>
-      <c r="C40" s="271">
+      <c r="C40" s="264">
         <v>51589494</v>
       </c>
-      <c r="D40" s="271">
+      <c r="D40" s="264">
         <v>0</v>
       </c>
       <c r="E40" s="156">
         <v>0</v>
       </c>
       <c r="F40" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>386921.2049999999</v>
       </c>
       <c r="G40" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>51976415.204999998</v>
       </c>
       <c r="H40" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I40" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J40" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>51976415.204999998</v>
       </c>
-      <c r="K40" s="275">
+      <c r="K40" s="156">
         <v>6000000</v>
       </c>
       <c r="L40" s="156">
@@ -52241,19 +52231,19 @@
         <v>0</v>
       </c>
       <c r="O40" s="156">
+        <f t="shared" si="7"/>
+        <v>11200000</v>
+      </c>
+      <c r="P40" s="156">
+        <f t="shared" si="8"/>
+        <v>10181818.181818182</v>
+      </c>
+      <c r="Q40" s="156">
+        <f t="shared" si="9"/>
+        <v>4181818.1818181816</v>
+      </c>
+      <c r="R40" s="156">
         <f t="shared" si="6"/>
-        <v>11200000</v>
-      </c>
-      <c r="P40" s="156">
-        <f t="shared" si="7"/>
-        <v>10181818.181818182</v>
-      </c>
-      <c r="Q40" s="156">
-        <f t="shared" si="8"/>
-        <v>4181818.1818181816</v>
-      </c>
-      <c r="R40" s="156">
-        <f t="shared" si="5"/>
         <v>12.429142766413044</v>
       </c>
     </row>
@@ -52264,36 +52254,36 @@
       <c r="B41" s="50" t="s">
         <v>578</v>
       </c>
-      <c r="C41" s="271">
+      <c r="C41" s="264">
         <v>35720080</v>
       </c>
-      <c r="D41" s="271">
+      <c r="D41" s="264">
         <v>0</v>
       </c>
       <c r="E41" s="156">
         <v>0</v>
       </c>
       <c r="F41" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>267900.59999999998</v>
       </c>
       <c r="G41" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>35987980.600000001</v>
       </c>
       <c r="H41" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I41" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J41" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>35987980.600000001</v>
       </c>
-      <c r="K41" s="275">
+      <c r="K41" s="156">
         <v>4000000</v>
       </c>
       <c r="L41" s="156">
@@ -52306,19 +52296,19 @@
         <v>0</v>
       </c>
       <c r="O41" s="156">
+        <f t="shared" si="7"/>
+        <v>7000000</v>
+      </c>
+      <c r="P41" s="156">
+        <f t="shared" si="8"/>
+        <v>6363636.3636363633</v>
+      </c>
+      <c r="Q41" s="156">
+        <f t="shared" si="9"/>
+        <v>2363636.3636363633</v>
+      </c>
+      <c r="R41" s="156">
         <f t="shared" si="6"/>
-        <v>7000000</v>
-      </c>
-      <c r="P41" s="156">
-        <f t="shared" si="7"/>
-        <v>6363636.3636363633</v>
-      </c>
-      <c r="Q41" s="156">
-        <f t="shared" si="8"/>
-        <v>2363636.3636363633</v>
-      </c>
-      <c r="R41" s="156">
-        <f t="shared" si="5"/>
         <v>15.225684100000002</v>
       </c>
     </row>
@@ -52329,36 +52319,36 @@
       <c r="B42" s="50" t="s">
         <v>579</v>
       </c>
-      <c r="C42" s="271">
+      <c r="C42" s="264">
         <v>36671580</v>
       </c>
-      <c r="D42" s="271">
+      <c r="D42" s="264">
         <v>0</v>
       </c>
       <c r="E42" s="156">
         <v>0</v>
       </c>
       <c r="F42" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>275036.84999999998</v>
       </c>
       <c r="G42" s="156">
-        <f t="shared" si="11"/>
+        <f t="shared" si="2"/>
         <v>36946616.850000001</v>
       </c>
       <c r="H42" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I42" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J42" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>36946616.850000001</v>
       </c>
-      <c r="K42" s="275">
+      <c r="K42" s="156">
         <v>4000000</v>
       </c>
       <c r="L42" s="156">
@@ -52371,19 +52361,19 @@
         <v>0</v>
       </c>
       <c r="O42" s="156">
+        <f t="shared" si="7"/>
+        <v>7000000</v>
+      </c>
+      <c r="P42" s="156">
+        <f t="shared" si="8"/>
+        <v>6363636.3636363633</v>
+      </c>
+      <c r="Q42" s="156">
+        <f t="shared" si="9"/>
+        <v>2363636.3636363633</v>
+      </c>
+      <c r="R42" s="156">
         <f t="shared" si="6"/>
-        <v>7000000</v>
-      </c>
-      <c r="P42" s="156">
-        <f t="shared" si="7"/>
-        <v>6363636.3636363633</v>
-      </c>
-      <c r="Q42" s="156">
-        <f t="shared" si="8"/>
-        <v>2363636.3636363633</v>
-      </c>
-      <c r="R42" s="156">
-        <f t="shared" si="5"/>
         <v>15.631260975000004</v>
       </c>
     </row>
@@ -52394,36 +52384,36 @@
       <c r="B43" s="50" t="s">
         <v>580</v>
       </c>
-      <c r="C43" s="271">
+      <c r="C43" s="264">
         <v>87881750</v>
       </c>
-      <c r="D43" s="271">
+      <c r="D43" s="264">
         <v>0</v>
       </c>
       <c r="E43" s="156">
         <v>0</v>
       </c>
       <c r="F43" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>659113.125</v>
       </c>
       <c r="G43" s="156">
-        <f t="shared" ref="G43" si="16">SUM(C43:F43)</f>
+        <f t="shared" si="2"/>
         <v>88540863.125</v>
       </c>
       <c r="H43" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I43" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J43" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>88540863.125</v>
       </c>
-      <c r="K43" s="275">
+      <c r="K43" s="156">
         <v>6500000</v>
       </c>
       <c r="L43" s="156">
@@ -52436,19 +52426,19 @@
         <v>0</v>
       </c>
       <c r="O43" s="156">
-        <f t="shared" ref="O43:O92" si="17">SUM(L43:N43)</f>
+        <f t="shared" si="7"/>
         <v>10100000</v>
       </c>
       <c r="P43" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9181818.1818181816</v>
       </c>
       <c r="Q43" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2681818.1818181816</v>
       </c>
       <c r="R43" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>33.015237097457629</v>
       </c>
     </row>
@@ -52459,36 +52449,36 @@
       <c r="B44" s="50" t="s">
         <v>576</v>
       </c>
-      <c r="C44" s="271">
+      <c r="C44" s="264">
         <v>39775776</v>
       </c>
-      <c r="D44" s="271">
+      <c r="D44" s="264">
         <v>0</v>
       </c>
       <c r="E44" s="156">
         <v>0</v>
       </c>
       <c r="F44" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>298318.32</v>
       </c>
       <c r="G44" s="156">
-        <f t="shared" ref="G44:G92" si="18">SUM(C44:F44)</f>
+        <f t="shared" si="2"/>
         <v>40074094.32</v>
       </c>
       <c r="H44" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I44" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J44" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>40074094.32</v>
       </c>
-      <c r="K44" s="275">
+      <c r="K44" s="156">
         <v>4300000</v>
       </c>
       <c r="L44" s="156">
@@ -52501,19 +52491,19 @@
         <v>0</v>
       </c>
       <c r="O44" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>6400000</v>
       </c>
       <c r="P44" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5818181.8181818174</v>
       </c>
       <c r="Q44" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1518181.8181818174</v>
       </c>
       <c r="R44" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>26.396110031137738</v>
       </c>
     </row>
@@ -52524,37 +52514,37 @@
       <c r="B45" s="50" t="s">
         <v>622</v>
       </c>
-      <c r="C45" s="271">
+      <c r="C45" s="264">
         <v>70388694</v>
       </c>
-      <c r="D45" s="271">
+      <c r="D45" s="264">
         <v>0</v>
       </c>
       <c r="E45" s="156">
         <v>0</v>
       </c>
       <c r="F45" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>527915.20499999996</v>
       </c>
       <c r="G45" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>70916609.204999998</v>
       </c>
       <c r="H45" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I45" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J45" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>70916609.204999998</v>
       </c>
-      <c r="K45" s="275">
-        <v>6000000</v>
+      <c r="K45" s="156">
+        <v>6500000</v>
       </c>
       <c r="L45" s="156">
         <v>10200000</v>
@@ -52566,20 +52556,20 @@
         <v>0</v>
       </c>
       <c r="O45" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>10200000</v>
       </c>
       <c r="P45" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9272727.2727272715</v>
       </c>
       <c r="Q45" s="156">
-        <f t="shared" si="8"/>
-        <v>3272727.2727272715</v>
+        <f t="shared" si="9"/>
+        <v>2772727.2727272715</v>
       </c>
       <c r="R45" s="156">
-        <f t="shared" si="5"/>
-        <v>21.668963923750006</v>
+        <f t="shared" si="6"/>
+        <v>25.576482008360667</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
@@ -52589,36 +52579,36 @@
       <c r="B46" s="50" t="s">
         <v>627</v>
       </c>
-      <c r="C46" s="271">
+      <c r="C46" s="264">
         <v>118127844</v>
       </c>
-      <c r="D46" s="271">
+      <c r="D46" s="264">
         <v>0</v>
       </c>
       <c r="E46" s="156">
         <v>0</v>
       </c>
       <c r="F46" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>885958.83</v>
       </c>
       <c r="G46" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>119013802.83</v>
       </c>
       <c r="H46" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I46" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J46" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>119013802.83</v>
       </c>
-      <c r="K46" s="275">
+      <c r="K46" s="156">
         <v>6000000</v>
       </c>
       <c r="L46" s="156">
@@ -52631,19 +52621,19 @@
         <v>0</v>
       </c>
       <c r="O46" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>11300000</v>
       </c>
       <c r="P46" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10272727.272727272</v>
       </c>
       <c r="Q46" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4272727.2727272715</v>
       </c>
       <c r="R46" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>27.85429427936171</v>
       </c>
     </row>
@@ -52654,36 +52644,36 @@
       <c r="B47" s="50" t="s">
         <v>616</v>
       </c>
-      <c r="C47" s="271">
+      <c r="C47" s="264">
         <v>158338280</v>
       </c>
-      <c r="D47" s="271">
+      <c r="D47" s="264">
         <v>0</v>
       </c>
       <c r="E47" s="156">
         <v>0</v>
       </c>
       <c r="F47" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>1187537.0999999999</v>
       </c>
       <c r="G47" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>159525817.09999999</v>
       </c>
       <c r="H47" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I47" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J47" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>159525817.09999999</v>
       </c>
-      <c r="K47" s="275">
+      <c r="K47" s="156">
         <v>6000000</v>
       </c>
       <c r="L47" s="156">
@@ -52696,19 +52686,19 @@
         <v>0</v>
       </c>
       <c r="O47" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>12000000</v>
       </c>
       <c r="P47" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10909090.909090908</v>
       </c>
       <c r="Q47" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4909090.9090909082</v>
       </c>
       <c r="R47" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>32.495999779629635</v>
       </c>
     </row>
@@ -52719,36 +52709,36 @@
       <c r="B48" s="50" t="s">
         <v>644</v>
       </c>
-      <c r="C48" s="271">
+      <c r="C48" s="264">
         <v>36165510</v>
       </c>
-      <c r="D48" s="271">
+      <c r="D48" s="264">
         <v>0</v>
       </c>
       <c r="E48" s="156">
         <v>0</v>
       </c>
       <c r="F48" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>271241.32500000001</v>
       </c>
       <c r="G48" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>36436751.325000003</v>
       </c>
       <c r="H48" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I48" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J48" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>36436751.325000003</v>
       </c>
-      <c r="K48" s="275">
+      <c r="K48" s="156">
         <v>4000000</v>
       </c>
       <c r="L48" s="156">
@@ -52761,19 +52751,19 @@
         <v>0</v>
       </c>
       <c r="O48" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>6600000</v>
       </c>
       <c r="P48" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5999999.9999999991</v>
       </c>
       <c r="Q48" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1999999.9999999991</v>
       </c>
       <c r="R48" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>18.218375662500009</v>
       </c>
     </row>
@@ -52784,36 +52774,36 @@
       <c r="B49" s="50" t="s">
         <v>645</v>
       </c>
-      <c r="C49" s="271">
+      <c r="C49" s="264">
         <v>33300660</v>
       </c>
-      <c r="D49" s="271">
+      <c r="D49" s="264">
         <v>0</v>
       </c>
       <c r="E49" s="156">
         <v>0</v>
       </c>
       <c r="F49" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>249754.94999999998</v>
       </c>
       <c r="G49" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>33550414.949999999</v>
       </c>
       <c r="H49" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I49" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J49" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>33550414.949999999</v>
       </c>
-      <c r="K49" s="275">
+      <c r="K49" s="156">
         <v>4500000</v>
       </c>
       <c r="L49" s="156">
@@ -52826,19 +52816,19 @@
         <v>0</v>
       </c>
       <c r="O49" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>6700000</v>
       </c>
       <c r="P49" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6090909.0909090908</v>
       </c>
       <c r="Q49" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1590909.0909090908</v>
       </c>
       <c r="R49" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>21.088832254285716</v>
       </c>
     </row>
@@ -52849,36 +52839,36 @@
       <c r="B50" s="50" t="s">
         <v>676</v>
       </c>
-      <c r="C50" s="271">
+      <c r="C50" s="264">
         <v>37001880</v>
       </c>
-      <c r="D50" s="271">
+      <c r="D50" s="264">
         <v>0</v>
       </c>
       <c r="E50" s="156">
         <v>0</v>
       </c>
       <c r="F50" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>277514.09999999998</v>
       </c>
       <c r="G50" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>37279394.100000001</v>
       </c>
       <c r="H50" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I50" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J50" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37279394.100000001</v>
       </c>
-      <c r="K50" s="275">
+      <c r="K50" s="156">
         <v>4000000</v>
       </c>
       <c r="L50" s="156">
@@ -52891,19 +52881,19 @@
         <v>0</v>
       </c>
       <c r="O50" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>6500000</v>
       </c>
       <c r="P50" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5909090.9090909082</v>
       </c>
       <c r="Q50" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1909090.9090909082</v>
       </c>
       <c r="R50" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>19.527301671428582</v>
       </c>
     </row>
@@ -52914,36 +52904,36 @@
       <c r="B51" s="50" t="s">
         <v>677</v>
       </c>
-      <c r="C51" s="271">
+      <c r="C51" s="264">
         <v>37253429.559904575</v>
       </c>
-      <c r="D51" s="271">
+      <c r="D51" s="264">
         <v>0</v>
       </c>
       <c r="E51" s="156">
         <v>0</v>
       </c>
       <c r="F51" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>279400.72169928433</v>
       </c>
       <c r="G51" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>37532830.281603858</v>
       </c>
       <c r="H51" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I51" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J51" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37532830.281603858</v>
       </c>
-      <c r="K51" s="275">
+      <c r="K51" s="156">
         <v>4000000</v>
       </c>
       <c r="L51" s="156">
@@ -52956,19 +52946,19 @@
         <v>0</v>
       </c>
       <c r="O51" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>6700000</v>
       </c>
       <c r="P51" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6090909.0909090908</v>
       </c>
       <c r="Q51" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2090909.0909090908</v>
       </c>
       <c r="R51" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>17.950484047723585</v>
       </c>
     </row>
@@ -52979,36 +52969,36 @@
       <c r="B52" s="50" t="s">
         <v>678</v>
       </c>
-      <c r="C52" s="271">
+      <c r="C52" s="264">
         <v>39068570</v>
       </c>
-      <c r="D52" s="271">
+      <c r="D52" s="264">
         <v>0</v>
       </c>
       <c r="E52" s="156">
         <v>0</v>
       </c>
       <c r="F52" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>293014.27499999997</v>
       </c>
       <c r="G52" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>39361584.274999999</v>
       </c>
       <c r="H52" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I52" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J52" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39361584.274999999</v>
       </c>
-      <c r="K52" s="275">
+      <c r="K52" s="156">
         <v>4000000</v>
       </c>
       <c r="L52" s="156">
@@ -53021,19 +53011,19 @@
         <v>0</v>
       </c>
       <c r="O52" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>6700000</v>
       </c>
       <c r="P52" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6090909.0909090908</v>
       </c>
       <c r="Q52" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2090909.0909090908</v>
       </c>
       <c r="R52" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>18.825105522826085</v>
       </c>
     </row>
@@ -53044,36 +53034,36 @@
       <c r="B53" s="50" t="s">
         <v>679</v>
       </c>
-      <c r="C53" s="271">
+      <c r="C53" s="264">
         <v>42202840</v>
       </c>
-      <c r="D53" s="271">
+      <c r="D53" s="264">
         <v>0</v>
       </c>
       <c r="E53" s="156">
         <v>0</v>
       </c>
       <c r="F53" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>316521.3</v>
       </c>
       <c r="G53" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>42519361.299999997</v>
       </c>
       <c r="H53" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I53" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J53" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>42519361.299999997</v>
       </c>
-      <c r="K53" s="275">
+      <c r="K53" s="156">
         <v>4000000</v>
       </c>
       <c r="L53" s="156">
@@ -53086,19 +53076,19 @@
         <v>0</v>
       </c>
       <c r="O53" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>6700000</v>
       </c>
       <c r="P53" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6090909.0909090908</v>
       </c>
       <c r="Q53" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2090909.0909090908</v>
       </c>
       <c r="R53" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>20.335346708695653</v>
       </c>
     </row>
@@ -53109,36 +53099,36 @@
       <c r="B54" s="50" t="s">
         <v>680</v>
       </c>
-      <c r="C54" s="271">
+      <c r="C54" s="264">
         <v>49387054.533519998</v>
       </c>
-      <c r="D54" s="271">
+      <c r="D54" s="264">
         <v>0</v>
       </c>
       <c r="E54" s="156">
         <v>0</v>
       </c>
       <c r="F54" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>370402.9090014</v>
       </c>
       <c r="G54" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>49757457.442521401</v>
       </c>
       <c r="H54" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I54" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J54" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>49757457.442521401</v>
       </c>
-      <c r="K54" s="275">
+      <c r="K54" s="156">
         <v>4000000</v>
       </c>
       <c r="L54" s="156">
@@ -53151,19 +53141,19 @@
         <v>0</v>
       </c>
       <c r="O54" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>6600000</v>
       </c>
       <c r="P54" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5999999.9999999991</v>
       </c>
       <c r="Q54" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1999999.9999999991</v>
       </c>
       <c r="R54" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>24.87872872126071</v>
       </c>
     </row>
@@ -53174,36 +53164,36 @@
       <c r="B55" s="50" t="s">
         <v>710</v>
       </c>
-      <c r="C55" s="271">
+      <c r="C55" s="264">
         <v>141279580</v>
       </c>
-      <c r="D55" s="271">
+      <c r="D55" s="264">
         <v>0</v>
       </c>
       <c r="E55" s="156">
         <v>0</v>
       </c>
       <c r="F55" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>1059596.8499999999</v>
       </c>
       <c r="G55" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>142339176.84999999</v>
       </c>
       <c r="H55" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I55" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J55" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>142339176.84999999</v>
       </c>
-      <c r="K55" s="275">
+      <c r="K55" s="156">
         <v>5500000</v>
       </c>
       <c r="L55" s="156">
@@ -53216,19 +53206,19 @@
         <v>0</v>
       </c>
       <c r="O55" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>11300000</v>
       </c>
       <c r="P55" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10272727.272727272</v>
       </c>
       <c r="Q55" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4772727.2727272715</v>
       </c>
       <c r="R55" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>29.823446578095243</v>
       </c>
     </row>
@@ -53239,38 +53229,37 @@
       <c r="B56" s="50" t="s">
         <v>713</v>
       </c>
-      <c r="C56" s="271">
+      <c r="C56" s="264">
         <v>120106550</v>
       </c>
-      <c r="D56" s="271">
+      <c r="D56" s="264">
         <v>0</v>
       </c>
       <c r="E56" s="156">
         <v>0</v>
       </c>
       <c r="F56" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>900799.125</v>
       </c>
       <c r="G56" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>121007349.125</v>
       </c>
       <c r="H56" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I56" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>72000000</v>
       </c>
       <c r="J56" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>193007349.125</v>
       </c>
-      <c r="K56" s="275">
-        <f>5000000+3000000</f>
-        <v>8000000</v>
+      <c r="K56" s="156">
+        <v>7000000</v>
       </c>
       <c r="L56" s="156">
         <f>9800000*0.8</f>
@@ -53283,20 +53272,20 @@
         <v>8000000</v>
       </c>
       <c r="O56" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>15840000</v>
       </c>
       <c r="P56" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>14399999.999999998</v>
       </c>
       <c r="Q56" s="156">
-        <f t="shared" si="8"/>
-        <v>6399999.9999999981</v>
+        <f t="shared" si="9"/>
+        <v>7399999.9999999981</v>
       </c>
       <c r="R56" s="156">
-        <f t="shared" si="5"/>
-        <v>30.15739830078126</v>
+        <f t="shared" si="6"/>
+        <v>26.082074206081089</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
@@ -53306,36 +53295,36 @@
       <c r="B57" s="50" t="s">
         <v>716</v>
       </c>
-      <c r="C57" s="271">
+      <c r="C57" s="264">
         <v>91642910</v>
       </c>
-      <c r="D57" s="271">
+      <c r="D57" s="264">
         <v>0</v>
       </c>
       <c r="E57" s="156">
         <v>0</v>
       </c>
       <c r="F57" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>687321.82499999995</v>
       </c>
       <c r="G57" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>92330231.825000003</v>
       </c>
       <c r="H57" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I57" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J57" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>92330231.825000003</v>
       </c>
-      <c r="K57" s="275">
+      <c r="K57" s="156">
         <v>7500000</v>
       </c>
       <c r="L57" s="156">
@@ -53348,19 +53337,19 @@
         <v>0</v>
       </c>
       <c r="O57" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>13300000</v>
       </c>
       <c r="P57" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>12090909.09090909</v>
       </c>
       <c r="Q57" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4590909.0909090899</v>
       </c>
       <c r="R57" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>20.111535645049511</v>
       </c>
     </row>
@@ -53371,36 +53360,36 @@
       <c r="B58" s="50" t="s">
         <v>719</v>
       </c>
-      <c r="C58" s="271">
+      <c r="C58" s="264">
         <v>108072480</v>
       </c>
-      <c r="D58" s="271">
+      <c r="D58" s="264">
         <v>0</v>
       </c>
       <c r="E58" s="156">
         <v>0</v>
       </c>
       <c r="F58" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>810543.6</v>
       </c>
       <c r="G58" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>108883023.59999999</v>
       </c>
       <c r="H58" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I58" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J58" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>108883023.59999999</v>
       </c>
-      <c r="K58" s="275">
+      <c r="K58" s="156">
         <v>5000000</v>
       </c>
       <c r="L58" s="156">
@@ -53413,19 +53402,19 @@
         <v>0</v>
       </c>
       <c r="O58" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>10000000</v>
       </c>
       <c r="P58" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9090909.0909090899</v>
       </c>
       <c r="Q58" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4090909.0909090899</v>
       </c>
       <c r="R58" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>26.615850213333339</v>
       </c>
     </row>
@@ -53436,36 +53425,36 @@
       <c r="B59" s="50" t="s">
         <v>731</v>
       </c>
-      <c r="C59" s="271">
+      <c r="C59" s="264">
         <v>82592868</v>
       </c>
-      <c r="D59" s="271">
+      <c r="D59" s="264">
         <v>0</v>
       </c>
       <c r="E59" s="156">
         <v>0</v>
       </c>
       <c r="F59" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>619446.51</v>
       </c>
       <c r="G59" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>83212314.510000005</v>
       </c>
       <c r="H59" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I59" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J59" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>83212314.510000005</v>
       </c>
-      <c r="K59" s="275">
+      <c r="K59" s="156">
         <v>5000000</v>
       </c>
       <c r="L59" s="156">
@@ -53478,19 +53467,19 @@
         <v>0</v>
       </c>
       <c r="O59" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>9500000</v>
       </c>
       <c r="P59" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8636363.6363636348</v>
       </c>
       <c r="Q59" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3636363.6363636348</v>
       </c>
       <c r="R59" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>22.883386490250011</v>
       </c>
     </row>
@@ -53501,36 +53490,36 @@
       <c r="B60" s="50" t="s">
         <v>731</v>
       </c>
-      <c r="C60" s="271">
+      <c r="C60" s="264">
         <v>82592868</v>
       </c>
-      <c r="D60" s="271">
+      <c r="D60" s="264">
         <v>0</v>
       </c>
       <c r="E60" s="156">
         <v>0</v>
       </c>
       <c r="F60" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>619446.51</v>
       </c>
       <c r="G60" s="156">
-        <f t="shared" ref="G60" si="19">SUM(C60:F60)</f>
+        <f t="shared" si="2"/>
         <v>83212314.510000005</v>
       </c>
       <c r="H60" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I60" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>50400000</v>
       </c>
       <c r="J60" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>133612314.51000001</v>
       </c>
-      <c r="K60" s="275">
+      <c r="K60" s="156">
         <v>5000000</v>
       </c>
       <c r="L60" s="156">
@@ -53544,19 +53533,19 @@
         <v>5600000</v>
       </c>
       <c r="O60" s="156">
-        <f t="shared" ref="O60" si="20">SUM(L60:N60)</f>
+        <f t="shared" si="7"/>
         <v>13200000</v>
       </c>
       <c r="P60" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>11999999.999999998</v>
       </c>
       <c r="Q60" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6999999.9999999981</v>
       </c>
       <c r="R60" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>19.087473501428576</v>
       </c>
     </row>
@@ -53567,36 +53556,36 @@
       <c r="B61" s="50" t="s">
         <v>738</v>
       </c>
-      <c r="C61" s="271">
+      <c r="C61" s="264">
         <v>37582700</v>
       </c>
-      <c r="D61" s="271">
+      <c r="D61" s="264">
         <v>0</v>
       </c>
       <c r="E61" s="156">
         <v>0</v>
       </c>
       <c r="F61" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>281870.25</v>
       </c>
       <c r="G61" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>37864570.25</v>
       </c>
       <c r="H61" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I61" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J61" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>37864570.25</v>
       </c>
-      <c r="K61" s="275">
+      <c r="K61" s="156">
         <v>4000000</v>
       </c>
       <c r="L61" s="156">
@@ -53609,19 +53598,19 @@
         <v>0</v>
       </c>
       <c r="O61" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>6400000</v>
       </c>
       <c r="P61" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5818181.8181818174</v>
       </c>
       <c r="Q61" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1818181.8181818174</v>
       </c>
       <c r="R61" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>20.825513637500009</v>
       </c>
     </row>
@@ -53632,36 +53621,36 @@
       <c r="B62" s="50" t="s">
         <v>748</v>
       </c>
-      <c r="C62" s="271">
+      <c r="C62" s="264">
         <v>110700000</v>
       </c>
-      <c r="D62" s="271">
+      <c r="D62" s="264">
         <v>0</v>
       </c>
       <c r="E62" s="156">
         <v>0</v>
       </c>
       <c r="F62" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>830250</v>
       </c>
       <c r="G62" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>111530250</v>
       </c>
       <c r="H62" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I62" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J62" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>111530250</v>
       </c>
-      <c r="K62" s="275">
+      <c r="K62" s="156">
         <v>5000000</v>
       </c>
       <c r="L62" s="156">
@@ -53674,19 +53663,19 @@
         <v>0</v>
       </c>
       <c r="O62" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>9000000</v>
       </c>
       <c r="P62" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8181818.1818181807</v>
       </c>
       <c r="Q62" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3181818.1818181807</v>
       </c>
       <c r="R62" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>35.052364285714297</v>
       </c>
     </row>
@@ -53697,36 +53686,36 @@
       <c r="B63" s="50" t="s">
         <v>749</v>
       </c>
-      <c r="C63" s="271">
+      <c r="C63" s="264">
         <v>44223000</v>
       </c>
-      <c r="D63" s="271">
+      <c r="D63" s="264">
         <v>0</v>
       </c>
       <c r="E63" s="156">
         <v>0</v>
       </c>
       <c r="F63" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>331672.5</v>
       </c>
       <c r="G63" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>44554672.5</v>
       </c>
       <c r="H63" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I63" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J63" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>44554672.5</v>
       </c>
-      <c r="K63" s="275">
+      <c r="K63" s="156">
         <v>4500000</v>
       </c>
       <c r="L63" s="156">
@@ -53739,19 +53728,19 @@
         <v>0</v>
       </c>
       <c r="O63" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>6400000</v>
       </c>
       <c r="P63" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5818181.8181818174</v>
       </c>
       <c r="Q63" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1318181.8181818174</v>
       </c>
       <c r="R63" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>33.800096379310361</v>
       </c>
     </row>
@@ -53762,36 +53751,36 @@
       <c r="B64" s="50" t="s">
         <v>750</v>
       </c>
-      <c r="C64" s="271">
+      <c r="C64" s="264">
         <v>117252198</v>
       </c>
-      <c r="D64" s="271">
+      <c r="D64" s="264">
         <v>0</v>
       </c>
       <c r="E64" s="156">
         <v>0</v>
       </c>
       <c r="F64" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>879391.48499999999</v>
       </c>
       <c r="G64" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>118131589.485</v>
       </c>
       <c r="H64" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I64" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J64" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>118131589.485</v>
       </c>
-      <c r="K64" s="275">
+      <c r="K64" s="156">
         <v>5500000</v>
       </c>
       <c r="L64" s="156">
@@ -53804,19 +53793,19 @@
         <v>0</v>
       </c>
       <c r="O64" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>9400000</v>
       </c>
       <c r="P64" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8545454.5454545449</v>
       </c>
       <c r="Q64" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3045454.5454545449</v>
       </c>
       <c r="R64" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>38.789477144328366</v>
       </c>
     </row>
@@ -53827,36 +53816,36 @@
       <c r="B65" s="50" t="s">
         <v>751</v>
       </c>
-      <c r="C65" s="271">
+      <c r="C65" s="264">
         <v>110700000</v>
       </c>
-      <c r="D65" s="271">
+      <c r="D65" s="264">
         <v>0</v>
       </c>
       <c r="E65" s="156">
         <v>0</v>
       </c>
       <c r="F65" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>830250</v>
       </c>
       <c r="G65" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>111530250</v>
       </c>
       <c r="H65" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I65" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J65" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>111530250</v>
       </c>
-      <c r="K65" s="275">
+      <c r="K65" s="156">
         <v>5000000</v>
       </c>
       <c r="L65" s="156">
@@ -53869,19 +53858,19 @@
         <v>0</v>
       </c>
       <c r="O65" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>9400000</v>
       </c>
       <c r="P65" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8545454.5454545449</v>
       </c>
       <c r="Q65" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3545454.5454545449</v>
       </c>
       <c r="R65" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>31.457250000000005</v>
       </c>
     </row>
@@ -53892,36 +53881,36 @@
       <c r="B66" s="50" t="s">
         <v>746</v>
       </c>
-      <c r="C66" s="271">
+      <c r="C66" s="264">
         <v>40000000</v>
       </c>
-      <c r="D66" s="271">
+      <c r="D66" s="264">
         <v>0</v>
       </c>
       <c r="E66" s="156">
         <v>0</v>
       </c>
       <c r="F66" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>300000</v>
       </c>
       <c r="G66" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>40300000</v>
       </c>
       <c r="H66" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I66" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J66" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>40300000</v>
       </c>
-      <c r="K66" s="275">
+      <c r="K66" s="156">
         <v>4000000</v>
       </c>
       <c r="L66" s="156">
@@ -53934,19 +53923,19 @@
         <v>0</v>
       </c>
       <c r="O66" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>6700000</v>
       </c>
       <c r="P66" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6090909.0909090908</v>
       </c>
       <c r="Q66" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2090909.0909090908</v>
       </c>
       <c r="R66" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>19.273913043478263</v>
       </c>
     </row>
@@ -53957,36 +53946,36 @@
       <c r="B67" s="50" t="s">
         <v>615</v>
       </c>
-      <c r="C67" s="271">
+      <c r="C67" s="264">
         <v>40000000</v>
       </c>
-      <c r="D67" s="271">
+      <c r="D67" s="264">
         <v>0</v>
       </c>
       <c r="E67" s="156">
         <v>0</v>
       </c>
       <c r="F67" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
         <v>300000</v>
       </c>
       <c r="G67" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" si="2"/>
         <v>40300000</v>
       </c>
       <c r="H67" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I67" s="156">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J67" s="156">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>40300000</v>
       </c>
-      <c r="K67" s="275">
+      <c r="K67" s="156">
         <v>5500000</v>
       </c>
       <c r="L67" s="156">
@@ -53999,19 +53988,19 @@
         <v>0</v>
       </c>
       <c r="O67" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>7500000</v>
       </c>
       <c r="P67" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6818181.8181818174</v>
       </c>
       <c r="Q67" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1318181.8181818174</v>
       </c>
       <c r="R67" s="156">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>30.572413793103465</v>
       </c>
     </row>
@@ -54022,36 +54011,36 @@
       <c r="B68" s="50" t="s">
         <v>780</v>
       </c>
-      <c r="C68" s="271">
+      <c r="C68" s="264">
         <v>115000000</v>
       </c>
-      <c r="D68" s="271">
+      <c r="D68" s="264">
         <v>0</v>
       </c>
       <c r="E68" s="156">
         <v>0</v>
       </c>
       <c r="F68" s="156">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="F68:F92" si="10">(C68*12%+(C68/2)*12%)/24</f>
         <v>862500</v>
       </c>
       <c r="G68" s="156">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G68:G92" si="11">SUM(C68:F68)</f>
         <v>115862500</v>
       </c>
       <c r="H68" s="156">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="H68:H92" si="12">M68*6/1.1</f>
         <v>0</v>
       </c>
       <c r="I68" s="156">
-        <f t="shared" ref="I68:I92" si="21">N68*9</f>
+        <f t="shared" ref="I68:I92" si="13">N68*9</f>
         <v>0</v>
       </c>
       <c r="J68" s="156">
-        <f t="shared" ref="J68:J92" si="22">G68+H68+I68</f>
+        <f t="shared" ref="J68:J92" si="14">G68+H68+I68</f>
         <v>115862500</v>
       </c>
-      <c r="K68" s="275">
+      <c r="K68" s="156">
         <v>6000000</v>
       </c>
       <c r="L68" s="156">
@@ -54064,19 +54053,19 @@
         <v>0</v>
       </c>
       <c r="O68" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v>10500000</v>
       </c>
       <c r="P68" s="156">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9545454.5454545449</v>
       </c>
       <c r="Q68" s="156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3545454.5454545449</v>
       </c>
       <c r="R68" s="156">
-        <f t="shared" ref="R68:R92" si="23">J68/Q68</f>
+        <f t="shared" ref="R68:R92" si="15">J68/Q68</f>
         <v>32.679166666666674</v>
       </c>
     </row>
@@ -54084,39 +54073,39 @@
       <c r="A69" s="120">
         <v>66</v>
       </c>
-      <c r="B69" s="277" t="s">
+      <c r="B69" s="268" t="s">
         <v>787</v>
       </c>
-      <c r="C69" s="271">
+      <c r="C69" s="264">
         <v>40000000</v>
       </c>
-      <c r="D69" s="271">
+      <c r="D69" s="264">
         <v>0</v>
       </c>
       <c r="E69" s="156">
         <v>0</v>
       </c>
       <c r="F69" s="156">
+        <f t="shared" si="10"/>
+        <v>300000</v>
+      </c>
+      <c r="G69" s="156">
+        <f t="shared" si="11"/>
+        <v>40300000</v>
+      </c>
+      <c r="H69" s="156">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I69" s="156">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="156">
         <f t="shared" si="14"/>
-        <v>300000</v>
-      </c>
-      <c r="G69" s="156">
-        <f t="shared" si="18"/>
         <v>40300000</v>
       </c>
-      <c r="H69" s="156">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="I69" s="156">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="156">
-        <f t="shared" si="22"/>
-        <v>40300000</v>
-      </c>
-      <c r="K69" s="275">
+      <c r="K69" s="156">
         <v>4000000</v>
       </c>
       <c r="L69" s="95">
@@ -54129,19 +54118,19 @@
         <v>0</v>
       </c>
       <c r="O69" s="156">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="O69:O92" si="16">SUM(L69:N69)</f>
         <v>6400000</v>
       </c>
       <c r="P69" s="156">
-        <f t="shared" ref="P69:P92" si="24">O69/1.1</f>
+        <f t="shared" ref="P69:P92" si="17">O69/1.1</f>
         <v>5818181.8181818174</v>
       </c>
       <c r="Q69" s="156">
-        <f t="shared" ref="Q69:Q92" si="25">P69-K69</f>
+        <f t="shared" ref="Q69:Q92" si="18">P69-K69</f>
         <v>1818181.8181818174</v>
       </c>
       <c r="R69" s="156">
-        <f t="shared" si="23"/>
+        <f t="shared" si="15"/>
         <v>22.16500000000001</v>
       </c>
     </row>
@@ -54149,39 +54138,39 @@
       <c r="A70" s="120">
         <v>67</v>
       </c>
-      <c r="B70" s="277" t="s">
+      <c r="B70" s="268" t="s">
         <v>796</v>
       </c>
-      <c r="C70" s="271">
+      <c r="C70" s="264">
         <v>115000000</v>
       </c>
-      <c r="D70" s="271">
+      <c r="D70" s="264">
         <v>0</v>
       </c>
       <c r="E70" s="156">
         <v>0</v>
       </c>
       <c r="F70" s="156">
+        <f t="shared" si="10"/>
+        <v>862500</v>
+      </c>
+      <c r="G70" s="156">
+        <f t="shared" si="11"/>
+        <v>115862500</v>
+      </c>
+      <c r="H70" s="156">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I70" s="156">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="156">
         <f t="shared" si="14"/>
-        <v>862500</v>
-      </c>
-      <c r="G70" s="156">
-        <f t="shared" si="18"/>
         <v>115862500</v>
       </c>
-      <c r="H70" s="156">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="156">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="J70" s="156">
-        <f t="shared" si="22"/>
-        <v>115862500</v>
-      </c>
-      <c r="K70" s="275">
+      <c r="K70" s="156">
         <v>7000000</v>
       </c>
       <c r="L70" s="156">
@@ -54194,19 +54183,19 @@
         <v>0</v>
       </c>
       <c r="O70" s="156">
+        <f t="shared" si="16"/>
+        <v>11400000</v>
+      </c>
+      <c r="P70" s="156">
         <f t="shared" si="17"/>
-        <v>11400000</v>
-      </c>
-      <c r="P70" s="156">
-        <f t="shared" si="24"/>
         <v>10363636.363636363</v>
       </c>
       <c r="Q70" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>3363636.3636363633</v>
       </c>
       <c r="R70" s="156">
-        <f t="shared" si="23"/>
+        <f t="shared" si="15"/>
         <v>34.445608108108111</v>
       </c>
     </row>
@@ -54214,39 +54203,39 @@
       <c r="A71" s="120">
         <v>68</v>
       </c>
-      <c r="B71" s="277" t="s">
+      <c r="B71" s="268" t="s">
         <v>800</v>
       </c>
-      <c r="C71" s="271">
+      <c r="C71" s="264">
         <v>40000000</v>
       </c>
-      <c r="D71" s="271">
+      <c r="D71" s="264">
         <v>0</v>
       </c>
       <c r="E71" s="156">
         <v>0</v>
       </c>
       <c r="F71" s="156">
+        <f t="shared" si="10"/>
+        <v>300000</v>
+      </c>
+      <c r="G71" s="156">
+        <f t="shared" si="11"/>
+        <v>40300000</v>
+      </c>
+      <c r="H71" s="156">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I71" s="156">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="J71" s="156">
         <f t="shared" si="14"/>
-        <v>300000</v>
-      </c>
-      <c r="G71" s="156">
-        <f t="shared" si="18"/>
         <v>40300000</v>
       </c>
-      <c r="H71" s="156">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="I71" s="156">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="J71" s="156">
-        <f t="shared" si="22"/>
-        <v>40300000</v>
-      </c>
-      <c r="K71" s="275">
+      <c r="K71" s="156">
         <v>4000000</v>
       </c>
       <c r="L71" s="95">
@@ -54259,19 +54248,19 @@
         <v>0</v>
       </c>
       <c r="O71" s="156">
+        <f t="shared" si="16"/>
+        <v>6400000</v>
+      </c>
+      <c r="P71" s="156">
         <f t="shared" si="17"/>
-        <v>6400000</v>
-      </c>
-      <c r="P71" s="156">
-        <f t="shared" si="24"/>
         <v>5818181.8181818174</v>
       </c>
       <c r="Q71" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1818181.8181818174</v>
       </c>
       <c r="R71" s="156">
-        <f t="shared" si="23"/>
+        <f t="shared" si="15"/>
         <v>22.16500000000001</v>
       </c>
     </row>
@@ -54279,39 +54268,39 @@
       <c r="A72" s="120">
         <v>69</v>
       </c>
-      <c r="B72" s="277" t="s">
+      <c r="B72" s="268" t="s">
         <v>801</v>
       </c>
-      <c r="C72" s="271">
+      <c r="C72" s="264">
         <v>40000000</v>
       </c>
-      <c r="D72" s="271">
+      <c r="D72" s="264">
         <v>0</v>
       </c>
       <c r="E72" s="156">
         <v>0</v>
       </c>
       <c r="F72" s="156">
+        <f t="shared" si="10"/>
+        <v>300000</v>
+      </c>
+      <c r="G72" s="156">
+        <f t="shared" si="11"/>
+        <v>40300000</v>
+      </c>
+      <c r="H72" s="156">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I72" s="156">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="J72" s="156">
         <f t="shared" si="14"/>
-        <v>300000</v>
-      </c>
-      <c r="G72" s="156">
-        <f t="shared" si="18"/>
         <v>40300000</v>
       </c>
-      <c r="H72" s="156">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="I72" s="156">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="J72" s="156">
-        <f t="shared" si="22"/>
-        <v>40300000</v>
-      </c>
-      <c r="K72" s="275">
+      <c r="K72" s="156">
         <v>4000000</v>
       </c>
       <c r="L72" s="95">
@@ -54324,19 +54313,19 @@
         <v>0</v>
       </c>
       <c r="O72" s="156">
+        <f t="shared" si="16"/>
+        <v>6400000</v>
+      </c>
+      <c r="P72" s="156">
         <f t="shared" si="17"/>
-        <v>6400000</v>
-      </c>
-      <c r="P72" s="156">
-        <f t="shared" si="24"/>
         <v>5818181.8181818174</v>
       </c>
       <c r="Q72" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1818181.8181818174</v>
       </c>
       <c r="R72" s="156">
-        <f t="shared" si="23"/>
+        <f t="shared" si="15"/>
         <v>22.16500000000001</v>
       </c>
     </row>
@@ -54344,40 +54333,40 @@
       <c r="A73" s="120">
         <v>70</v>
       </c>
-      <c r="B73" s="270" t="s">
+      <c r="B73" s="263" t="s">
         <v>254</v>
       </c>
-      <c r="C73" s="271">
+      <c r="C73" s="264">
         <v>201971209.00000003</v>
       </c>
-      <c r="D73" s="271">
+      <c r="D73" s="264">
         <v>0</v>
       </c>
       <c r="E73" s="156">
         <v>0</v>
       </c>
       <c r="F73" s="156">
-        <f t="shared" ref="F73:F92" si="26">(C73*12%+(C73/2)*12%)/54</f>
-        <v>673237.3633333334</v>
+        <f t="shared" si="10"/>
+        <v>1514784.0675000001</v>
       </c>
       <c r="G73" s="156">
-        <f t="shared" si="18"/>
-        <v>202644446.36333337</v>
+        <f t="shared" si="11"/>
+        <v>203485993.06750003</v>
       </c>
       <c r="H73" s="156">
-        <f>M73*6/1.1</f>
+        <f t="shared" si="12"/>
         <v>36000000</v>
       </c>
       <c r="I73" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>63000000</v>
       </c>
       <c r="J73" s="156">
-        <f t="shared" si="22"/>
-        <v>301644446.36333334</v>
+        <f t="shared" si="14"/>
+        <v>302485993.0675</v>
       </c>
       <c r="K73" s="156">
-        <v>9000000</v>
+        <v>8300000</v>
       </c>
       <c r="L73" s="156">
         <f>11900000*0.7</f>
@@ -54390,57 +54379,57 @@
         <v>7000000</v>
       </c>
       <c r="O73" s="156">
+        <f t="shared" si="16"/>
+        <v>21930000</v>
+      </c>
+      <c r="P73" s="156">
         <f t="shared" si="17"/>
-        <v>21930000</v>
-      </c>
-      <c r="P73" s="156">
-        <f t="shared" si="24"/>
         <v>19936363.636363633</v>
       </c>
       <c r="Q73" s="156">
-        <f t="shared" si="25"/>
-        <v>10936363.636363633</v>
+        <f t="shared" si="18"/>
+        <v>11636363.636363633</v>
       </c>
       <c r="R73" s="156">
-        <f t="shared" si="23"/>
-        <v>27.581786450512617</v>
+        <f t="shared" si="15"/>
+        <v>25.994890029238288</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="120">
         <v>71</v>
       </c>
-      <c r="B74" s="270" t="s">
+      <c r="B74" s="263" t="s">
         <v>812</v>
       </c>
-      <c r="C74" s="271">
+      <c r="C74" s="264">
         <v>104301307.5</v>
       </c>
-      <c r="D74" s="271">
+      <c r="D74" s="264">
         <v>0</v>
       </c>
       <c r="E74" s="156">
         <v>0</v>
       </c>
       <c r="F74" s="156">
-        <f t="shared" si="26"/>
-        <v>347671.02500000002</v>
+        <f t="shared" si="10"/>
+        <v>782259.80625000002</v>
       </c>
       <c r="G74" s="156">
-        <f t="shared" si="18"/>
-        <v>104648978.52500001</v>
+        <f t="shared" si="11"/>
+        <v>105083567.30625001</v>
       </c>
       <c r="H74" s="156">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I74" s="156">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I74" s="156">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="J74" s="156">
-        <f t="shared" si="22"/>
-        <v>104648978.52500001</v>
+        <f t="shared" si="14"/>
+        <v>105083567.30625001</v>
       </c>
       <c r="K74" s="156">
         <v>5000000</v>
@@ -54455,57 +54444,57 @@
         <v>0</v>
       </c>
       <c r="O74" s="156">
+        <f t="shared" si="16"/>
+        <v>9300000</v>
+      </c>
+      <c r="P74" s="156">
         <f t="shared" si="17"/>
-        <v>9300000</v>
-      </c>
-      <c r="P74" s="156">
-        <f t="shared" si="24"/>
         <v>8454545.4545454532</v>
       </c>
       <c r="Q74" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>3454545.4545454532</v>
       </c>
       <c r="R74" s="156">
-        <f t="shared" si="23"/>
-        <v>30.293125362500014</v>
+        <f t="shared" si="15"/>
+        <v>30.418927378125012</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="120">
         <v>72</v>
       </c>
-      <c r="B75" s="270" t="s">
+      <c r="B75" s="263" t="s">
         <v>823</v>
       </c>
-      <c r="C75" s="271">
+      <c r="C75" s="264">
         <v>8750000</v>
       </c>
-      <c r="D75" s="271">
+      <c r="D75" s="264">
         <v>0</v>
       </c>
       <c r="E75" s="156">
         <v>0</v>
       </c>
       <c r="F75" s="156">
-        <f t="shared" si="26"/>
-        <v>29166.666666666668</v>
+        <f t="shared" si="10"/>
+        <v>65625</v>
       </c>
       <c r="G75" s="156">
-        <f t="shared" si="18"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="11"/>
+        <v>8815625</v>
       </c>
       <c r="H75" s="156">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I75" s="156">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I75" s="156">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="J75" s="156">
-        <f t="shared" si="22"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="14"/>
+        <v>8815625</v>
       </c>
       <c r="K75" s="156">
         <v>0</v>
@@ -54520,57 +54509,57 @@
         <v>0</v>
       </c>
       <c r="O75" s="156">
+        <f t="shared" si="16"/>
+        <v>1500000</v>
+      </c>
+      <c r="P75" s="156">
         <f t="shared" si="17"/>
-        <v>1500000</v>
-      </c>
-      <c r="P75" s="156">
-        <f t="shared" si="24"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="Q75" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="R75" s="156">
-        <f t="shared" si="23"/>
-        <v>6.4380555555555556</v>
+        <f t="shared" si="15"/>
+        <v>6.4647916666666676</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="120">
         <v>73</v>
       </c>
-      <c r="B76" s="270" t="s">
+      <c r="B76" s="263" t="s">
         <v>824</v>
       </c>
-      <c r="C76" s="271">
+      <c r="C76" s="264">
         <v>8750000</v>
       </c>
-      <c r="D76" s="271">
+      <c r="D76" s="264">
         <v>0</v>
       </c>
       <c r="E76" s="156">
         <v>0</v>
       </c>
       <c r="F76" s="156">
-        <f t="shared" si="26"/>
-        <v>29166.666666666668</v>
+        <f t="shared" si="10"/>
+        <v>65625</v>
       </c>
       <c r="G76" s="156">
-        <f t="shared" si="18"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="11"/>
+        <v>8815625</v>
       </c>
       <c r="H76" s="156">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I76" s="156">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I76" s="156">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="J76" s="156">
-        <f t="shared" si="22"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="14"/>
+        <v>8815625</v>
       </c>
       <c r="K76" s="156">
         <v>0</v>
@@ -54585,57 +54574,57 @@
         <v>0</v>
       </c>
       <c r="O76" s="156">
+        <f t="shared" si="16"/>
+        <v>1500000</v>
+      </c>
+      <c r="P76" s="156">
         <f t="shared" si="17"/>
-        <v>1500000</v>
-      </c>
-      <c r="P76" s="156">
-        <f t="shared" si="24"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="Q76" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="R76" s="156">
-        <f t="shared" si="23"/>
-        <v>6.4380555555555556</v>
+        <f t="shared" si="15"/>
+        <v>6.4647916666666676</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="120">
         <v>74</v>
       </c>
-      <c r="B77" s="270" t="s">
+      <c r="B77" s="263" t="s">
         <v>825</v>
       </c>
-      <c r="C77" s="271">
+      <c r="C77" s="264">
         <v>8750000</v>
       </c>
-      <c r="D77" s="271">
+      <c r="D77" s="264">
         <v>0</v>
       </c>
       <c r="E77" s="156">
         <v>0</v>
       </c>
       <c r="F77" s="156">
-        <f t="shared" si="26"/>
-        <v>29166.666666666668</v>
+        <f t="shared" si="10"/>
+        <v>65625</v>
       </c>
       <c r="G77" s="156">
-        <f t="shared" si="18"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="11"/>
+        <v>8815625</v>
       </c>
       <c r="H77" s="156">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I77" s="156">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I77" s="156">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
       <c r="J77" s="156">
-        <f t="shared" si="22"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="14"/>
+        <v>8815625</v>
       </c>
       <c r="K77" s="156">
         <v>0</v>
@@ -54650,57 +54639,57 @@
         <v>0</v>
       </c>
       <c r="O77" s="156">
+        <f t="shared" si="16"/>
+        <v>1500000</v>
+      </c>
+      <c r="P77" s="156">
         <f t="shared" si="17"/>
-        <v>1500000</v>
-      </c>
-      <c r="P77" s="156">
-        <f t="shared" si="24"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="Q77" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="R77" s="156">
-        <f t="shared" si="23"/>
-        <v>6.4380555555555556</v>
+        <f t="shared" si="15"/>
+        <v>6.4647916666666676</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="120">
         <v>75</v>
       </c>
-      <c r="B78" s="270" t="s">
+      <c r="B78" s="263" t="s">
         <v>826</v>
       </c>
-      <c r="C78" s="271">
+      <c r="C78" s="264">
         <v>8750000</v>
       </c>
-      <c r="D78" s="271">
+      <c r="D78" s="264">
         <v>0</v>
       </c>
       <c r="E78" s="156">
         <v>0</v>
       </c>
       <c r="F78" s="156">
-        <f t="shared" si="26"/>
-        <v>29166.666666666668</v>
+        <f t="shared" si="10"/>
+        <v>65625</v>
       </c>
       <c r="G78" s="156">
-        <f t="shared" si="18"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="11"/>
+        <v>8815625</v>
       </c>
       <c r="H78" s="156">
-        <f t="shared" ref="H78:H92" si="27">M78*6</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I78" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J78" s="156">
-        <f t="shared" si="22"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="14"/>
+        <v>8815625</v>
       </c>
       <c r="K78" s="156">
         <v>0</v>
@@ -54715,57 +54704,57 @@
         <v>0</v>
       </c>
       <c r="O78" s="156">
+        <f t="shared" si="16"/>
+        <v>1500000</v>
+      </c>
+      <c r="P78" s="156">
         <f t="shared" si="17"/>
-        <v>1500000</v>
-      </c>
-      <c r="P78" s="156">
-        <f t="shared" si="24"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="Q78" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="R78" s="156">
-        <f t="shared" si="23"/>
-        <v>6.4380555555555556</v>
+        <f t="shared" si="15"/>
+        <v>6.4647916666666676</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="120">
         <v>76</v>
       </c>
-      <c r="B79" s="270" t="s">
+      <c r="B79" s="263" t="s">
         <v>827</v>
       </c>
-      <c r="C79" s="271">
+      <c r="C79" s="264">
         <v>8750000</v>
       </c>
-      <c r="D79" s="271">
+      <c r="D79" s="264">
         <v>0</v>
       </c>
       <c r="E79" s="156">
         <v>0</v>
       </c>
       <c r="F79" s="156">
-        <f t="shared" si="26"/>
-        <v>29166.666666666668</v>
+        <f t="shared" si="10"/>
+        <v>65625</v>
       </c>
       <c r="G79" s="156">
-        <f t="shared" si="18"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="11"/>
+        <v>8815625</v>
       </c>
       <c r="H79" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I79" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J79" s="156">
-        <f t="shared" si="22"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="14"/>
+        <v>8815625</v>
       </c>
       <c r="K79" s="156">
         <v>0</v>
@@ -54780,57 +54769,57 @@
         <v>0</v>
       </c>
       <c r="O79" s="156">
+        <f t="shared" si="16"/>
+        <v>1500000</v>
+      </c>
+      <c r="P79" s="156">
         <f t="shared" si="17"/>
-        <v>1500000</v>
-      </c>
-      <c r="P79" s="156">
-        <f t="shared" si="24"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="Q79" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="R79" s="156">
-        <f t="shared" si="23"/>
-        <v>6.4380555555555556</v>
+        <f t="shared" si="15"/>
+        <v>6.4647916666666676</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" s="120">
         <v>77</v>
       </c>
-      <c r="B80" s="270" t="s">
+      <c r="B80" s="263" t="s">
         <v>828</v>
       </c>
-      <c r="C80" s="271">
+      <c r="C80" s="264">
         <v>8750000</v>
       </c>
-      <c r="D80" s="271">
+      <c r="D80" s="264">
         <v>0</v>
       </c>
       <c r="E80" s="156">
         <v>0</v>
       </c>
       <c r="F80" s="156">
-        <f t="shared" si="26"/>
-        <v>29166.666666666668</v>
+        <f t="shared" si="10"/>
+        <v>65625</v>
       </c>
       <c r="G80" s="156">
-        <f t="shared" si="18"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="11"/>
+        <v>8815625</v>
       </c>
       <c r="H80" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I80" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J80" s="156">
-        <f t="shared" si="22"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="14"/>
+        <v>8815625</v>
       </c>
       <c r="K80" s="156">
         <v>0</v>
@@ -54845,57 +54834,57 @@
         <v>0</v>
       </c>
       <c r="O80" s="156">
+        <f t="shared" si="16"/>
+        <v>1500000</v>
+      </c>
+      <c r="P80" s="156">
         <f t="shared" si="17"/>
-        <v>1500000</v>
-      </c>
-      <c r="P80" s="156">
-        <f t="shared" si="24"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="Q80" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="R80" s="156">
-        <f t="shared" si="23"/>
-        <v>6.4380555555555556</v>
+        <f t="shared" si="15"/>
+        <v>6.4647916666666676</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" s="120">
         <v>78</v>
       </c>
-      <c r="B81" s="270" t="s">
+      <c r="B81" s="263" t="s">
         <v>829</v>
       </c>
-      <c r="C81" s="271">
+      <c r="C81" s="264">
         <v>8750000</v>
       </c>
-      <c r="D81" s="271">
+      <c r="D81" s="264">
         <v>0</v>
       </c>
       <c r="E81" s="156">
         <v>0</v>
       </c>
       <c r="F81" s="156">
-        <f t="shared" si="26"/>
-        <v>29166.666666666668</v>
+        <f t="shared" si="10"/>
+        <v>65625</v>
       </c>
       <c r="G81" s="156">
-        <f t="shared" si="18"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="11"/>
+        <v>8815625</v>
       </c>
       <c r="H81" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I81" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J81" s="156">
-        <f t="shared" si="22"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="14"/>
+        <v>8815625</v>
       </c>
       <c r="K81" s="156">
         <v>0</v>
@@ -54910,57 +54899,57 @@
         <v>0</v>
       </c>
       <c r="O81" s="156">
+        <f t="shared" si="16"/>
+        <v>1500000</v>
+      </c>
+      <c r="P81" s="156">
         <f t="shared" si="17"/>
-        <v>1500000</v>
-      </c>
-      <c r="P81" s="156">
-        <f t="shared" si="24"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="Q81" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="R81" s="156">
-        <f t="shared" si="23"/>
-        <v>6.4380555555555556</v>
+        <f t="shared" si="15"/>
+        <v>6.4647916666666676</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="120">
         <v>79</v>
       </c>
-      <c r="B82" s="270" t="s">
+      <c r="B82" s="263" t="s">
         <v>830</v>
       </c>
-      <c r="C82" s="271">
+      <c r="C82" s="264">
         <v>8750000</v>
       </c>
-      <c r="D82" s="271">
+      <c r="D82" s="264">
         <v>0</v>
       </c>
       <c r="E82" s="156">
         <v>0</v>
       </c>
       <c r="F82" s="156">
-        <f t="shared" si="26"/>
-        <v>29166.666666666668</v>
+        <f t="shared" si="10"/>
+        <v>65625</v>
       </c>
       <c r="G82" s="156">
-        <f t="shared" si="18"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="11"/>
+        <v>8815625</v>
       </c>
       <c r="H82" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I82" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J82" s="156">
-        <f t="shared" si="22"/>
-        <v>8779166.666666666</v>
+        <f t="shared" si="14"/>
+        <v>8815625</v>
       </c>
       <c r="K82" s="156">
         <v>0</v>
@@ -54975,57 +54964,57 @@
         <v>0</v>
       </c>
       <c r="O82" s="156">
+        <f t="shared" si="16"/>
+        <v>1500000</v>
+      </c>
+      <c r="P82" s="156">
         <f t="shared" si="17"/>
-        <v>1500000</v>
-      </c>
-      <c r="P82" s="156">
-        <f t="shared" si="24"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="Q82" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1363636.3636363635</v>
       </c>
       <c r="R82" s="156">
-        <f t="shared" si="23"/>
-        <v>6.4380555555555556</v>
+        <f t="shared" si="15"/>
+        <v>6.4647916666666676</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="120">
         <v>80</v>
       </c>
-      <c r="B83" s="270" t="s">
+      <c r="B83" s="263" t="s">
         <v>831</v>
       </c>
-      <c r="C83" s="271">
+      <c r="C83" s="264">
         <v>10000000</v>
       </c>
-      <c r="D83" s="271">
+      <c r="D83" s="264">
         <v>0</v>
       </c>
       <c r="E83" s="156">
         <v>0</v>
       </c>
       <c r="F83" s="156">
-        <f t="shared" si="26"/>
-        <v>33333.333333333336</v>
+        <f t="shared" si="10"/>
+        <v>75000</v>
       </c>
       <c r="G83" s="156">
-        <f t="shared" si="18"/>
-        <v>10033333.333333334</v>
+        <f t="shared" si="11"/>
+        <v>10075000</v>
       </c>
       <c r="H83" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I83" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J83" s="156">
-        <f t="shared" si="22"/>
-        <v>10033333.333333334</v>
+        <f t="shared" si="14"/>
+        <v>10075000</v>
       </c>
       <c r="K83" s="156">
         <v>250000</v>
@@ -55040,57 +55029,57 @@
         <v>0</v>
       </c>
       <c r="O83" s="156">
+        <f t="shared" si="16"/>
+        <v>2200000</v>
+      </c>
+      <c r="P83" s="156">
         <f t="shared" si="17"/>
-        <v>2200000</v>
-      </c>
-      <c r="P83" s="156">
-        <f t="shared" si="24"/>
         <v>1999999.9999999998</v>
       </c>
       <c r="Q83" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1749999.9999999998</v>
       </c>
       <c r="R83" s="156">
-        <f t="shared" si="23"/>
-        <v>5.7333333333333343</v>
+        <f t="shared" si="15"/>
+        <v>5.757142857142858</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="120">
         <v>81</v>
       </c>
-      <c r="B84" s="270" t="s">
+      <c r="B84" s="263" t="s">
         <v>832</v>
       </c>
-      <c r="C84" s="271">
+      <c r="C84" s="264">
         <v>10000000</v>
       </c>
-      <c r="D84" s="271">
+      <c r="D84" s="264">
         <v>0</v>
       </c>
       <c r="E84" s="156">
         <v>0</v>
       </c>
       <c r="F84" s="156">
-        <f t="shared" si="26"/>
-        <v>33333.333333333336</v>
+        <f t="shared" si="10"/>
+        <v>75000</v>
       </c>
       <c r="G84" s="156">
-        <f t="shared" si="18"/>
-        <v>10033333.333333334</v>
+        <f t="shared" si="11"/>
+        <v>10075000</v>
       </c>
       <c r="H84" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I84" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J84" s="156">
-        <f t="shared" si="22"/>
-        <v>10033333.333333334</v>
+        <f t="shared" si="14"/>
+        <v>10075000</v>
       </c>
       <c r="K84" s="156">
         <v>250000</v>
@@ -55105,57 +55094,57 @@
         <v>0</v>
       </c>
       <c r="O84" s="156">
+        <f t="shared" si="16"/>
+        <v>2200000</v>
+      </c>
+      <c r="P84" s="156">
         <f t="shared" si="17"/>
-        <v>2200000</v>
-      </c>
-      <c r="P84" s="156">
-        <f t="shared" si="24"/>
         <v>1999999.9999999998</v>
       </c>
       <c r="Q84" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1749999.9999999998</v>
       </c>
       <c r="R84" s="156">
-        <f t="shared" si="23"/>
-        <v>5.7333333333333343</v>
+        <f t="shared" si="15"/>
+        <v>5.757142857142858</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="120">
         <v>82</v>
       </c>
-      <c r="B85" s="270" t="s">
+      <c r="B85" s="263" t="s">
         <v>833</v>
       </c>
-      <c r="C85" s="271">
+      <c r="C85" s="264">
         <v>10000000</v>
       </c>
-      <c r="D85" s="271">
+      <c r="D85" s="264">
         <v>0</v>
       </c>
       <c r="E85" s="156">
         <v>0</v>
       </c>
       <c r="F85" s="156">
-        <f t="shared" si="26"/>
-        <v>33333.333333333336</v>
+        <f t="shared" si="10"/>
+        <v>75000</v>
       </c>
       <c r="G85" s="156">
-        <f t="shared" si="18"/>
-        <v>10033333.333333334</v>
+        <f t="shared" si="11"/>
+        <v>10075000</v>
       </c>
       <c r="H85" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I85" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J85" s="156">
-        <f t="shared" si="22"/>
-        <v>10033333.333333334</v>
+        <f t="shared" si="14"/>
+        <v>10075000</v>
       </c>
       <c r="K85" s="156">
         <v>250000</v>
@@ -55170,57 +55159,57 @@
         <v>0</v>
       </c>
       <c r="O85" s="156">
+        <f t="shared" si="16"/>
+        <v>2200000</v>
+      </c>
+      <c r="P85" s="156">
         <f t="shared" si="17"/>
-        <v>2200000</v>
-      </c>
-      <c r="P85" s="156">
-        <f t="shared" si="24"/>
         <v>1999999.9999999998</v>
       </c>
       <c r="Q85" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1749999.9999999998</v>
       </c>
       <c r="R85" s="156">
-        <f t="shared" si="23"/>
-        <v>5.7333333333333343</v>
+        <f t="shared" si="15"/>
+        <v>5.757142857142858</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="120">
         <v>83</v>
       </c>
-      <c r="B86" s="270" t="s">
+      <c r="B86" s="263" t="s">
         <v>834</v>
       </c>
-      <c r="C86" s="271">
+      <c r="C86" s="264">
         <v>10000000</v>
       </c>
-      <c r="D86" s="271">
+      <c r="D86" s="264">
         <v>0</v>
       </c>
       <c r="E86" s="156">
         <v>0</v>
       </c>
       <c r="F86" s="156">
-        <f t="shared" si="26"/>
-        <v>33333.333333333336</v>
+        <f t="shared" si="10"/>
+        <v>75000</v>
       </c>
       <c r="G86" s="156">
-        <f t="shared" si="18"/>
-        <v>10033333.333333334</v>
+        <f t="shared" si="11"/>
+        <v>10075000</v>
       </c>
       <c r="H86" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I86" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J86" s="156">
-        <f t="shared" si="22"/>
-        <v>10033333.333333334</v>
+        <f t="shared" si="14"/>
+        <v>10075000</v>
       </c>
       <c r="K86" s="156">
         <v>250000</v>
@@ -55235,57 +55224,57 @@
         <v>0</v>
       </c>
       <c r="O86" s="156">
+        <f t="shared" si="16"/>
+        <v>2200000</v>
+      </c>
+      <c r="P86" s="156">
         <f t="shared" si="17"/>
-        <v>2200000</v>
-      </c>
-      <c r="P86" s="156">
-        <f t="shared" si="24"/>
         <v>1999999.9999999998</v>
       </c>
       <c r="Q86" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1749999.9999999998</v>
       </c>
       <c r="R86" s="156">
-        <f t="shared" si="23"/>
-        <v>5.7333333333333343</v>
+        <f t="shared" si="15"/>
+        <v>5.757142857142858</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="120">
         <v>84</v>
       </c>
-      <c r="B87" s="270" t="s">
+      <c r="B87" s="263" t="s">
         <v>840</v>
       </c>
-      <c r="C87" s="271">
+      <c r="C87" s="264">
         <v>108495654.625</v>
       </c>
-      <c r="D87" s="271">
+      <c r="D87" s="264">
         <v>0</v>
       </c>
       <c r="E87" s="156">
         <v>0</v>
       </c>
       <c r="F87" s="156">
-        <f t="shared" si="26"/>
-        <v>361652.18208333332</v>
+        <f t="shared" si="10"/>
+        <v>813717.40968749998</v>
       </c>
       <c r="G87" s="156">
-        <f t="shared" si="18"/>
-        <v>108857306.80708334</v>
+        <f t="shared" si="11"/>
+        <v>109309372.0346875</v>
       </c>
       <c r="H87" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I87" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J87" s="156">
-        <f t="shared" si="22"/>
-        <v>108857306.80708334</v>
+        <f t="shared" si="14"/>
+        <v>109309372.0346875</v>
       </c>
       <c r="K87" s="156">
         <v>5000000</v>
@@ -55300,57 +55289,57 @@
         <v>0</v>
       </c>
       <c r="O87" s="156">
+        <f t="shared" si="16"/>
+        <v>9100000</v>
+      </c>
+      <c r="P87" s="156">
         <f t="shared" si="17"/>
-        <v>9100000</v>
-      </c>
-      <c r="P87" s="156">
-        <f t="shared" si="24"/>
         <v>8272727.2727272725</v>
       </c>
       <c r="Q87" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>3272727.2727272725</v>
       </c>
       <c r="R87" s="156">
-        <f t="shared" si="23"/>
-        <v>33.261954857719914</v>
+        <f t="shared" si="15"/>
+        <v>33.400085899487848</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="120">
         <v>85</v>
       </c>
-      <c r="B88" s="270" t="s">
+      <c r="B88" s="263" t="s">
         <v>842</v>
       </c>
-      <c r="C88" s="271">
+      <c r="C88" s="264">
         <v>81125117.5</v>
       </c>
-      <c r="D88" s="271">
+      <c r="D88" s="264">
         <v>0</v>
       </c>
       <c r="E88" s="156">
         <v>0</v>
       </c>
       <c r="F88" s="156">
-        <f t="shared" si="26"/>
-        <v>270417.05833333329</v>
+        <f t="shared" si="10"/>
+        <v>608438.38124999998</v>
       </c>
       <c r="G88" s="156">
-        <f t="shared" si="18"/>
-        <v>81395534.558333337</v>
+        <f t="shared" si="11"/>
+        <v>81733555.881249994</v>
       </c>
       <c r="H88" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I88" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J88" s="156">
-        <f t="shared" si="22"/>
-        <v>81395534.558333337</v>
+        <f t="shared" si="14"/>
+        <v>81733555.881249994</v>
       </c>
       <c r="K88" s="156">
         <v>5000000</v>
@@ -55365,59 +55354,59 @@
         <v>0</v>
       </c>
       <c r="O88" s="156">
+        <f t="shared" si="16"/>
+        <v>9900000</v>
+      </c>
+      <c r="P88" s="156">
         <f t="shared" si="17"/>
-        <v>9900000</v>
-      </c>
-      <c r="P88" s="156">
-        <f t="shared" si="24"/>
         <v>9000000</v>
       </c>
       <c r="Q88" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>4000000</v>
       </c>
       <c r="R88" s="156">
-        <f t="shared" si="23"/>
-        <v>20.348883639583335</v>
+        <f t="shared" si="15"/>
+        <v>20.4333889703125</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="120">
         <v>86</v>
       </c>
-      <c r="B89" s="270" t="s">
+      <c r="B89" s="263" t="s">
         <v>844</v>
       </c>
-      <c r="C89" s="271">
+      <c r="C89" s="264">
         <v>43669980</v>
       </c>
-      <c r="D89" s="271">
+      <c r="D89" s="264">
         <v>0</v>
       </c>
       <c r="E89" s="156">
         <v>0</v>
       </c>
       <c r="F89" s="156">
-        <f t="shared" si="26"/>
-        <v>145566.59999999998</v>
+        <f t="shared" si="10"/>
+        <v>327524.84999999998</v>
       </c>
       <c r="G89" s="156">
-        <f t="shared" si="18"/>
-        <v>43815546.600000001</v>
+        <f t="shared" si="11"/>
+        <v>43997504.850000001</v>
       </c>
       <c r="H89" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I89" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J89" s="156">
-        <f t="shared" si="22"/>
-        <v>43815546.600000001</v>
-      </c>
-      <c r="K89" s="275">
+        <f t="shared" si="14"/>
+        <v>43997504.850000001</v>
+      </c>
+      <c r="K89" s="156">
         <v>4000000</v>
       </c>
       <c r="L89" s="156">
@@ -55430,59 +55419,59 @@
         <v>0</v>
       </c>
       <c r="O89" s="156">
+        <f t="shared" si="16"/>
+        <v>6250000</v>
+      </c>
+      <c r="P89" s="156">
         <f t="shared" si="17"/>
-        <v>6250000</v>
-      </c>
-      <c r="P89" s="156">
-        <f t="shared" si="24"/>
         <v>5681818.1818181816</v>
       </c>
       <c r="Q89" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1681818.1818181816</v>
       </c>
       <c r="R89" s="156">
-        <f t="shared" si="23"/>
-        <v>26.05248716756757</v>
+        <f t="shared" si="15"/>
+        <v>26.160678559459463</v>
       </c>
     </row>
     <row r="90" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A90" s="120">
         <v>87</v>
       </c>
-      <c r="B90" s="270" t="s">
+      <c r="B90" s="263" t="s">
         <v>987</v>
       </c>
-      <c r="C90" s="271">
+      <c r="C90" s="264">
         <v>48646730</v>
       </c>
-      <c r="D90" s="271">
+      <c r="D90" s="264">
         <v>0</v>
       </c>
       <c r="E90" s="156">
         <v>0</v>
       </c>
       <c r="F90" s="156">
-        <f t="shared" si="26"/>
-        <v>162155.76666666663</v>
+        <f t="shared" si="10"/>
+        <v>364850.47499999992</v>
       </c>
       <c r="G90" s="156">
-        <f t="shared" si="18"/>
-        <v>48808885.766666666</v>
+        <f t="shared" si="11"/>
+        <v>49011580.475000001</v>
       </c>
       <c r="H90" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I90" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J90" s="156">
-        <f t="shared" si="22"/>
-        <v>48808885.766666666</v>
-      </c>
-      <c r="K90" s="275">
+        <f t="shared" si="14"/>
+        <v>49011580.475000001</v>
+      </c>
+      <c r="K90" s="156">
         <v>4000000</v>
       </c>
       <c r="L90" s="156">
@@ -55495,58 +55484,58 @@
         <v>0</v>
       </c>
       <c r="O90" s="156">
+        <f t="shared" si="16"/>
+        <v>6400000</v>
+      </c>
+      <c r="P90" s="156">
         <f t="shared" si="17"/>
-        <v>6400000</v>
-      </c>
-      <c r="P90" s="156">
-        <f t="shared" si="24"/>
         <v>5818181.8181818174</v>
       </c>
       <c r="Q90" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1818181.8181818174</v>
       </c>
       <c r="R90" s="156">
-        <f t="shared" si="23"/>
-        <v>26.844887171666677</v>
+        <f t="shared" si="15"/>
+        <v>26.956369261250011</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" s="120">
         <v>88</v>
       </c>
-      <c r="B91" s="270" t="s">
+      <c r="B91" s="263" t="s">
         <v>817</v>
       </c>
-      <c r="C91" s="271">
+      <c r="C91" s="264">
         <f>439479545.0825+80000000</f>
         <v>519479545.08249998</v>
       </c>
-      <c r="D91" s="271">
+      <c r="D91" s="264">
         <v>0</v>
       </c>
       <c r="E91" s="156">
         <v>0</v>
       </c>
       <c r="F91" s="156">
-        <f t="shared" si="26"/>
-        <v>1731598.4836083332</v>
+        <f t="shared" si="10"/>
+        <v>3896096.5881187492</v>
       </c>
       <c r="G91" s="156">
-        <f t="shared" si="18"/>
-        <v>521211143.56610829</v>
+        <f t="shared" si="11"/>
+        <v>523375641.67061871</v>
       </c>
       <c r="H91" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I91" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J91" s="156">
-        <f t="shared" si="22"/>
-        <v>521211143.56610829</v>
+        <f t="shared" si="14"/>
+        <v>523375641.67061871</v>
       </c>
       <c r="K91" s="156">
         <v>3000000</v>
@@ -55561,57 +55550,57 @@
         <v>0</v>
       </c>
       <c r="O91" s="156">
+        <f t="shared" si="16"/>
+        <v>13400000</v>
+      </c>
+      <c r="P91" s="156">
         <f t="shared" si="17"/>
-        <v>13400000</v>
-      </c>
-      <c r="P91" s="156">
-        <f t="shared" si="24"/>
         <v>12181818.181818182</v>
       </c>
       <c r="Q91" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>9181818.1818181816</v>
       </c>
-      <c r="R91" s="278">
-        <f t="shared" si="23"/>
-        <v>56.765570091358327</v>
+      <c r="R91" s="156">
+        <f t="shared" si="15"/>
+        <v>57.001307508681244</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" s="120">
         <v>89</v>
       </c>
-      <c r="B92" s="270" t="s">
+      <c r="B92" s="263" t="s">
         <v>843</v>
       </c>
-      <c r="C92" s="271">
+      <c r="C92" s="264">
         <v>54733838</v>
       </c>
-      <c r="D92" s="271">
+      <c r="D92" s="264">
         <v>0</v>
       </c>
       <c r="E92" s="156">
         <v>0</v>
       </c>
       <c r="F92" s="156">
-        <f t="shared" si="26"/>
-        <v>182446.12666666668</v>
+        <f t="shared" si="10"/>
+        <v>410503.78499999997</v>
       </c>
       <c r="G92" s="156">
-        <f t="shared" si="18"/>
-        <v>54916284.126666665</v>
+        <f t="shared" si="11"/>
+        <v>55144341.784999996</v>
       </c>
       <c r="H92" s="156">
-        <f t="shared" si="27"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I92" s="156">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J92" s="156">
-        <f t="shared" si="22"/>
-        <v>54916284.126666665</v>
+        <f t="shared" si="14"/>
+        <v>55144341.784999996</v>
       </c>
       <c r="K92" s="156">
         <v>5000000</v>
@@ -55626,20 +55615,20 @@
         <v>0</v>
       </c>
       <c r="O92" s="156">
+        <f t="shared" si="16"/>
+        <v>6800000</v>
+      </c>
+      <c r="P92" s="156">
         <f t="shared" si="17"/>
-        <v>6800000</v>
-      </c>
-      <c r="P92" s="156">
-        <f t="shared" si="24"/>
         <v>6181818.1818181816</v>
       </c>
       <c r="Q92" s="156">
-        <f t="shared" si="25"/>
+        <f t="shared" si="18"/>
         <v>1181818.1818181816</v>
       </c>
       <c r="R92" s="156">
-        <f t="shared" si="23"/>
-        <v>46.467625030256414</v>
+        <f t="shared" si="15"/>
+        <v>46.660596895000005</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105355CE-26CD-499A-B1D2-D4A9D6F3D789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14101549-0797-461E-B20B-933AF83FEE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="912" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Theo dõi HĐ_Chi tiết" sheetId="2" r:id="rId1"/>
@@ -17250,7 +17250,7 @@
       </c>
       <c r="AP41" s="122"/>
     </row>
-    <row r="42" spans="1:42" s="123" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:42" s="123" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>39</v>
       </c>
@@ -26279,7 +26279,7 @@
       </c>
       <c r="AH4" s="171">
         <f ca="1">AA4-TODAY()</f>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AI4" s="172">
         <f>3*D4</f>
@@ -26414,7 +26414,7 @@
       </c>
       <c r="AH5" s="181">
         <f ca="1">AB5-TODAY()</f>
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="AI5" s="175">
         <f>3*D5</f>
@@ -26549,7 +26549,7 @@
       </c>
       <c r="AH6" s="171">
         <f ca="1">Z6-TODAY()</f>
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AI6" s="172">
         <f>3*D6</f>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="AH7" s="181">
         <f ca="1">R7-TODAY()</f>
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="AI7" s="175">
         <f>6*D7</f>
@@ -26819,7 +26819,7 @@
       </c>
       <c r="AH8" s="188">
         <f ca="1">Z8-TODAY()</f>
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="AI8" s="166">
         <f>3*D8</f>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="AH9" s="171">
         <f ca="1">Z9-TODAY()</f>
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AI9" s="166">
         <f>3*D9</f>
@@ -27089,7 +27089,7 @@
       </c>
       <c r="AH10" s="171">
         <f ca="1">Z10-TODAY()</f>
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="AI10" s="166">
         <f>D10*3</f>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="AH11" s="171">
         <f ca="1">Z11-TODAY()</f>
-        <v>-9</v>
+        <v>-23</v>
       </c>
       <c r="AI11" s="189">
         <f>D11*3</f>
@@ -27359,7 +27359,7 @@
       </c>
       <c r="AH12" s="171">
         <f ca="1">Y12-TODAY()</f>
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="AI12" s="166">
         <f>3*D12</f>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="AH13" s="171">
         <f ca="1">Z13-TODAY()</f>
-        <v>-1</v>
+        <v>-15</v>
       </c>
       <c r="AI13" s="166">
         <f>3*7000000</f>
@@ -27629,7 +27629,7 @@
       </c>
       <c r="AH14" s="188">
         <f ca="1">Y14-TODAY()</f>
-        <v>8</v>
+        <v>-6</v>
       </c>
       <c r="AI14" s="166">
         <f>3*D14</f>
@@ -27764,7 +27764,7 @@
       </c>
       <c r="AH15" s="188">
         <f ca="1">R15-TODAY()</f>
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="AI15" s="166">
         <f>6*D15</f>
@@ -27898,7 +27898,7 @@
       </c>
       <c r="AH16" s="171">
         <f ca="1">R16-TODAY()</f>
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="AI16" s="166">
         <f>6*D16</f>
@@ -28033,7 +28033,7 @@
       </c>
       <c r="AH17" s="188">
         <f ca="1">Z17-TODAY()</f>
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="AI17" s="166">
         <f>3*D17</f>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="AH18" s="188">
         <f ca="1">R18-TODAY()</f>
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="AI18" s="166">
         <f>6*D18</f>
@@ -28303,7 +28303,7 @@
       </c>
       <c r="AH19" s="188">
         <f ca="1">Y19-TODAY()</f>
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="AI19" s="166">
         <f>3*D19</f>
@@ -28438,7 +28438,7 @@
       </c>
       <c r="AH20" s="194">
         <f ca="1">R20-TODAY()</f>
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="AI20" s="175">
         <f>6*D20</f>
@@ -28573,7 +28573,7 @@
       </c>
       <c r="AH21" s="188">
         <f ca="1">Z21-TODAY()</f>
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="AI21" s="166">
         <f>3*D21</f>
@@ -28709,7 +28709,7 @@
       </c>
       <c r="AH22" s="188">
         <f ca="1">R22-TODAY()</f>
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="AI22" s="166">
         <f>6*D22</f>
@@ -28844,7 +28844,7 @@
       </c>
       <c r="AH23" s="188">
         <f ca="1">R23-TODAY()</f>
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="AI23" s="166">
         <f>D23*6</f>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="AH24" s="188">
         <f ca="1">X24-TODAY()</f>
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="AI24" s="189">
         <f>3*D24</f>
@@ -29114,7 +29114,7 @@
       </c>
       <c r="AH25" s="194">
         <f ca="1">Y25-TODAY()</f>
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AI25" s="175">
         <f>3*D25</f>
@@ -29249,7 +29249,7 @@
       </c>
       <c r="AH26" s="188">
         <f ca="1">Q26-TODAY()</f>
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="AI26" s="166">
         <f>6*D26</f>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="AH27" s="188">
         <f ca="1">Y27-TODAY()</f>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AI27" s="166">
         <f>3*D27</f>
@@ -29519,7 +29519,7 @@
       </c>
       <c r="AH28" s="194">
         <f ca="1">R28-TODAY()</f>
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="AI28" s="175">
         <f>6*D28</f>
@@ -29652,7 +29652,7 @@
       </c>
       <c r="AH29" s="188">
         <f ca="1">S29-TODAY()</f>
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AI29" s="203">
         <f>D29*6</f>
@@ -29787,7 +29787,7 @@
       </c>
       <c r="AH30" s="188">
         <f ca="1">X30-TODAY()</f>
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="AI30" s="203">
         <f>D30*3</f>
@@ -29922,7 +29922,7 @@
       </c>
       <c r="AH31" s="194">
         <f ca="1">R31-TODAY()</f>
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="AI31" s="196">
         <f>D31*6</f>
@@ -30057,7 +30057,7 @@
       </c>
       <c r="AH32" s="188">
         <f ca="1">X32-TODAY()</f>
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="AI32" s="203">
         <f t="shared" ref="AI32:AI36" si="40">D32*3</f>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="AH33" s="188">
         <f ca="1">X33-TODAY()</f>
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AI33" s="207">
         <f t="shared" si="40"/>
@@ -30327,7 +30327,7 @@
       </c>
       <c r="AH34" s="194">
         <f ca="1">X34-TODAY()</f>
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="AI34" s="196">
         <f t="shared" si="40"/>
@@ -30462,7 +30462,7 @@
       </c>
       <c r="AH35" s="188">
         <f ca="1">X35-TODAY()</f>
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="AI35" s="203">
         <f t="shared" si="40"/>
@@ -30597,7 +30597,7 @@
       </c>
       <c r="AH36" s="188">
         <f ca="1">X36-TODAY()</f>
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="AI36" s="203">
         <f t="shared" si="40"/>
@@ -30731,7 +30731,7 @@
       </c>
       <c r="AH37" s="188">
         <f ca="1">Q37-TODAY()</f>
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="AI37" s="203">
         <f>D37*6</f>
@@ -30866,7 +30866,7 @@
       </c>
       <c r="AH38" s="188">
         <f ca="1">Q38-TODAY()</f>
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="AI38" s="203">
         <f>D38*6</f>
@@ -31001,7 +31001,7 @@
       </c>
       <c r="AH39" s="188">
         <f ca="1">Q39-TODAY()</f>
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="AI39" s="203">
         <f>D39*6</f>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="AH40" s="188">
         <f ca="1">X40-TODAY()</f>
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="AI40" s="203">
         <f>D40*3</f>
@@ -31271,7 +31271,7 @@
       </c>
       <c r="AH41" s="188">
         <f ca="1">W41-TODAY()</f>
-        <v>-9</v>
+        <v>-23</v>
       </c>
       <c r="AI41" s="203">
         <f>D41*3</f>
@@ -31406,7 +31406,7 @@
       </c>
       <c r="AH42" s="188">
         <f ca="1">V42-TODAY()</f>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AI42" s="203">
         <f t="shared" ref="AI42:AI43" si="49">D42*3</f>
@@ -31541,7 +31541,7 @@
       </c>
       <c r="AH43" s="194">
         <f ca="1">V43-TODAY()</f>
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AI43" s="196">
         <f t="shared" si="49"/>
@@ -31673,7 +31673,7 @@
       </c>
       <c r="AH44" s="188">
         <f ca="1">S44-TODAY()</f>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AI44" s="203">
         <f>D44*6</f>
@@ -31808,7 +31808,7 @@
       </c>
       <c r="AH45" s="194">
         <f ca="1">P45-TODAY()</f>
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="AI45" s="196">
         <f>D45*6</f>
@@ -31902,48 +31902,48 @@
         <v>46127</v>
       </c>
       <c r="X46" s="184">
-        <f t="shared" si="50"/>
+        <f>EDATE(W46,1)</f>
+        <v>46157</v>
+      </c>
+      <c r="Y46" s="184">
+        <f t="shared" ref="Y46:AG46" si="54">EDATE(X46,1)</f>
+        <v>46188</v>
+      </c>
+      <c r="Z46" s="184">
+        <f t="shared" si="54"/>
+        <v>46218</v>
+      </c>
+      <c r="AA46" s="184">
+        <f t="shared" si="54"/>
+        <v>46249</v>
+      </c>
+      <c r="AB46" s="184">
+        <f t="shared" si="54"/>
+        <v>46280</v>
+      </c>
+      <c r="AC46" s="184">
+        <f t="shared" si="54"/>
         <v>46310</v>
       </c>
-      <c r="Y46" s="184">
-        <f t="shared" si="50"/>
-        <v>46492</v>
-      </c>
-      <c r="Z46" s="184">
-        <f t="shared" si="50"/>
-        <v>46675</v>
-      </c>
-      <c r="AA46" s="184">
-        <f t="shared" si="50"/>
-        <v>46858</v>
-      </c>
-      <c r="AB46" s="184">
-        <f t="shared" si="50"/>
-        <v>47041</v>
-      </c>
-      <c r="AC46" s="184">
-        <f t="shared" si="50"/>
-        <v>47223</v>
-      </c>
       <c r="AD46" s="184">
-        <f t="shared" si="50"/>
-        <v>47406</v>
+        <f t="shared" si="54"/>
+        <v>46341</v>
       </c>
       <c r="AE46" s="184">
-        <f t="shared" si="50"/>
-        <v>47588</v>
+        <f t="shared" si="54"/>
+        <v>46371</v>
       </c>
       <c r="AF46" s="184">
-        <f t="shared" si="51"/>
-        <v>47771</v>
+        <f t="shared" si="54"/>
+        <v>46402</v>
       </c>
       <c r="AG46" s="184">
-        <f t="shared" si="51"/>
-        <v>47953</v>
+        <f t="shared" si="54"/>
+        <v>46433</v>
       </c>
       <c r="AH46" s="188">
         <f ca="1">W46-TODAY()</f>
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="AI46" s="203">
         <f>D46*1</f>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="AH47" s="188">
         <f ca="1">P47-TODAY()</f>
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="AI47" s="203">
         <v>24000000</v>
@@ -32212,7 +32212,7 @@
       </c>
       <c r="AH48" s="188">
         <f ca="1">P48-TODAY()</f>
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="AI48" s="203">
         <v>24000000</v>
@@ -32333,7 +32333,7 @@
         <v>48819</v>
       </c>
       <c r="AE49" s="184">
-        <f t="shared" ref="AE49:AE78" si="54">EDATE(AD49,6)</f>
+        <f t="shared" ref="AE49:AE78" si="55">EDATE(AD49,6)</f>
         <v>49003</v>
       </c>
       <c r="AF49" s="184">
@@ -32346,7 +32346,7 @@
       </c>
       <c r="AH49" s="188">
         <f ca="1">P49-TODAY()</f>
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="AI49" s="203">
         <f>D49*6</f>
@@ -32468,7 +32468,7 @@
         <v>48884</v>
       </c>
       <c r="AE50" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49065</v>
       </c>
       <c r="AF50" s="184">
@@ -32480,8 +32480,8 @@
         <v>49430</v>
       </c>
       <c r="AH50" s="188">
-        <f t="shared" ref="AH50:AH54" ca="1" si="55">O50-TODAY()</f>
-        <v>28</v>
+        <f t="shared" ref="AH50:AH54" ca="1" si="56">O50-TODAY()</f>
+        <v>14</v>
       </c>
       <c r="AI50" s="203">
         <f>D50*6</f>
@@ -32603,7 +32603,7 @@
         <v>48966</v>
       </c>
       <c r="AE51" s="178">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49147</v>
       </c>
       <c r="AF51" s="178">
@@ -32615,11 +32615,11 @@
         <v>49512</v>
       </c>
       <c r="AH51" s="188">
-        <f t="shared" ca="1" si="55"/>
-        <v>110</v>
+        <f t="shared" ca="1" si="56"/>
+        <v>96</v>
       </c>
       <c r="AI51" s="196">
-        <f t="shared" ref="AI51:AI60" si="56">D51*6</f>
+        <f t="shared" ref="AI51:AI60" si="57">D51*6</f>
         <v>36000000</v>
       </c>
       <c r="AJ51" s="173" t="s">
@@ -32738,7 +32738,7 @@
         <v>48945</v>
       </c>
       <c r="AE52" s="169">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49126</v>
       </c>
       <c r="AF52" s="169">
@@ -32750,8 +32750,8 @@
         <v>49491</v>
       </c>
       <c r="AH52" s="188">
-        <f t="shared" ca="1" si="55"/>
-        <v>89</v>
+        <f t="shared" ca="1" si="56"/>
+        <v>75</v>
       </c>
       <c r="AI52" s="203">
         <f>D52*6</f>
@@ -32793,15 +32793,15 @@
         <v>45287</v>
       </c>
       <c r="K53" s="184">
-        <f t="shared" ref="K53:N68" si="57">EDATE(J53,6)</f>
+        <f t="shared" ref="K53:N68" si="58">EDATE(J53,6)</f>
         <v>45470</v>
       </c>
       <c r="L53" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45653</v>
       </c>
       <c r="M53" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45835</v>
       </c>
       <c r="N53" s="184">
@@ -32873,7 +32873,7 @@
         <v>48940</v>
       </c>
       <c r="AE53" s="169">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49122</v>
       </c>
       <c r="AF53" s="169">
@@ -32885,11 +32885,11 @@
         <v>49487</v>
       </c>
       <c r="AH53" s="188">
-        <f t="shared" ca="1" si="55"/>
-        <v>85</v>
+        <f t="shared" ca="1" si="56"/>
+        <v>71</v>
       </c>
       <c r="AI53" s="203">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>27000000</v>
       </c>
       <c r="AJ53" s="164" t="s">
@@ -32928,15 +32928,15 @@
         <v>45286</v>
       </c>
       <c r="K54" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45469</v>
       </c>
       <c r="L54" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45652</v>
       </c>
       <c r="M54" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45834</v>
       </c>
       <c r="N54" s="184">
@@ -33008,7 +33008,7 @@
         <v>48939</v>
       </c>
       <c r="AE54" s="169">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49121</v>
       </c>
       <c r="AF54" s="169">
@@ -33020,11 +33020,11 @@
         <v>49486</v>
       </c>
       <c r="AH54" s="188">
-        <f t="shared" ca="1" si="55"/>
-        <v>84</v>
+        <f t="shared" ca="1" si="56"/>
+        <v>70</v>
       </c>
       <c r="AI54" s="203">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>24000000</v>
       </c>
       <c r="AJ54" s="164" t="s">
@@ -33063,7 +33063,7 @@
         <v>45139</v>
       </c>
       <c r="K55" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45323</v>
       </c>
       <c r="L55" s="184">
@@ -33143,7 +33143,7 @@
         <v>48792</v>
       </c>
       <c r="AE55" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>48976</v>
       </c>
       <c r="AF55" s="184">
@@ -33156,10 +33156,10 @@
       </c>
       <c r="AH55" s="188">
         <f ca="1">P55-TODAY()</f>
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AI55" s="203">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>33000000</v>
       </c>
       <c r="AJ55" s="164" t="s">
@@ -33198,15 +33198,15 @@
         <v>45379</v>
       </c>
       <c r="K56" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45563</v>
       </c>
       <c r="L56" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45744</v>
       </c>
       <c r="M56" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45928</v>
       </c>
       <c r="N56" s="184">
@@ -33278,7 +33278,7 @@
         <v>49031</v>
       </c>
       <c r="AE56" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49215</v>
       </c>
       <c r="AF56" s="184">
@@ -33290,11 +33290,11 @@
         <v>49580</v>
       </c>
       <c r="AH56" s="188">
-        <f t="shared" ref="AH56:AH67" ca="1" si="58">N56-TODAY()</f>
-        <v>-6</v>
+        <f t="shared" ref="AH56:AH67" ca="1" si="59">N56-TODAY()</f>
+        <v>-20</v>
       </c>
       <c r="AI56" s="203">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>24000000</v>
       </c>
       <c r="AJ56" s="164" t="s">
@@ -33333,15 +33333,15 @@
         <v>45392</v>
       </c>
       <c r="K57" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45575</v>
       </c>
       <c r="L57" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45757</v>
       </c>
       <c r="M57" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45940</v>
       </c>
       <c r="N57" s="184">
@@ -33413,7 +33413,7 @@
         <v>49044</v>
       </c>
       <c r="AE57" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49227</v>
       </c>
       <c r="AF57" s="184">
@@ -33425,11 +33425,11 @@
         <v>49592</v>
       </c>
       <c r="AH57" s="188">
-        <f t="shared" ca="1" si="58"/>
-        <v>7</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>-7</v>
       </c>
       <c r="AI57" s="203">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>24000000</v>
       </c>
       <c r="AJ57" s="164" t="s">
@@ -33468,7 +33468,7 @@
         <v>45356</v>
       </c>
       <c r="K58" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45540</v>
       </c>
       <c r="L58" s="184">
@@ -33476,7 +33476,7 @@
         <v>45721</v>
       </c>
       <c r="M58" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45905</v>
       </c>
       <c r="N58" s="214">
@@ -33548,7 +33548,7 @@
         <v>49008</v>
       </c>
       <c r="AE58" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49192</v>
       </c>
       <c r="AF58" s="184">
@@ -33561,10 +33561,10 @@
       </c>
       <c r="AH58" s="188">
         <f ca="1">O58-TODAY()</f>
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="AI58" s="203">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>24000000</v>
       </c>
       <c r="AJ58" s="164" t="s">
@@ -33603,7 +33603,7 @@
         <v>45413</v>
       </c>
       <c r="K59" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45597</v>
       </c>
       <c r="L59" s="184">
@@ -33683,7 +33683,7 @@
         <v>49065</v>
       </c>
       <c r="AE59" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49249</v>
       </c>
       <c r="AF59" s="184">
@@ -33695,11 +33695,11 @@
         <v>49614</v>
       </c>
       <c r="AH59" s="188">
-        <f t="shared" ca="1" si="58"/>
-        <v>28</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>14</v>
       </c>
       <c r="AI59" s="203">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>24000000</v>
       </c>
       <c r="AJ59" s="164" t="s">
@@ -33754,71 +33754,71 @@
         <v>46143</v>
       </c>
       <c r="O60" s="184">
-        <f t="shared" ref="O60:AA79" si="59">EDATE(N60,6)</f>
+        <f t="shared" ref="O60:AA79" si="60">EDATE(N60,6)</f>
         <v>46327</v>
       </c>
       <c r="P60" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46508</v>
       </c>
       <c r="Q60" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46692</v>
       </c>
       <c r="R60" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46874</v>
       </c>
       <c r="S60" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47058</v>
       </c>
       <c r="T60" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47239</v>
       </c>
       <c r="U60" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47423</v>
       </c>
       <c r="V60" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47604</v>
       </c>
       <c r="W60" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47788</v>
       </c>
       <c r="X60" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47969</v>
       </c>
       <c r="Y60" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48153</v>
       </c>
       <c r="Z60" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48335</v>
       </c>
       <c r="AA60" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48519</v>
       </c>
       <c r="AB60" s="184">
-        <f t="shared" ref="AB60:AD78" si="60">EDATE(AA60,6)</f>
+        <f t="shared" ref="AB60:AD78" si="61">EDATE(AA60,6)</f>
         <v>48700</v>
       </c>
       <c r="AC60" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48884</v>
       </c>
       <c r="AD60" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49065</v>
       </c>
       <c r="AE60" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49249</v>
       </c>
       <c r="AF60" s="184">
@@ -33830,11 +33830,11 @@
         <v>49614</v>
       </c>
       <c r="AH60" s="188">
-        <f t="shared" ca="1" si="58"/>
-        <v>28</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>14</v>
       </c>
       <c r="AI60" s="203">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>24000000</v>
       </c>
       <c r="AJ60" s="164" t="s">
@@ -33877,83 +33877,83 @@
         <v>45587</v>
       </c>
       <c r="L61" s="219">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45769</v>
       </c>
       <c r="M61" s="214">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45952</v>
       </c>
       <c r="N61" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46134</v>
       </c>
       <c r="O61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46317</v>
       </c>
       <c r="P61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46499</v>
       </c>
       <c r="Q61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46682</v>
       </c>
       <c r="R61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46865</v>
       </c>
       <c r="S61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47048</v>
       </c>
       <c r="T61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47230</v>
       </c>
       <c r="U61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47413</v>
       </c>
       <c r="V61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47595</v>
       </c>
       <c r="W61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47778</v>
       </c>
       <c r="X61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47960</v>
       </c>
       <c r="Y61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48143</v>
       </c>
       <c r="Z61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48326</v>
       </c>
       <c r="AA61" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48509</v>
       </c>
       <c r="AB61" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48691</v>
       </c>
       <c r="AC61" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48874</v>
       </c>
       <c r="AD61" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49056</v>
       </c>
       <c r="AE61" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49239</v>
       </c>
       <c r="AF61" s="184">
@@ -33965,8 +33965,8 @@
         <v>49604</v>
       </c>
       <c r="AH61" s="188">
-        <f t="shared" ca="1" si="58"/>
-        <v>19</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>5</v>
       </c>
       <c r="AI61" s="203">
         <f>D61*6</f>
@@ -34012,83 +34012,83 @@
         <v>45632</v>
       </c>
       <c r="L62" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45814</v>
       </c>
       <c r="M62" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45997</v>
       </c>
       <c r="N62" s="214">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46179</v>
       </c>
       <c r="O62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46362</v>
       </c>
       <c r="P62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46544</v>
       </c>
       <c r="Q62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46727</v>
       </c>
       <c r="R62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46910</v>
       </c>
       <c r="S62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47093</v>
       </c>
       <c r="T62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47275</v>
       </c>
       <c r="U62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47458</v>
       </c>
       <c r="V62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47640</v>
       </c>
       <c r="W62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47823</v>
       </c>
       <c r="X62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48005</v>
       </c>
       <c r="Y62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48188</v>
       </c>
       <c r="Z62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48371</v>
       </c>
       <c r="AA62" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48554</v>
       </c>
       <c r="AB62" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48736</v>
       </c>
       <c r="AC62" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48919</v>
       </c>
       <c r="AD62" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49101</v>
       </c>
       <c r="AE62" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49284</v>
       </c>
       <c r="AF62" s="184">
@@ -34100,11 +34100,11 @@
         <v>49649</v>
       </c>
       <c r="AH62" s="188">
-        <f t="shared" ca="1" si="58"/>
-        <v>64</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>50</v>
       </c>
       <c r="AI62" s="203">
-        <f t="shared" ref="AI62:AI85" si="61">D62*6</f>
+        <f t="shared" ref="AI62:AI85" si="62">D62*6</f>
         <v>24000000</v>
       </c>
       <c r="AJ62" s="164" t="s">
@@ -34147,83 +34147,83 @@
         <v>45641</v>
       </c>
       <c r="L63" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45823</v>
       </c>
       <c r="M63" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46006</v>
       </c>
       <c r="N63" s="214">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46188</v>
       </c>
       <c r="O63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46371</v>
       </c>
       <c r="P63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46553</v>
       </c>
       <c r="Q63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46736</v>
       </c>
       <c r="R63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46919</v>
       </c>
       <c r="S63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47102</v>
       </c>
       <c r="T63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47284</v>
       </c>
       <c r="U63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47467</v>
       </c>
       <c r="V63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47649</v>
       </c>
       <c r="W63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47832</v>
       </c>
       <c r="X63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48014</v>
       </c>
       <c r="Y63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48197</v>
       </c>
       <c r="Z63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48380</v>
       </c>
       <c r="AA63" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48563</v>
       </c>
       <c r="AB63" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48745</v>
       </c>
       <c r="AC63" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48928</v>
       </c>
       <c r="AD63" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49110</v>
       </c>
       <c r="AE63" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49293</v>
       </c>
       <c r="AF63" s="184">
@@ -34235,11 +34235,11 @@
         <v>49658</v>
       </c>
       <c r="AH63" s="188">
-        <f t="shared" ca="1" si="58"/>
-        <v>73</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>59</v>
       </c>
       <c r="AI63" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>30000000</v>
       </c>
       <c r="AJ63" s="164" t="s">
@@ -34278,87 +34278,87 @@
         <v>45453</v>
       </c>
       <c r="K64" s="184">
-        <f t="shared" ref="K64:L79" si="62">EDATE(J64,6)</f>
+        <f t="shared" ref="K64:L79" si="63">EDATE(J64,6)</f>
         <v>45636</v>
       </c>
       <c r="L64" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45818</v>
       </c>
       <c r="M64" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46001</v>
       </c>
       <c r="N64" s="214">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46183</v>
       </c>
       <c r="O64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46366</v>
       </c>
       <c r="P64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46548</v>
       </c>
       <c r="Q64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46731</v>
       </c>
       <c r="R64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46914</v>
       </c>
       <c r="S64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47097</v>
       </c>
       <c r="T64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47279</v>
       </c>
       <c r="U64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47462</v>
       </c>
       <c r="V64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47644</v>
       </c>
       <c r="W64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47827</v>
       </c>
       <c r="X64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48009</v>
       </c>
       <c r="Y64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48192</v>
       </c>
       <c r="Z64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48375</v>
       </c>
       <c r="AA64" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48558</v>
       </c>
       <c r="AB64" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48740</v>
       </c>
       <c r="AC64" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48923</v>
       </c>
       <c r="AD64" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49105</v>
       </c>
       <c r="AE64" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49288</v>
       </c>
       <c r="AF64" s="184">
@@ -34370,8 +34370,8 @@
         <v>49653</v>
       </c>
       <c r="AH64" s="188">
-        <f t="shared" ca="1" si="58"/>
-        <v>68</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>54</v>
       </c>
       <c r="AI64" s="203">
         <f>D64*6</f>
@@ -34413,87 +34413,87 @@
         <v>45463</v>
       </c>
       <c r="K65" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45646</v>
       </c>
       <c r="L65" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>45828</v>
       </c>
       <c r="M65" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46011</v>
       </c>
       <c r="N65" s="214">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46193</v>
       </c>
       <c r="O65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46376</v>
       </c>
       <c r="P65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46558</v>
       </c>
       <c r="Q65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46741</v>
       </c>
       <c r="R65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46924</v>
       </c>
       <c r="S65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47107</v>
       </c>
       <c r="T65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47289</v>
       </c>
       <c r="U65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47472</v>
       </c>
       <c r="V65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47654</v>
       </c>
       <c r="W65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47837</v>
       </c>
       <c r="X65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48019</v>
       </c>
       <c r="Y65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48202</v>
       </c>
       <c r="Z65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48385</v>
       </c>
       <c r="AA65" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48568</v>
       </c>
       <c r="AB65" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48750</v>
       </c>
       <c r="AC65" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48933</v>
       </c>
       <c r="AD65" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49115</v>
       </c>
       <c r="AE65" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49298</v>
       </c>
       <c r="AF65" s="184">
@@ -34505,11 +34505,11 @@
         <v>49663</v>
       </c>
       <c r="AH65" s="188">
-        <f t="shared" ca="1" si="58"/>
-        <v>78</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>64</v>
       </c>
       <c r="AI65" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>42000000</v>
       </c>
       <c r="AJ65" s="164" t="s">
@@ -34548,7 +34548,7 @@
         <v>45483</v>
       </c>
       <c r="K66" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45667</v>
       </c>
       <c r="L66" s="184">
@@ -34564,71 +34564,71 @@
         <v>46213</v>
       </c>
       <c r="O66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46397</v>
       </c>
       <c r="P66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46578</v>
       </c>
       <c r="Q66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46762</v>
       </c>
       <c r="R66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46944</v>
       </c>
       <c r="S66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47128</v>
       </c>
       <c r="T66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47309</v>
       </c>
       <c r="U66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47493</v>
       </c>
       <c r="V66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47674</v>
       </c>
       <c r="W66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47858</v>
       </c>
       <c r="X66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48039</v>
       </c>
       <c r="Y66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48223</v>
       </c>
       <c r="Z66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48405</v>
       </c>
       <c r="AA66" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48589</v>
       </c>
       <c r="AB66" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48770</v>
       </c>
       <c r="AC66" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48954</v>
       </c>
       <c r="AD66" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49135</v>
       </c>
       <c r="AE66" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49319</v>
       </c>
       <c r="AF66" s="184">
@@ -34640,8 +34640,8 @@
         <v>49684</v>
       </c>
       <c r="AH66" s="188">
-        <f t="shared" ca="1" si="58"/>
-        <v>98</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>84</v>
       </c>
       <c r="AI66" s="203">
         <f>D66*6</f>
@@ -34683,7 +34683,7 @@
         <v>45491</v>
       </c>
       <c r="K67" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45675</v>
       </c>
       <c r="L67" s="184">
@@ -34691,79 +34691,79 @@
         <v>45856</v>
       </c>
       <c r="M67" s="214">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46040</v>
       </c>
       <c r="N67" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46221</v>
       </c>
       <c r="O67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46405</v>
       </c>
       <c r="P67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46586</v>
       </c>
       <c r="Q67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46770</v>
       </c>
       <c r="R67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46952</v>
       </c>
       <c r="S67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47136</v>
       </c>
       <c r="T67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47317</v>
       </c>
       <c r="U67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47501</v>
       </c>
       <c r="V67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47682</v>
       </c>
       <c r="W67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47866</v>
       </c>
       <c r="X67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48047</v>
       </c>
       <c r="Y67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48231</v>
       </c>
       <c r="Z67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48413</v>
       </c>
       <c r="AA67" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48597</v>
       </c>
       <c r="AB67" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48778</v>
       </c>
       <c r="AC67" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48962</v>
       </c>
       <c r="AD67" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49143</v>
       </c>
       <c r="AE67" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49327</v>
       </c>
       <c r="AF67" s="184">
@@ -34775,11 +34775,11 @@
         <v>49692</v>
       </c>
       <c r="AH67" s="188">
-        <f t="shared" ca="1" si="58"/>
-        <v>106</v>
+        <f t="shared" ca="1" si="59"/>
+        <v>92</v>
       </c>
       <c r="AI67" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>30000000</v>
       </c>
       <c r="AJ67" s="164" t="s">
@@ -34818,87 +34818,87 @@
         <v>45545</v>
       </c>
       <c r="K68" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45726</v>
       </c>
       <c r="L68" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45910</v>
       </c>
       <c r="M68" s="184">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46091</v>
       </c>
       <c r="N68" s="214">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46275</v>
       </c>
       <c r="O68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46456</v>
       </c>
       <c r="P68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46640</v>
       </c>
       <c r="Q68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46822</v>
       </c>
       <c r="R68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47006</v>
       </c>
       <c r="S68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47187</v>
       </c>
       <c r="T68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47371</v>
       </c>
       <c r="U68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47552</v>
       </c>
       <c r="V68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47736</v>
       </c>
       <c r="W68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47917</v>
       </c>
       <c r="X68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48101</v>
       </c>
       <c r="Y68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48283</v>
       </c>
       <c r="Z68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48467</v>
       </c>
       <c r="AA68" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48648</v>
       </c>
       <c r="AB68" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48832</v>
       </c>
       <c r="AC68" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49013</v>
       </c>
       <c r="AD68" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49197</v>
       </c>
       <c r="AE68" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49378</v>
       </c>
       <c r="AF68" s="184">
@@ -34911,10 +34911,10 @@
       </c>
       <c r="AH68" s="188">
         <f ca="1">N68-TODAY()</f>
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="AI68" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>33000000</v>
       </c>
       <c r="AJ68" s="164" t="s">
@@ -34953,7 +34953,7 @@
         <v>45545</v>
       </c>
       <c r="K69" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45726</v>
       </c>
       <c r="L69" s="184">
@@ -34961,79 +34961,79 @@
         <v>45910</v>
       </c>
       <c r="M69" s="184">
-        <f t="shared" ref="M69:V84" si="63">EDATE(L69,6)</f>
+        <f t="shared" ref="M69:V84" si="64">EDATE(L69,6)</f>
         <v>46091</v>
       </c>
       <c r="N69" s="214">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46275</v>
       </c>
       <c r="O69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46456</v>
       </c>
       <c r="P69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46640</v>
       </c>
       <c r="Q69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46822</v>
       </c>
       <c r="R69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47006</v>
       </c>
       <c r="S69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47187</v>
       </c>
       <c r="T69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47371</v>
       </c>
       <c r="U69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47552</v>
       </c>
       <c r="V69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47736</v>
       </c>
       <c r="W69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47917</v>
       </c>
       <c r="X69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48101</v>
       </c>
       <c r="Y69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48283</v>
       </c>
       <c r="Z69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48467</v>
       </c>
       <c r="AA69" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48648</v>
       </c>
       <c r="AB69" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48832</v>
       </c>
       <c r="AC69" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49013</v>
       </c>
       <c r="AD69" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49197</v>
       </c>
       <c r="AE69" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49378</v>
       </c>
       <c r="AF69" s="184">
@@ -35046,10 +35046,10 @@
       </c>
       <c r="AH69" s="188">
         <f ca="1">N69-TODAY()</f>
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="AI69" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>30000000</v>
       </c>
       <c r="AJ69" s="164" t="s">
@@ -35088,87 +35088,87 @@
         <v>45583</v>
       </c>
       <c r="K70" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45765</v>
       </c>
       <c r="L70" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45948</v>
       </c>
       <c r="M70" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46130</v>
       </c>
       <c r="N70" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46313</v>
       </c>
       <c r="O70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46495</v>
       </c>
       <c r="P70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46678</v>
       </c>
       <c r="Q70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46861</v>
       </c>
       <c r="R70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47044</v>
       </c>
       <c r="S70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47226</v>
       </c>
       <c r="T70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47409</v>
       </c>
       <c r="U70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47591</v>
       </c>
       <c r="V70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47774</v>
       </c>
       <c r="W70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47956</v>
       </c>
       <c r="X70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48139</v>
       </c>
       <c r="Y70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48322</v>
       </c>
       <c r="Z70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48505</v>
       </c>
       <c r="AA70" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48687</v>
       </c>
       <c r="AB70" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48870</v>
       </c>
       <c r="AC70" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49052</v>
       </c>
       <c r="AD70" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49235</v>
       </c>
       <c r="AE70" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49417</v>
       </c>
       <c r="AF70" s="184">
@@ -35180,11 +35180,11 @@
         <v>49783</v>
       </c>
       <c r="AH70" s="188">
-        <f t="shared" ref="AH70:AH73" ca="1" si="64">M70-TODAY()</f>
-        <v>15</v>
+        <f t="shared" ref="AH70:AH73" ca="1" si="65">M70-TODAY()</f>
+        <v>1</v>
       </c>
       <c r="AI70" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>30000000</v>
       </c>
       <c r="AJ70" s="164" t="s">
@@ -35223,87 +35223,87 @@
         <v>45530</v>
       </c>
       <c r="K71" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45714</v>
       </c>
       <c r="L71" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45895</v>
       </c>
       <c r="M71" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46079</v>
       </c>
       <c r="N71" s="214">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46260</v>
       </c>
       <c r="O71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46444</v>
       </c>
       <c r="P71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46625</v>
       </c>
       <c r="Q71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46809</v>
       </c>
       <c r="R71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46991</v>
       </c>
       <c r="S71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47175</v>
       </c>
       <c r="T71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47356</v>
       </c>
       <c r="U71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47540</v>
       </c>
       <c r="V71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47721</v>
       </c>
       <c r="W71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47905</v>
       </c>
       <c r="X71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48086</v>
       </c>
       <c r="Y71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48270</v>
       </c>
       <c r="Z71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48452</v>
       </c>
       <c r="AA71" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48636</v>
       </c>
       <c r="AB71" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48817</v>
       </c>
       <c r="AC71" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49001</v>
       </c>
       <c r="AD71" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49182</v>
       </c>
       <c r="AE71" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49366</v>
       </c>
       <c r="AF71" s="184">
@@ -35316,10 +35316,10 @@
       </c>
       <c r="AH71" s="188">
         <f ca="1">N71-TODAY()</f>
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="AI71" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>27000000</v>
       </c>
       <c r="AJ71" s="164" t="s">
@@ -35358,87 +35358,87 @@
         <v>45622</v>
       </c>
       <c r="K72" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45803</v>
       </c>
       <c r="L72" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45987</v>
       </c>
       <c r="M72" s="214">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46168</v>
       </c>
       <c r="N72" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46352</v>
       </c>
       <c r="O72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46533</v>
       </c>
       <c r="P72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46717</v>
       </c>
       <c r="Q72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46899</v>
       </c>
       <c r="R72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47083</v>
       </c>
       <c r="S72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47264</v>
       </c>
       <c r="T72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47448</v>
       </c>
       <c r="U72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47629</v>
       </c>
       <c r="V72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47813</v>
       </c>
       <c r="W72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47994</v>
       </c>
       <c r="X72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48178</v>
       </c>
       <c r="Y72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48360</v>
       </c>
       <c r="Z72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48544</v>
       </c>
       <c r="AA72" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48725</v>
       </c>
       <c r="AB72" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48909</v>
       </c>
       <c r="AC72" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49090</v>
       </c>
       <c r="AD72" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49274</v>
       </c>
       <c r="AE72" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49455</v>
       </c>
       <c r="AF72" s="184">
@@ -35450,11 +35450,11 @@
         <v>49821</v>
       </c>
       <c r="AH72" s="188">
-        <f t="shared" ca="1" si="64"/>
-        <v>53</v>
+        <f t="shared" ca="1" si="65"/>
+        <v>39</v>
       </c>
       <c r="AI72" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>36000000</v>
       </c>
       <c r="AJ72" s="164" t="s">
@@ -35493,87 +35493,87 @@
         <v>45639</v>
       </c>
       <c r="K73" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45821</v>
       </c>
       <c r="L73" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>46004</v>
       </c>
       <c r="M73" s="214">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46186</v>
       </c>
       <c r="N73" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46369</v>
       </c>
       <c r="O73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46551</v>
       </c>
       <c r="P73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46734</v>
       </c>
       <c r="Q73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46917</v>
       </c>
       <c r="R73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47100</v>
       </c>
       <c r="S73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47282</v>
       </c>
       <c r="T73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47465</v>
       </c>
       <c r="U73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47647</v>
       </c>
       <c r="V73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47830</v>
       </c>
       <c r="W73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48012</v>
       </c>
       <c r="X73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48195</v>
       </c>
       <c r="Y73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48378</v>
       </c>
       <c r="Z73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48561</v>
       </c>
       <c r="AA73" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48743</v>
       </c>
       <c r="AB73" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48926</v>
       </c>
       <c r="AC73" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49108</v>
       </c>
       <c r="AD73" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49291</v>
       </c>
       <c r="AE73" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49473</v>
       </c>
       <c r="AF73" s="184">
@@ -35585,11 +35585,11 @@
         <v>49839</v>
       </c>
       <c r="AH73" s="188">
-        <f t="shared" ca="1" si="64"/>
-        <v>71</v>
+        <f t="shared" ca="1" si="65"/>
+        <v>57</v>
       </c>
       <c r="AI73" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>24000000</v>
       </c>
       <c r="AJ73" s="164" t="s">
@@ -35628,87 +35628,87 @@
         <v>45677</v>
       </c>
       <c r="K74" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45858</v>
       </c>
       <c r="L74" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>46042</v>
       </c>
       <c r="M74" s="214">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46223</v>
       </c>
       <c r="N74" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46407</v>
       </c>
       <c r="O74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46588</v>
       </c>
       <c r="P74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46772</v>
       </c>
       <c r="Q74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46954</v>
       </c>
       <c r="R74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47138</v>
       </c>
       <c r="S74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47319</v>
       </c>
       <c r="T74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47503</v>
       </c>
       <c r="U74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47684</v>
       </c>
       <c r="V74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47868</v>
       </c>
       <c r="W74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48049</v>
       </c>
       <c r="X74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48233</v>
       </c>
       <c r="Y74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48415</v>
       </c>
       <c r="Z74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48599</v>
       </c>
       <c r="AA74" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48780</v>
       </c>
       <c r="AB74" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48964</v>
       </c>
       <c r="AC74" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49145</v>
       </c>
       <c r="AD74" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49329</v>
       </c>
       <c r="AE74" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49510</v>
       </c>
       <c r="AF74" s="184">
@@ -35721,10 +35721,10 @@
       </c>
       <c r="AH74" s="188">
         <f ca="1">M74-TODAY()</f>
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="AI74" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>42000000</v>
       </c>
       <c r="AJ74" s="164" t="s">
@@ -35763,87 +35763,87 @@
         <v>45683</v>
       </c>
       <c r="K75" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45864</v>
       </c>
       <c r="L75" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>46048</v>
       </c>
       <c r="M75" s="214">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46229</v>
       </c>
       <c r="N75" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46413</v>
       </c>
       <c r="O75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46594</v>
       </c>
       <c r="P75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46778</v>
       </c>
       <c r="Q75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46960</v>
       </c>
       <c r="R75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47144</v>
       </c>
       <c r="S75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47325</v>
       </c>
       <c r="T75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47509</v>
       </c>
       <c r="U75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47690</v>
       </c>
       <c r="V75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47874</v>
       </c>
       <c r="W75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48055</v>
       </c>
       <c r="X75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48239</v>
       </c>
       <c r="Y75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48421</v>
       </c>
       <c r="Z75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48605</v>
       </c>
       <c r="AA75" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48786</v>
       </c>
       <c r="AB75" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48970</v>
       </c>
       <c r="AC75" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49151</v>
       </c>
       <c r="AD75" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49335</v>
       </c>
       <c r="AE75" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49516</v>
       </c>
       <c r="AF75" s="184">
@@ -35856,10 +35856,10 @@
       </c>
       <c r="AH75" s="188">
         <f ca="1">M75-TODAY()</f>
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="AI75" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>24000000</v>
       </c>
       <c r="AJ75" s="164" t="s">
@@ -35898,87 +35898,87 @@
         <v>45675</v>
       </c>
       <c r="K76" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45856</v>
       </c>
       <c r="L76" s="214">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>46040</v>
       </c>
       <c r="M76" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46221</v>
       </c>
       <c r="N76" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46405</v>
       </c>
       <c r="O76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46586</v>
       </c>
       <c r="P76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46770</v>
       </c>
       <c r="Q76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46952</v>
       </c>
       <c r="R76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47136</v>
       </c>
       <c r="S76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47317</v>
       </c>
       <c r="T76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47501</v>
       </c>
       <c r="U76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47682</v>
       </c>
       <c r="V76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47866</v>
       </c>
       <c r="W76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48047</v>
       </c>
       <c r="X76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48231</v>
       </c>
       <c r="Y76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48413</v>
       </c>
       <c r="Z76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48597</v>
       </c>
       <c r="AA76" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48778</v>
       </c>
       <c r="AB76" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48962</v>
       </c>
       <c r="AC76" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49143</v>
       </c>
       <c r="AD76" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49327</v>
       </c>
       <c r="AE76" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49508</v>
       </c>
       <c r="AF76" s="184">
@@ -35991,10 +35991,10 @@
       </c>
       <c r="AH76" s="188">
         <f ca="1">M76-TODAY()</f>
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="AI76" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>24000000</v>
       </c>
       <c r="AJ76" s="164" t="s">
@@ -36033,87 +36033,87 @@
         <v>45705</v>
       </c>
       <c r="K77" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45886</v>
       </c>
       <c r="L77" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>46070</v>
       </c>
       <c r="M77" s="214">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46251</v>
       </c>
       <c r="N77" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46435</v>
       </c>
       <c r="O77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46616</v>
       </c>
       <c r="P77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46800</v>
       </c>
       <c r="Q77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46982</v>
       </c>
       <c r="R77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47166</v>
       </c>
       <c r="S77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47347</v>
       </c>
       <c r="T77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47531</v>
       </c>
       <c r="U77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47712</v>
       </c>
       <c r="V77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47896</v>
       </c>
       <c r="W77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48077</v>
       </c>
       <c r="X77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48261</v>
       </c>
       <c r="Y77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48443</v>
       </c>
       <c r="Z77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48627</v>
       </c>
       <c r="AA77" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48808</v>
       </c>
       <c r="AB77" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>48992</v>
       </c>
       <c r="AC77" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49173</v>
       </c>
       <c r="AD77" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49357</v>
       </c>
       <c r="AE77" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49538</v>
       </c>
       <c r="AF77" s="184">
@@ -36126,10 +36126,10 @@
       </c>
       <c r="AH77" s="188">
         <f ca="1">M77-TODAY()</f>
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="AI77" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>30000000</v>
       </c>
       <c r="AJ77" s="164" t="s">
@@ -36168,87 +36168,87 @@
         <v>45799</v>
       </c>
       <c r="K78" s="214">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>45983</v>
       </c>
       <c r="L78" s="184">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>46164</v>
       </c>
       <c r="M78" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46348</v>
       </c>
       <c r="N78" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46529</v>
       </c>
       <c r="O78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46713</v>
       </c>
       <c r="P78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>46895</v>
       </c>
       <c r="Q78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47079</v>
       </c>
       <c r="R78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47260</v>
       </c>
       <c r="S78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47444</v>
       </c>
       <c r="T78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47625</v>
       </c>
       <c r="U78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47809</v>
       </c>
       <c r="V78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>47990</v>
       </c>
       <c r="W78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48174</v>
       </c>
       <c r="X78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48356</v>
       </c>
       <c r="Y78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48540</v>
       </c>
       <c r="Z78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48721</v>
       </c>
       <c r="AA78" s="184">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>48905</v>
       </c>
       <c r="AB78" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49086</v>
       </c>
       <c r="AC78" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49270</v>
       </c>
       <c r="AD78" s="184">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>49451</v>
       </c>
       <c r="AE78" s="184">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>49635</v>
       </c>
       <c r="AF78" s="184">
@@ -36260,11 +36260,11 @@
         <v>50001</v>
       </c>
       <c r="AH78" s="188">
-        <f t="shared" ref="AH78:AH79" ca="1" si="65">L78-TODAY()</f>
-        <v>49</v>
+        <f t="shared" ref="AH78:AH79" ca="1" si="66">L78-TODAY()</f>
+        <v>35</v>
       </c>
       <c r="AI78" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>18000000</v>
       </c>
       <c r="AJ78" s="164" t="s">
@@ -36303,103 +36303,103 @@
         <v>45804</v>
       </c>
       <c r="K79" s="184">
+        <f t="shared" si="63"/>
+        <v>45988</v>
+      </c>
+      <c r="L79" s="214">
+        <f t="shared" si="63"/>
+        <v>46169</v>
+      </c>
+      <c r="M79" s="184">
+        <f t="shared" si="64"/>
+        <v>46353</v>
+      </c>
+      <c r="N79" s="184">
+        <f t="shared" si="64"/>
+        <v>46534</v>
+      </c>
+      <c r="O79" s="184">
+        <f t="shared" si="60"/>
+        <v>46718</v>
+      </c>
+      <c r="P79" s="184">
+        <f t="shared" si="60"/>
+        <v>46900</v>
+      </c>
+      <c r="Q79" s="184">
+        <f t="shared" si="60"/>
+        <v>47084</v>
+      </c>
+      <c r="R79" s="184">
+        <f t="shared" si="60"/>
+        <v>47265</v>
+      </c>
+      <c r="S79" s="184">
+        <f t="shared" si="60"/>
+        <v>47449</v>
+      </c>
+      <c r="T79" s="184">
+        <f t="shared" si="60"/>
+        <v>47630</v>
+      </c>
+      <c r="U79" s="184">
+        <f t="shared" si="60"/>
+        <v>47814</v>
+      </c>
+      <c r="V79" s="184">
+        <f t="shared" si="60"/>
+        <v>47995</v>
+      </c>
+      <c r="W79" s="184">
+        <f t="shared" ref="W79:AG85" si="67">EDATE(V79,6)</f>
+        <v>48179</v>
+      </c>
+      <c r="X79" s="184">
+        <f t="shared" si="67"/>
+        <v>48361</v>
+      </c>
+      <c r="Y79" s="184">
+        <f t="shared" si="67"/>
+        <v>48545</v>
+      </c>
+      <c r="Z79" s="184">
+        <f t="shared" si="67"/>
+        <v>48726</v>
+      </c>
+      <c r="AA79" s="184">
+        <f t="shared" si="67"/>
+        <v>48910</v>
+      </c>
+      <c r="AB79" s="184">
+        <f t="shared" si="67"/>
+        <v>49091</v>
+      </c>
+      <c r="AC79" s="184">
+        <f t="shared" si="67"/>
+        <v>49275</v>
+      </c>
+      <c r="AD79" s="184">
+        <f t="shared" si="67"/>
+        <v>49456</v>
+      </c>
+      <c r="AE79" s="184">
+        <f t="shared" si="67"/>
+        <v>49640</v>
+      </c>
+      <c r="AF79" s="184">
+        <f t="shared" si="67"/>
+        <v>49822</v>
+      </c>
+      <c r="AG79" s="184">
+        <f t="shared" si="67"/>
+        <v>50006</v>
+      </c>
+      <c r="AH79" s="188">
+        <f t="shared" ca="1" si="66"/>
+        <v>40</v>
+      </c>
+      <c r="AI79" s="203">
         <f t="shared" si="62"/>
-        <v>45988</v>
-      </c>
-      <c r="L79" s="214">
-        <f t="shared" si="62"/>
-        <v>46169</v>
-      </c>
-      <c r="M79" s="184">
-        <f t="shared" si="63"/>
-        <v>46353</v>
-      </c>
-      <c r="N79" s="184">
-        <f t="shared" si="63"/>
-        <v>46534</v>
-      </c>
-      <c r="O79" s="184">
-        <f t="shared" si="59"/>
-        <v>46718</v>
-      </c>
-      <c r="P79" s="184">
-        <f t="shared" si="59"/>
-        <v>46900</v>
-      </c>
-      <c r="Q79" s="184">
-        <f t="shared" si="59"/>
-        <v>47084</v>
-      </c>
-      <c r="R79" s="184">
-        <f t="shared" si="59"/>
-        <v>47265</v>
-      </c>
-      <c r="S79" s="184">
-        <f t="shared" si="59"/>
-        <v>47449</v>
-      </c>
-      <c r="T79" s="184">
-        <f t="shared" si="59"/>
-        <v>47630</v>
-      </c>
-      <c r="U79" s="184">
-        <f t="shared" si="59"/>
-        <v>47814</v>
-      </c>
-      <c r="V79" s="184">
-        <f t="shared" si="59"/>
-        <v>47995</v>
-      </c>
-      <c r="W79" s="184">
-        <f t="shared" ref="W79:AG85" si="66">EDATE(V79,6)</f>
-        <v>48179</v>
-      </c>
-      <c r="X79" s="184">
-        <f t="shared" si="66"/>
-        <v>48361</v>
-      </c>
-      <c r="Y79" s="184">
-        <f t="shared" si="66"/>
-        <v>48545</v>
-      </c>
-      <c r="Z79" s="184">
-        <f t="shared" si="66"/>
-        <v>48726</v>
-      </c>
-      <c r="AA79" s="184">
-        <f t="shared" si="66"/>
-        <v>48910</v>
-      </c>
-      <c r="AB79" s="184">
-        <f t="shared" si="66"/>
-        <v>49091</v>
-      </c>
-      <c r="AC79" s="184">
-        <f t="shared" si="66"/>
-        <v>49275</v>
-      </c>
-      <c r="AD79" s="184">
-        <f t="shared" si="66"/>
-        <v>49456</v>
-      </c>
-      <c r="AE79" s="184">
-        <f t="shared" si="66"/>
-        <v>49640</v>
-      </c>
-      <c r="AF79" s="184">
-        <f t="shared" si="66"/>
-        <v>49822</v>
-      </c>
-      <c r="AG79" s="184">
-        <f t="shared" si="66"/>
-        <v>50006</v>
-      </c>
-      <c r="AH79" s="188">
-        <f t="shared" ca="1" si="65"/>
-        <v>54</v>
-      </c>
-      <c r="AI79" s="203">
-        <f t="shared" si="61"/>
         <v>24000000</v>
       </c>
       <c r="AJ79" s="164" t="s">
@@ -36438,103 +36438,103 @@
         <v>45857</v>
       </c>
       <c r="K80" s="184">
-        <f t="shared" ref="K80:V85" si="67">EDATE(J80,6)</f>
+        <f t="shared" ref="K80:V85" si="68">EDATE(J80,6)</f>
         <v>46041</v>
       </c>
       <c r="L80" s="214">
+        <f t="shared" si="68"/>
+        <v>46222</v>
+      </c>
+      <c r="M80" s="184">
+        <f t="shared" si="64"/>
+        <v>46406</v>
+      </c>
+      <c r="N80" s="184">
+        <f t="shared" si="64"/>
+        <v>46587</v>
+      </c>
+      <c r="O80" s="184">
+        <f t="shared" si="64"/>
+        <v>46771</v>
+      </c>
+      <c r="P80" s="184">
+        <f t="shared" si="64"/>
+        <v>46953</v>
+      </c>
+      <c r="Q80" s="184">
+        <f t="shared" si="64"/>
+        <v>47137</v>
+      </c>
+      <c r="R80" s="184">
+        <f t="shared" si="64"/>
+        <v>47318</v>
+      </c>
+      <c r="S80" s="184">
+        <f t="shared" si="64"/>
+        <v>47502</v>
+      </c>
+      <c r="T80" s="184">
+        <f t="shared" si="64"/>
+        <v>47683</v>
+      </c>
+      <c r="U80" s="184">
+        <f t="shared" si="64"/>
+        <v>47867</v>
+      </c>
+      <c r="V80" s="184">
+        <f t="shared" si="64"/>
+        <v>48048</v>
+      </c>
+      <c r="W80" s="184">
         <f t="shared" si="67"/>
-        <v>46222</v>
-      </c>
-      <c r="M80" s="184">
-        <f t="shared" si="63"/>
-        <v>46406</v>
-      </c>
-      <c r="N80" s="184">
-        <f t="shared" si="63"/>
-        <v>46587</v>
-      </c>
-      <c r="O80" s="184">
-        <f t="shared" si="63"/>
-        <v>46771</v>
-      </c>
-      <c r="P80" s="184">
-        <f t="shared" si="63"/>
-        <v>46953</v>
-      </c>
-      <c r="Q80" s="184">
-        <f t="shared" si="63"/>
-        <v>47137</v>
-      </c>
-      <c r="R80" s="184">
-        <f t="shared" si="63"/>
-        <v>47318</v>
-      </c>
-      <c r="S80" s="184">
-        <f t="shared" si="63"/>
-        <v>47502</v>
-      </c>
-      <c r="T80" s="184">
-        <f t="shared" si="63"/>
-        <v>47683</v>
-      </c>
-      <c r="U80" s="184">
-        <f t="shared" si="63"/>
-        <v>47867</v>
-      </c>
-      <c r="V80" s="184">
-        <f t="shared" si="63"/>
-        <v>48048</v>
-      </c>
-      <c r="W80" s="184">
-        <f t="shared" si="66"/>
         <v>48232</v>
       </c>
       <c r="X80" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48414</v>
       </c>
       <c r="Y80" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48598</v>
       </c>
       <c r="Z80" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48779</v>
       </c>
       <c r="AA80" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48963</v>
       </c>
       <c r="AB80" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49144</v>
       </c>
       <c r="AC80" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49328</v>
       </c>
       <c r="AD80" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49509</v>
       </c>
       <c r="AE80" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49693</v>
       </c>
       <c r="AF80" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49875</v>
       </c>
       <c r="AG80" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>50059</v>
       </c>
       <c r="AH80" s="188">
         <f ca="1">L80-TODAY()</f>
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="AI80" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>30000000</v>
       </c>
       <c r="AJ80" s="222" t="s">
@@ -36581,95 +36581,95 @@
         <v>46235</v>
       </c>
       <c r="M81" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46419</v>
       </c>
       <c r="N81" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46600</v>
       </c>
       <c r="O81" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46784</v>
       </c>
       <c r="P81" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>46966</v>
       </c>
       <c r="Q81" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>47150</v>
       </c>
       <c r="R81" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>47331</v>
       </c>
       <c r="S81" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>47515</v>
       </c>
       <c r="T81" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>47696</v>
       </c>
       <c r="U81" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>47880</v>
       </c>
       <c r="V81" s="184">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>48061</v>
       </c>
       <c r="W81" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48245</v>
       </c>
       <c r="X81" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48427</v>
       </c>
       <c r="Y81" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48611</v>
       </c>
       <c r="Z81" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48792</v>
       </c>
       <c r="AA81" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48976</v>
       </c>
       <c r="AB81" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49157</v>
       </c>
       <c r="AC81" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49341</v>
       </c>
       <c r="AD81" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49522</v>
       </c>
       <c r="AE81" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49706</v>
       </c>
       <c r="AF81" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49888</v>
       </c>
       <c r="AG81" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>50072</v>
       </c>
       <c r="AH81" s="188">
         <f ca="1">L81-TODAY()</f>
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AI81" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>30000000</v>
       </c>
       <c r="AJ81" s="164" t="s">
@@ -36712,99 +36712,99 @@
         <v>46030</v>
       </c>
       <c r="L82" s="214">
+        <f t="shared" si="68"/>
+        <v>46211</v>
+      </c>
+      <c r="M82" s="184">
+        <f t="shared" si="64"/>
+        <v>46395</v>
+      </c>
+      <c r="N82" s="184">
+        <f t="shared" si="64"/>
+        <v>46576</v>
+      </c>
+      <c r="O82" s="184">
+        <f t="shared" si="64"/>
+        <v>46760</v>
+      </c>
+      <c r="P82" s="184">
+        <f t="shared" si="64"/>
+        <v>46942</v>
+      </c>
+      <c r="Q82" s="184">
+        <f t="shared" si="64"/>
+        <v>47126</v>
+      </c>
+      <c r="R82" s="184">
+        <f t="shared" si="64"/>
+        <v>47307</v>
+      </c>
+      <c r="S82" s="184">
+        <f t="shared" si="64"/>
+        <v>47491</v>
+      </c>
+      <c r="T82" s="184">
+        <f t="shared" si="64"/>
+        <v>47672</v>
+      </c>
+      <c r="U82" s="184">
+        <f t="shared" si="64"/>
+        <v>47856</v>
+      </c>
+      <c r="V82" s="184">
+        <f t="shared" si="64"/>
+        <v>48037</v>
+      </c>
+      <c r="W82" s="184">
         <f t="shared" si="67"/>
-        <v>46211</v>
-      </c>
-      <c r="M82" s="184">
-        <f t="shared" si="63"/>
-        <v>46395</v>
-      </c>
-      <c r="N82" s="184">
-        <f t="shared" si="63"/>
-        <v>46576</v>
-      </c>
-      <c r="O82" s="184">
-        <f t="shared" si="63"/>
-        <v>46760</v>
-      </c>
-      <c r="P82" s="184">
-        <f t="shared" si="63"/>
-        <v>46942</v>
-      </c>
-      <c r="Q82" s="184">
-        <f t="shared" si="63"/>
-        <v>47126</v>
-      </c>
-      <c r="R82" s="184">
-        <f t="shared" si="63"/>
-        <v>47307</v>
-      </c>
-      <c r="S82" s="184">
-        <f t="shared" si="63"/>
-        <v>47491</v>
-      </c>
-      <c r="T82" s="184">
-        <f t="shared" si="63"/>
-        <v>47672</v>
-      </c>
-      <c r="U82" s="184">
-        <f t="shared" si="63"/>
-        <v>47856</v>
-      </c>
-      <c r="V82" s="184">
-        <f t="shared" si="63"/>
-        <v>48037</v>
-      </c>
-      <c r="W82" s="184">
-        <f t="shared" si="66"/>
         <v>48221</v>
       </c>
       <c r="X82" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48403</v>
       </c>
       <c r="Y82" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48587</v>
       </c>
       <c r="Z82" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48768</v>
       </c>
       <c r="AA82" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48952</v>
       </c>
       <c r="AB82" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49133</v>
       </c>
       <c r="AC82" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49317</v>
       </c>
       <c r="AD82" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49498</v>
       </c>
       <c r="AE82" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49682</v>
       </c>
       <c r="AF82" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49864</v>
       </c>
       <c r="AG82" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>50048</v>
       </c>
       <c r="AH82" s="188">
         <f ca="1">L82-TODAY()</f>
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="AI82" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>24000000</v>
       </c>
       <c r="AJ82" s="222" t="s">
@@ -36847,99 +36847,99 @@
         <v>46031</v>
       </c>
       <c r="L83" s="214">
+        <f t="shared" si="68"/>
+        <v>46212</v>
+      </c>
+      <c r="M83" s="184">
+        <f t="shared" si="64"/>
+        <v>46396</v>
+      </c>
+      <c r="N83" s="184">
+        <f t="shared" si="64"/>
+        <v>46577</v>
+      </c>
+      <c r="O83" s="184">
+        <f t="shared" si="64"/>
+        <v>46761</v>
+      </c>
+      <c r="P83" s="184">
+        <f t="shared" si="64"/>
+        <v>46943</v>
+      </c>
+      <c r="Q83" s="184">
+        <f t="shared" si="64"/>
+        <v>47127</v>
+      </c>
+      <c r="R83" s="184">
+        <f t="shared" si="64"/>
+        <v>47308</v>
+      </c>
+      <c r="S83" s="184">
+        <f t="shared" si="64"/>
+        <v>47492</v>
+      </c>
+      <c r="T83" s="184">
+        <f t="shared" si="64"/>
+        <v>47673</v>
+      </c>
+      <c r="U83" s="184">
+        <f t="shared" si="64"/>
+        <v>47857</v>
+      </c>
+      <c r="V83" s="184">
+        <f t="shared" si="64"/>
+        <v>48038</v>
+      </c>
+      <c r="W83" s="184">
         <f t="shared" si="67"/>
-        <v>46212</v>
-      </c>
-      <c r="M83" s="184">
-        <f t="shared" si="63"/>
-        <v>46396</v>
-      </c>
-      <c r="N83" s="184">
-        <f t="shared" si="63"/>
-        <v>46577</v>
-      </c>
-      <c r="O83" s="184">
-        <f t="shared" si="63"/>
-        <v>46761</v>
-      </c>
-      <c r="P83" s="184">
-        <f t="shared" si="63"/>
-        <v>46943</v>
-      </c>
-      <c r="Q83" s="184">
-        <f t="shared" si="63"/>
-        <v>47127</v>
-      </c>
-      <c r="R83" s="184">
-        <f t="shared" si="63"/>
-        <v>47308</v>
-      </c>
-      <c r="S83" s="184">
-        <f t="shared" si="63"/>
-        <v>47492</v>
-      </c>
-      <c r="T83" s="184">
-        <f t="shared" si="63"/>
-        <v>47673</v>
-      </c>
-      <c r="U83" s="184">
-        <f t="shared" si="63"/>
-        <v>47857</v>
-      </c>
-      <c r="V83" s="184">
-        <f t="shared" si="63"/>
-        <v>48038</v>
-      </c>
-      <c r="W83" s="184">
-        <f t="shared" si="66"/>
         <v>48222</v>
       </c>
       <c r="X83" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48404</v>
       </c>
       <c r="Y83" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48588</v>
       </c>
       <c r="Z83" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48769</v>
       </c>
       <c r="AA83" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48953</v>
       </c>
       <c r="AB83" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49134</v>
       </c>
       <c r="AC83" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49318</v>
       </c>
       <c r="AD83" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49499</v>
       </c>
       <c r="AE83" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49683</v>
       </c>
       <c r="AF83" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49865</v>
       </c>
       <c r="AG83" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>50049</v>
       </c>
       <c r="AH83" s="188">
         <f ca="1">L83-TODAY()</f>
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="AI83" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>30000000</v>
       </c>
       <c r="AJ83" s="164" t="s">
@@ -36982,99 +36982,99 @@
         <v>46086</v>
       </c>
       <c r="L84" s="214">
+        <f t="shared" si="68"/>
+        <v>46270</v>
+      </c>
+      <c r="M84" s="184">
+        <f t="shared" si="64"/>
+        <v>46451</v>
+      </c>
+      <c r="N84" s="184">
+        <f t="shared" si="64"/>
+        <v>46635</v>
+      </c>
+      <c r="O84" s="184">
+        <f t="shared" si="64"/>
+        <v>46817</v>
+      </c>
+      <c r="P84" s="184">
+        <f t="shared" si="64"/>
+        <v>47001</v>
+      </c>
+      <c r="Q84" s="184">
+        <f t="shared" si="64"/>
+        <v>47182</v>
+      </c>
+      <c r="R84" s="184">
+        <f t="shared" si="64"/>
+        <v>47366</v>
+      </c>
+      <c r="S84" s="184">
+        <f t="shared" si="64"/>
+        <v>47547</v>
+      </c>
+      <c r="T84" s="184">
+        <f t="shared" si="64"/>
+        <v>47731</v>
+      </c>
+      <c r="U84" s="184">
+        <f t="shared" si="64"/>
+        <v>47912</v>
+      </c>
+      <c r="V84" s="184">
+        <f t="shared" si="64"/>
+        <v>48096</v>
+      </c>
+      <c r="W84" s="184">
         <f t="shared" si="67"/>
-        <v>46270</v>
-      </c>
-      <c r="M84" s="184">
-        <f t="shared" si="63"/>
-        <v>46451</v>
-      </c>
-      <c r="N84" s="184">
-        <f t="shared" si="63"/>
-        <v>46635</v>
-      </c>
-      <c r="O84" s="184">
-        <f t="shared" si="63"/>
-        <v>46817</v>
-      </c>
-      <c r="P84" s="184">
-        <f t="shared" si="63"/>
-        <v>47001</v>
-      </c>
-      <c r="Q84" s="184">
-        <f t="shared" si="63"/>
-        <v>47182</v>
-      </c>
-      <c r="R84" s="184">
-        <f t="shared" si="63"/>
-        <v>47366</v>
-      </c>
-      <c r="S84" s="184">
-        <f t="shared" si="63"/>
-        <v>47547</v>
-      </c>
-      <c r="T84" s="184">
-        <f t="shared" si="63"/>
-        <v>47731</v>
-      </c>
-      <c r="U84" s="184">
-        <f t="shared" si="63"/>
-        <v>47912</v>
-      </c>
-      <c r="V84" s="184">
-        <f t="shared" si="63"/>
-        <v>48096</v>
-      </c>
-      <c r="W84" s="184">
-        <f t="shared" si="66"/>
         <v>48278</v>
       </c>
       <c r="X84" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48462</v>
       </c>
       <c r="Y84" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48643</v>
       </c>
       <c r="Z84" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>48827</v>
       </c>
       <c r="AA84" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49008</v>
       </c>
       <c r="AB84" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49192</v>
       </c>
       <c r="AC84" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49373</v>
       </c>
       <c r="AD84" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49557</v>
       </c>
       <c r="AE84" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49739</v>
       </c>
       <c r="AF84" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>49923</v>
       </c>
       <c r="AG84" s="184">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>50104</v>
       </c>
       <c r="AH84" s="188">
         <f ca="1">L84-TODAY()</f>
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="AI84" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>24000000</v>
       </c>
       <c r="AJ84" s="164" t="s">
@@ -37117,99 +37117,99 @@
         <v>46113</v>
       </c>
       <c r="L85" s="184">
+        <f t="shared" si="68"/>
+        <v>46296</v>
+      </c>
+      <c r="M85" s="184">
+        <f t="shared" si="68"/>
+        <v>46478</v>
+      </c>
+      <c r="N85" s="184">
+        <f t="shared" si="68"/>
+        <v>46661</v>
+      </c>
+      <c r="O85" s="184">
+        <f t="shared" si="68"/>
+        <v>46844</v>
+      </c>
+      <c r="P85" s="184">
+        <f t="shared" si="68"/>
+        <v>47027</v>
+      </c>
+      <c r="Q85" s="184">
+        <f t="shared" si="68"/>
+        <v>47209</v>
+      </c>
+      <c r="R85" s="184">
+        <f t="shared" si="68"/>
+        <v>47392</v>
+      </c>
+      <c r="S85" s="184">
+        <f t="shared" si="68"/>
+        <v>47574</v>
+      </c>
+      <c r="T85" s="184">
+        <f t="shared" si="68"/>
+        <v>47757</v>
+      </c>
+      <c r="U85" s="184">
+        <f t="shared" si="68"/>
+        <v>47939</v>
+      </c>
+      <c r="V85" s="184">
+        <f t="shared" si="68"/>
+        <v>48122</v>
+      </c>
+      <c r="W85" s="184">
         <f t="shared" si="67"/>
-        <v>46296</v>
-      </c>
-      <c r="M85" s="184">
+        <v>48305</v>
+      </c>
+      <c r="X85" s="184">
         <f t="shared" si="67"/>
-        <v>46478</v>
-      </c>
-      <c r="N85" s="184">
+        <v>48488</v>
+      </c>
+      <c r="Y85" s="184">
         <f t="shared" si="67"/>
-        <v>46661</v>
-      </c>
-      <c r="O85" s="184">
+        <v>48670</v>
+      </c>
+      <c r="Z85" s="184">
         <f t="shared" si="67"/>
-        <v>46844</v>
-      </c>
-      <c r="P85" s="184">
+        <v>48853</v>
+      </c>
+      <c r="AA85" s="184">
         <f t="shared" si="67"/>
-        <v>47027</v>
-      </c>
-      <c r="Q85" s="184">
+        <v>49035</v>
+      </c>
+      <c r="AB85" s="184">
         <f t="shared" si="67"/>
-        <v>47209</v>
-      </c>
-      <c r="R85" s="184">
+        <v>49218</v>
+      </c>
+      <c r="AC85" s="184">
         <f t="shared" si="67"/>
-        <v>47392</v>
-      </c>
-      <c r="S85" s="184">
+        <v>49400</v>
+      </c>
+      <c r="AD85" s="184">
         <f t="shared" si="67"/>
-        <v>47574</v>
-      </c>
-      <c r="T85" s="184">
+        <v>49583</v>
+      </c>
+      <c r="AE85" s="184">
         <f t="shared" si="67"/>
-        <v>47757</v>
-      </c>
-      <c r="U85" s="184">
+        <v>49766</v>
+      </c>
+      <c r="AF85" s="184">
         <f t="shared" si="67"/>
-        <v>47939</v>
-      </c>
-      <c r="V85" s="184">
+        <v>49949</v>
+      </c>
+      <c r="AG85" s="184">
         <f t="shared" si="67"/>
-        <v>48122</v>
-      </c>
-      <c r="W85" s="184">
-        <f t="shared" si="66"/>
-        <v>48305</v>
-      </c>
-      <c r="X85" s="184">
-        <f t="shared" si="66"/>
-        <v>48488</v>
-      </c>
-      <c r="Y85" s="184">
-        <f t="shared" si="66"/>
-        <v>48670</v>
-      </c>
-      <c r="Z85" s="184">
-        <f t="shared" si="66"/>
-        <v>48853</v>
-      </c>
-      <c r="AA85" s="184">
-        <f t="shared" si="66"/>
-        <v>49035</v>
-      </c>
-      <c r="AB85" s="184">
-        <f t="shared" si="66"/>
-        <v>49218</v>
-      </c>
-      <c r="AC85" s="184">
-        <f t="shared" si="66"/>
-        <v>49400</v>
-      </c>
-      <c r="AD85" s="184">
-        <f t="shared" si="66"/>
-        <v>49583</v>
-      </c>
-      <c r="AE85" s="184">
-        <f t="shared" si="66"/>
-        <v>49766</v>
-      </c>
-      <c r="AF85" s="184">
-        <f t="shared" si="66"/>
-        <v>49949</v>
-      </c>
-      <c r="AG85" s="184">
-        <f t="shared" si="66"/>
         <v>50131</v>
       </c>
       <c r="AH85" s="188">
         <f ca="1">K85-TODAY()</f>
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="AI85" s="203">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>36000000</v>
       </c>
       <c r="AJ85" s="164" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14101549-0797-461E-B20B-933AF83FEE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B029BB51-220C-4013-BCE3-4AD8A8F0E637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,7 +507,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3372" uniqueCount="1171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3372" uniqueCount="1172">
   <si>
     <t>filter</t>
   </si>
@@ -4323,6 +4323,9 @@
   </si>
   <si>
     <t>Delta, lãi ròng/tháng</t>
+  </si>
+  <si>
+    <t>1 tháng</t>
   </si>
 </sst>
 </file>
@@ -31844,7 +31847,7 @@
         <v>585</v>
       </c>
       <c r="I46" s="199" t="s">
-        <v>79</v>
+        <v>1171</v>
       </c>
       <c r="J46" s="169">
         <v>45122</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B029BB51-220C-4013-BCE3-4AD8A8F0E637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E82AD0-0979-42C5-8AA0-6D8816EE6E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17977,7 +17977,7 @@
       </c>
       <c r="AE49" s="87"/>
       <c r="AF49" s="113" t="s">
-        <v>79</v>
+        <v>1171</v>
       </c>
       <c r="AG49" s="120"/>
       <c r="AH49" s="121" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E82AD0-0979-42C5-8AA0-6D8816EE6E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA159F23-1166-4A34-AAAA-B909DB223AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Theo dõi HĐ_Chi tiết" sheetId="2" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF96CB6C-9B89-4AEF-BAA3-2D7F3605BDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75C998A-57BD-43C1-A418-C0C0D6D868F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8515BA71-0917-47F5-9BEA-87E4A51C814B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9681ED5-38F2-43D5-BE75-D597D075FB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Theo dõi HĐ_Chi tiết" sheetId="2" r:id="rId1"/>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="AR41" s="120"/>
     </row>
-    <row r="42" spans="1:44" s="121" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:44" s="121" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>39</v>
       </c>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="AJ4" s="169">
         <f ca="1">AC4-TODAY()</f>
-        <v>-117</v>
+        <v>-125</v>
       </c>
       <c r="AK4" s="170">
         <f>3*D4</f>
@@ -20878,7 +20878,7 @@
       </c>
       <c r="AJ5" s="179">
         <f ca="1">AD5-TODAY()</f>
-        <v>-82</v>
+        <v>-90</v>
       </c>
       <c r="AK5" s="173">
         <f>3*D5</f>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="AJ6" s="169">
         <f ca="1">AB6-TODAY()</f>
-        <v>-118</v>
+        <v>-126</v>
       </c>
       <c r="AK6" s="170">
         <f>3*D6</f>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="AJ7" s="179">
         <f ca="1">T7-TODAY()</f>
-        <v>-147</v>
+        <v>-155</v>
       </c>
       <c r="AK7" s="173">
         <f>6*D7</f>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="AJ8" s="186">
         <f ca="1">AB8-TODAY()</f>
-        <v>-87</v>
+        <v>-95</v>
       </c>
       <c r="AK8" s="164">
         <f>3*D8</f>
@@ -21426,7 +21426,7 @@
       </c>
       <c r="AJ9" s="169">
         <f ca="1">AB9-TODAY()</f>
-        <v>-103</v>
+        <v>-111</v>
       </c>
       <c r="AK9" s="164">
         <f>3*D9</f>
@@ -21563,7 +21563,7 @@
       </c>
       <c r="AJ10" s="169">
         <f ca="1">AB10-TODAY()</f>
-        <v>-147</v>
+        <v>-155</v>
       </c>
       <c r="AK10" s="164">
         <f>D10*3</f>
@@ -21700,7 +21700,7 @@
       </c>
       <c r="AJ11" s="169">
         <f ca="1">AB11-TODAY()</f>
-        <v>-154</v>
+        <v>-162</v>
       </c>
       <c r="AK11" s="187">
         <f>D11*3</f>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="AJ12" s="169">
         <f ca="1">AA12-TODAY()</f>
-        <v>-147</v>
+        <v>-155</v>
       </c>
       <c r="AK12" s="164">
         <f>3*D12</f>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="AJ13" s="169">
         <f ca="1">AB13-TODAY()</f>
-        <v>-146</v>
+        <v>-154</v>
       </c>
       <c r="AK13" s="164">
         <f>3*7000000</f>
@@ -22111,7 +22111,7 @@
       </c>
       <c r="AJ14" s="186">
         <f ca="1">AA14-TODAY()</f>
-        <v>-137</v>
+        <v>-145</v>
       </c>
       <c r="AK14" s="164">
         <f>3*D14</f>
@@ -22248,7 +22248,7 @@
       </c>
       <c r="AJ15" s="186">
         <f ca="1">T15-TODAY()</f>
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="AK15" s="164">
         <f>6*D15</f>
@@ -22384,7 +22384,7 @@
       </c>
       <c r="AJ16" s="169">
         <f ca="1">T16-TODAY()</f>
-        <v>-93</v>
+        <v>-101</v>
       </c>
       <c r="AK16" s="164">
         <f>6*D16</f>
@@ -22525,7 +22525,7 @@
       </c>
       <c r="AJ17" s="186">
         <f ca="1">AB17-TODAY()</f>
-        <v>-86</v>
+        <v>-94</v>
       </c>
       <c r="AK17" s="164">
         <f>3*D17</f>
@@ -22662,7 +22662,7 @@
       </c>
       <c r="AJ18" s="186">
         <f ca="1">T18-TODAY()</f>
-        <v>-72</v>
+        <v>-80</v>
       </c>
       <c r="AK18" s="164">
         <f>6*D18</f>
@@ -22799,7 +22799,7 @@
       </c>
       <c r="AJ19" s="186">
         <f ca="1">AA19-TODAY()</f>
-        <v>-106</v>
+        <v>-114</v>
       </c>
       <c r="AK19" s="164">
         <f>3*D19</f>
@@ -22936,7 +22936,7 @@
       </c>
       <c r="AJ20" s="192">
         <f ca="1">T20-TODAY()</f>
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="AK20" s="173">
         <f>6*D20</f>
@@ -23073,7 +23073,7 @@
       </c>
       <c r="AJ21" s="186">
         <f ca="1">AB21-TODAY()</f>
-        <v>-82</v>
+        <v>-90</v>
       </c>
       <c r="AK21" s="164">
         <f>3*D21</f>
@@ -23210,7 +23210,7 @@
       </c>
       <c r="AJ22" s="186">
         <f ca="1">T22-TODAY()</f>
-        <v>-18</v>
+        <v>-26</v>
       </c>
       <c r="AK22" s="164">
         <f>6*D22</f>
@@ -23347,7 +23347,7 @@
       </c>
       <c r="AJ23" s="186">
         <f ca="1">T23-TODAY()</f>
-        <v>-18</v>
+        <v>-26</v>
       </c>
       <c r="AK23" s="164">
         <f>D23*6</f>
@@ -23484,7 +23484,7 @@
       </c>
       <c r="AJ24" s="186">
         <f ca="1">Z24-TODAY()</f>
-        <v>-65</v>
+        <v>-73</v>
       </c>
       <c r="AK24" s="187">
         <f>3*D24</f>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="AJ25" s="192">
         <f ca="1">AA25-TODAY()</f>
-        <v>-103</v>
+        <v>-111</v>
       </c>
       <c r="AK25" s="173">
         <f>3*D25</f>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="AJ26" s="186">
         <f ca="1">S26-TODAY()</f>
-        <v>-147</v>
+        <v>-155</v>
       </c>
       <c r="AK26" s="164">
         <f>6*D26</f>
@@ -23895,7 +23895,7 @@
       </c>
       <c r="AJ27" s="186">
         <f ca="1">AA27-TODAY()</f>
-        <v>-117</v>
+        <v>-125</v>
       </c>
       <c r="AK27" s="164">
         <f>3*D27</f>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="AJ28" s="192">
         <f ca="1">T28-TODAY()</f>
-        <v>-71</v>
+        <v>-79</v>
       </c>
       <c r="AK28" s="173">
         <f>6*D28</f>
@@ -24167,7 +24167,7 @@
       </c>
       <c r="AJ29" s="186">
         <f ca="1">U29-TODAY()</f>
-        <v>-56</v>
+        <v>-64</v>
       </c>
       <c r="AK29" s="201">
         <f>D29*6</f>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="AJ30" s="186">
         <f ca="1">Z30-TODAY()</f>
-        <v>-113</v>
+        <v>-121</v>
       </c>
       <c r="AK30" s="201">
         <f>D30*3</f>
@@ -24441,7 +24441,7 @@
       </c>
       <c r="AJ31" s="192">
         <f ca="1">T31-TODAY()</f>
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AK31" s="194">
         <f>D31*6</f>
@@ -24578,7 +24578,7 @@
       </c>
       <c r="AJ32" s="186">
         <f ca="1">Z32-TODAY()</f>
-        <v>-77</v>
+        <v>-85</v>
       </c>
       <c r="AK32" s="201">
         <f t="shared" ref="AK32:AK36" si="41">D32*3</f>
@@ -24715,7 +24715,7 @@
       </c>
       <c r="AJ33" s="186">
         <f ca="1">Z33-TODAY()</f>
-        <v>-120</v>
+        <v>-128</v>
       </c>
       <c r="AK33" s="205">
         <f t="shared" si="41"/>
@@ -24852,7 +24852,7 @@
       </c>
       <c r="AJ34" s="192">
         <f ca="1">Z34-TODAY()</f>
-        <v>-93</v>
+        <v>-101</v>
       </c>
       <c r="AK34" s="194">
         <f t="shared" si="41"/>
@@ -24989,7 +24989,7 @@
       </c>
       <c r="AJ35" s="186">
         <f ca="1">Z35-TODAY()</f>
-        <v>-87</v>
+        <v>-95</v>
       </c>
       <c r="AK35" s="201">
         <f t="shared" si="41"/>
@@ -25126,7 +25126,7 @@
       </c>
       <c r="AJ36" s="186">
         <f ca="1">Z36-TODAY()</f>
-        <v>-87</v>
+        <v>-95</v>
       </c>
       <c r="AK36" s="201">
         <f t="shared" si="41"/>
@@ -25262,7 +25262,7 @@
       </c>
       <c r="AJ37" s="186">
         <f ca="1">S37-TODAY()</f>
-        <v>-86</v>
+        <v>-94</v>
       </c>
       <c r="AK37" s="201">
         <f>D37*6</f>
@@ -25399,7 +25399,7 @@
       </c>
       <c r="AJ38" s="186">
         <f ca="1">S38-TODAY()</f>
-        <v>-86</v>
+        <v>-94</v>
       </c>
       <c r="AK38" s="201">
         <f>D38*6</f>
@@ -25536,7 +25536,7 @@
       </c>
       <c r="AJ39" s="186">
         <f ca="1">S39-TODAY()</f>
-        <v>-72</v>
+        <v>-80</v>
       </c>
       <c r="AK39" s="201">
         <f>D39*6</f>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="AJ40" s="186">
         <f ca="1">Z40-TODAY()</f>
-        <v>-72</v>
+        <v>-80</v>
       </c>
       <c r="AK40" s="201">
         <f>D40*3</f>
@@ -25810,7 +25810,7 @@
       </c>
       <c r="AJ41" s="186">
         <f ca="1">Y41-TODAY()</f>
-        <v>-154</v>
+        <v>-162</v>
       </c>
       <c r="AK41" s="201">
         <f>D41*3</f>
@@ -25947,7 +25947,7 @@
       </c>
       <c r="AJ42" s="186">
         <f ca="1">X42-TODAY()</f>
-        <v>-117</v>
+        <v>-125</v>
       </c>
       <c r="AK42" s="201">
         <f t="shared" ref="AK42:AK43" si="50">D42*3</f>
@@ -26084,7 +26084,7 @@
       </c>
       <c r="AJ43" s="192">
         <f ca="1">X43-TODAY()</f>
-        <v>-103</v>
+        <v>-111</v>
       </c>
       <c r="AK43" s="194">
         <f t="shared" si="50"/>
@@ -26218,7 +26218,7 @@
       </c>
       <c r="AJ44" s="186">
         <f ca="1">U44-TODAY()</f>
-        <v>-117</v>
+        <v>-125</v>
       </c>
       <c r="AK44" s="201">
         <f>D44*6</f>
@@ -26355,7 +26355,7 @@
       </c>
       <c r="AJ45" s="192">
         <f ca="1">R45-TODAY()</f>
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AK45" s="194">
         <f>D45*6</f>
@@ -26492,7 +26492,7 @@
       </c>
       <c r="AJ46" s="186">
         <f ca="1">Y46-TODAY()</f>
-        <v>-133</v>
+        <v>-141</v>
       </c>
       <c r="AK46" s="201">
         <f>D46*1</f>
@@ -26629,7 +26629,7 @@
       </c>
       <c r="AJ47" s="186">
         <f ca="1">R47-TODAY()</f>
-        <v>-11</v>
+        <v>-19</v>
       </c>
       <c r="AK47" s="201">
         <v>24000000</v>
@@ -26765,7 +26765,7 @@
       </c>
       <c r="AJ48" s="186">
         <f ca="1">R48-TODAY()</f>
-        <v>-11</v>
+        <v>-19</v>
       </c>
       <c r="AK48" s="201">
         <v>24000000</v>
@@ -26901,7 +26901,7 @@
       </c>
       <c r="AJ49" s="186">
         <f ca="1">R49-TODAY()</f>
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="AK49" s="201">
         <f>D49*6</f>
@@ -27038,7 +27038,7 @@
       </c>
       <c r="AJ50" s="186">
         <f t="shared" ref="AJ50:AJ54" ca="1" si="57">Q50-TODAY()</f>
-        <v>-117</v>
+        <v>-125</v>
       </c>
       <c r="AK50" s="201">
         <f>D50*6</f>
@@ -27175,7 +27175,7 @@
       </c>
       <c r="AJ51" s="186">
         <f t="shared" ca="1" si="57"/>
-        <v>-35</v>
+        <v>-43</v>
       </c>
       <c r="AK51" s="194">
         <f t="shared" ref="AK51:AK60" si="58">D51*6</f>
@@ -27312,7 +27312,7 @@
       </c>
       <c r="AJ52" s="186">
         <f t="shared" ca="1" si="57"/>
-        <v>-56</v>
+        <v>-64</v>
       </c>
       <c r="AK52" s="201">
         <f>D52*6</f>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="AJ53" s="186">
         <f t="shared" ca="1" si="57"/>
-        <v>-60</v>
+        <v>-68</v>
       </c>
       <c r="AK53" s="201">
         <f t="shared" si="58"/>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="AJ54" s="186">
         <f t="shared" ca="1" si="57"/>
-        <v>-61</v>
+        <v>-69</v>
       </c>
       <c r="AK54" s="201">
         <f t="shared" si="58"/>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="AJ55" s="186">
         <f ca="1">R55-TODAY()</f>
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="AK55" s="201">
         <f t="shared" si="58"/>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="AJ56" s="186">
         <f t="shared" ref="AJ56:AJ67" ca="1" si="60">P56-TODAY()</f>
-        <v>-151</v>
+        <v>-159</v>
       </c>
       <c r="AK56" s="201">
         <f t="shared" si="58"/>
@@ -27997,7 +27997,7 @@
       </c>
       <c r="AJ57" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-138</v>
+        <v>-146</v>
       </c>
       <c r="AK57" s="201">
         <f t="shared" si="58"/>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="AJ58" s="186">
         <f ca="1">Q58-TODAY()</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AK58" s="201">
         <f t="shared" si="58"/>
@@ -28271,7 +28271,7 @@
       </c>
       <c r="AJ59" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-117</v>
+        <v>-125</v>
       </c>
       <c r="AK59" s="201">
         <f t="shared" si="58"/>
@@ -28408,7 +28408,7 @@
       </c>
       <c r="AJ60" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-117</v>
+        <v>-125</v>
       </c>
       <c r="AK60" s="201">
         <f t="shared" si="58"/>
@@ -28545,7 +28545,7 @@
       </c>
       <c r="AJ61" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-126</v>
+        <v>-134</v>
       </c>
       <c r="AK61" s="201">
         <f>D61*6</f>
@@ -28682,7 +28682,7 @@
       </c>
       <c r="AJ62" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-81</v>
+        <v>-89</v>
       </c>
       <c r="AK62" s="201">
         <f t="shared" ref="AK62:AK85" si="63">D62*6</f>
@@ -28819,7 +28819,7 @@
       </c>
       <c r="AJ63" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-72</v>
+        <v>-80</v>
       </c>
       <c r="AK63" s="201">
         <f t="shared" si="63"/>
@@ -28956,7 +28956,7 @@
       </c>
       <c r="AJ64" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-77</v>
+        <v>-85</v>
       </c>
       <c r="AK64" s="201">
         <f>D64*6</f>
@@ -29093,7 +29093,7 @@
       </c>
       <c r="AJ65" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-67</v>
+        <v>-75</v>
       </c>
       <c r="AK65" s="201">
         <f t="shared" si="63"/>
@@ -29230,7 +29230,7 @@
       </c>
       <c r="AJ66" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-47</v>
+        <v>-55</v>
       </c>
       <c r="AK66" s="201">
         <f>D66*6</f>
@@ -29367,7 +29367,7 @@
       </c>
       <c r="AJ67" s="186">
         <f t="shared" ca="1" si="60"/>
-        <v>-39</v>
+        <v>-47</v>
       </c>
       <c r="AK67" s="201">
         <f t="shared" si="63"/>
@@ -29504,7 +29504,7 @@
       </c>
       <c r="AJ68" s="186">
         <f ca="1">P68-TODAY()</f>
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AK68" s="201">
         <f t="shared" si="63"/>
@@ -29564,88 +29564,87 @@
         <v>46091</v>
       </c>
       <c r="P69" s="212">
-        <f t="shared" si="65"/>
-        <v>46275</v>
+        <v>46266</v>
       </c>
       <c r="Q69" s="182">
-        <f t="shared" si="61"/>
-        <v>46456</v>
+        <f>EDATE(P69,6)</f>
+        <v>46447</v>
       </c>
       <c r="R69" s="182">
         <f t="shared" si="61"/>
-        <v>46640</v>
+        <v>46631</v>
       </c>
       <c r="S69" s="182">
         <f t="shared" si="61"/>
-        <v>46822</v>
+        <v>46813</v>
       </c>
       <c r="T69" s="182">
         <f t="shared" si="61"/>
-        <v>47006</v>
+        <v>46997</v>
       </c>
       <c r="U69" s="182">
         <f t="shared" si="61"/>
-        <v>47187</v>
+        <v>47178</v>
       </c>
       <c r="V69" s="182">
         <f t="shared" si="61"/>
-        <v>47371</v>
+        <v>47362</v>
       </c>
       <c r="W69" s="182">
         <f t="shared" si="61"/>
-        <v>47552</v>
+        <v>47543</v>
       </c>
       <c r="X69" s="182">
         <f t="shared" si="61"/>
-        <v>47736</v>
+        <v>47727</v>
       </c>
       <c r="Y69" s="182">
         <f t="shared" si="61"/>
-        <v>47917</v>
+        <v>47908</v>
       </c>
       <c r="Z69" s="182">
         <f t="shared" si="61"/>
-        <v>48101</v>
+        <v>48092</v>
       </c>
       <c r="AA69" s="182">
         <f t="shared" si="61"/>
-        <v>48283</v>
+        <v>48274</v>
       </c>
       <c r="AB69" s="182">
         <f t="shared" si="61"/>
-        <v>48467</v>
+        <v>48458</v>
       </c>
       <c r="AC69" s="182">
         <f t="shared" si="61"/>
-        <v>48648</v>
+        <v>48639</v>
       </c>
       <c r="AD69" s="182">
         <f t="shared" si="62"/>
-        <v>48832</v>
+        <v>48823</v>
       </c>
       <c r="AE69" s="182">
         <f t="shared" si="62"/>
-        <v>49013</v>
+        <v>49004</v>
       </c>
       <c r="AF69" s="182">
         <f t="shared" si="62"/>
-        <v>49197</v>
+        <v>49188</v>
       </c>
       <c r="AG69" s="182">
         <f t="shared" si="56"/>
-        <v>49378</v>
+        <v>49369</v>
       </c>
       <c r="AH69" s="182">
         <f t="shared" si="52"/>
-        <v>49562</v>
+        <v>49553</v>
       </c>
       <c r="AI69" s="182">
         <f t="shared" si="52"/>
-        <v>49744</v>
+        <v>49735</v>
       </c>
       <c r="AJ69" s="186">
         <f ca="1">P69-TODAY()</f>
-        <v>15</v>
+        <v>-2</v>
       </c>
       <c r="AK69" s="201">
         <f t="shared" si="63"/>
@@ -29782,7 +29781,7 @@
       </c>
       <c r="AJ70" s="186">
         <f t="shared" ref="AJ70:AJ73" ca="1" si="66">O70-TODAY()</f>
-        <v>-130</v>
+        <v>-138</v>
       </c>
       <c r="AK70" s="201">
         <f t="shared" si="63"/>
@@ -29919,7 +29918,7 @@
       </c>
       <c r="AJ71" s="186">
         <f ca="1">P71-TODAY()</f>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AK71" s="201">
         <f t="shared" si="63"/>
@@ -30056,7 +30055,7 @@
       </c>
       <c r="AJ72" s="186">
         <f t="shared" ca="1" si="66"/>
-        <v>-92</v>
+        <v>-100</v>
       </c>
       <c r="AK72" s="201">
         <f t="shared" si="63"/>
@@ -30193,7 +30192,7 @@
       </c>
       <c r="AJ73" s="186">
         <f t="shared" ca="1" si="66"/>
-        <v>-74</v>
+        <v>-82</v>
       </c>
       <c r="AK73" s="201">
         <f t="shared" si="63"/>
@@ -30330,7 +30329,7 @@
       </c>
       <c r="AJ74" s="186">
         <f ca="1">O74-TODAY()</f>
-        <v>-37</v>
+        <v>-45</v>
       </c>
       <c r="AK74" s="201">
         <f t="shared" si="63"/>
@@ -30467,7 +30466,7 @@
       </c>
       <c r="AJ75" s="186">
         <f ca="1">O75-TODAY()</f>
-        <v>-31</v>
+        <v>-39</v>
       </c>
       <c r="AK75" s="201">
         <f t="shared" si="63"/>
@@ -30604,7 +30603,7 @@
       </c>
       <c r="AJ76" s="186">
         <f ca="1">O76-TODAY()</f>
-        <v>-39</v>
+        <v>-47</v>
       </c>
       <c r="AK76" s="201">
         <f t="shared" si="63"/>
@@ -30741,7 +30740,7 @@
       </c>
       <c r="AJ77" s="186">
         <f ca="1">O77-TODAY()</f>
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="AK77" s="201">
         <f t="shared" si="63"/>
@@ -30882,7 +30881,7 @@
       </c>
       <c r="AJ78" s="186">
         <f t="shared" ref="AJ78:AJ79" ca="1" si="67">N78-TODAY()</f>
-        <v>-96</v>
+        <v>-104</v>
       </c>
       <c r="AK78" s="201">
         <f t="shared" si="63"/>
@@ -31019,7 +31018,7 @@
       </c>
       <c r="AJ79" s="186">
         <f t="shared" ca="1" si="67"/>
-        <v>-91</v>
+        <v>-99</v>
       </c>
       <c r="AK79" s="201">
         <f t="shared" si="63"/>
@@ -31156,7 +31155,7 @@
       </c>
       <c r="AJ80" s="186">
         <f ca="1">N80-TODAY()</f>
-        <v>-38</v>
+        <v>-46</v>
       </c>
       <c r="AK80" s="201">
         <f t="shared" si="63"/>
@@ -31293,7 +31292,7 @@
       </c>
       <c r="AJ81" s="186">
         <f ca="1">N81-TODAY()</f>
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="AK81" s="201">
         <f t="shared" si="63"/>
@@ -31430,7 +31429,7 @@
       </c>
       <c r="AJ82" s="186">
         <f ca="1">N82-TODAY()</f>
-        <v>-49</v>
+        <v>-57</v>
       </c>
       <c r="AK82" s="201">
         <f t="shared" si="63"/>
@@ -31567,7 +31566,7 @@
       </c>
       <c r="AJ83" s="186">
         <f ca="1">N83-TODAY()</f>
-        <v>-48</v>
+        <v>-56</v>
       </c>
       <c r="AK83" s="201">
         <f t="shared" si="63"/>
@@ -31704,7 +31703,7 @@
       </c>
       <c r="AJ84" s="186">
         <f ca="1">N84-TODAY()</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AK84" s="201">
         <f t="shared" si="63"/>
@@ -31841,7 +31840,7 @@
       </c>
       <c r="AJ85" s="186">
         <f ca="1">M85-TODAY()</f>
-        <v>-147</v>
+        <v>-155</v>
       </c>
       <c r="AK85" s="201">
         <f t="shared" si="63"/>
